--- a/gstdatabase/GSTR-1-2021-2022.xlsx
+++ b/gstdatabase/GSTR-1-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF75280A-6169-49C4-A461-CC016E00E0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AA19BE-B423-4876-9872-E5559D341374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,10 +179,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 28th Feb 2026</t>
+    <t>Data Considered upto 31st May 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 28th Feb 2026</t>
+    <t>Filing %age as on 31st May 2026</t>
   </si>
 </sst>
 </file>
@@ -671,7 +671,7 @@
   <dimension ref="A1:BJ48"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="62" width="18.77734375" customWidth="1"/>
   </cols>
@@ -1044,14 +1044,14 @@
       </c>
       <c r="J10" s="6">
         <f>K10-I10</f>
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="K10" s="5">
-        <v>52098</v>
+        <v>52099</v>
       </c>
       <c r="L10" s="7">
         <f>K10/H10</f>
-        <v>0.96526040798176871</v>
+        <v>0.96527893576417834</v>
       </c>
       <c r="M10" s="2">
         <v>85686</v>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="O10" s="6">
         <f>P10-N10</f>
-        <v>58831</v>
+        <v>58833</v>
       </c>
       <c r="P10" s="5">
-        <v>82089</v>
+        <v>82091</v>
       </c>
       <c r="Q10" s="7">
         <f>P10/M10</f>
-        <v>0.95802114697850294</v>
+        <v>0.95804448801437803</v>
       </c>
       <c r="R10" s="5">
         <v>56418</v>
@@ -1112,14 +1112,14 @@
       </c>
       <c r="AD10" s="6">
         <f>AE10-AC10</f>
-        <v>50415</v>
+        <v>50417</v>
       </c>
       <c r="AE10" s="5">
-        <v>88067</v>
+        <v>88069</v>
       </c>
       <c r="AF10" s="7">
         <f>AE10/AB10</f>
-        <v>0.94658039274697159</v>
+        <v>0.94660188957081592</v>
       </c>
       <c r="AG10" s="5">
         <v>60457</v>
@@ -1163,14 +1163,14 @@
       </c>
       <c r="AS10" s="6">
         <f>AT10-AR10</f>
-        <v>54386</v>
+        <v>54388</v>
       </c>
       <c r="AT10" s="5">
-        <v>93652</v>
+        <v>93654</v>
       </c>
       <c r="AU10" s="7">
         <f>AT10/AQ10</f>
-        <v>0.94268516095263022</v>
+        <v>0.94270529261369351</v>
       </c>
       <c r="AV10" s="5">
         <v>63719</v>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="AX10" s="6">
         <f>AY10-AW10</f>
-        <v>31822</v>
+        <v>31823</v>
       </c>
       <c r="AY10" s="5">
-        <v>60270</v>
+        <v>60271</v>
       </c>
       <c r="AZ10" s="7">
         <f>AY10/AV10</f>
-        <v>0.94587171801189596</v>
+        <v>0.94588741191795223</v>
       </c>
       <c r="BA10" s="5">
         <v>65133</v>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="BC10" s="6">
         <f>BD10-BB10</f>
-        <v>32461</v>
+        <v>32462</v>
       </c>
       <c r="BD10" s="5">
-        <v>61501</v>
+        <v>61502</v>
       </c>
       <c r="BE10" s="7">
         <f>BD10/BA10</f>
-        <v>0.94423717623938708</v>
+        <v>0.94425252943976168</v>
       </c>
       <c r="BF10" s="5">
         <v>104274</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="BH10" s="6">
         <f>BI10-BG10</f>
-        <v>59407</v>
+        <v>59411</v>
       </c>
       <c r="BI10" s="5">
-        <v>97130</v>
+        <v>97134</v>
       </c>
       <c r="BJ10" s="7">
         <f>BI10/BF10</f>
-        <v>0.93148819456432097</v>
+        <v>0.93152655503768922</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="E11" s="6">
         <f t="shared" ref="E11:E48" si="0">F11-D11</f>
-        <v>35127</v>
+        <v>35129</v>
       </c>
       <c r="F11" s="5">
-        <v>41858</v>
+        <v>41860</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" ref="G11:G48" si="1">F11/C11</f>
-        <v>0.94232327780279157</v>
+        <v>0.94236830256641158</v>
       </c>
       <c r="H11" s="3">
         <v>44517</v>
@@ -1256,14 +1256,14 @@
       </c>
       <c r="J11" s="6">
         <f t="shared" ref="J11:J48" si="2">K11-I11</f>
-        <v>35862</v>
+        <v>35864</v>
       </c>
       <c r="K11" s="5">
-        <v>42119</v>
+        <v>42121</v>
       </c>
       <c r="L11" s="7">
         <f t="shared" ref="L11:L48" si="3">K11/H11</f>
-        <v>0.94613293797874964</v>
+        <v>0.94617786463598175</v>
       </c>
       <c r="M11" s="2">
         <v>92010</v>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="O11" s="6">
         <f t="shared" ref="O11:O48" si="4">P11-N11</f>
-        <v>54093</v>
+        <v>54096</v>
       </c>
       <c r="P11" s="5">
-        <v>88388</v>
+        <v>88391</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" ref="Q11:Q48" si="5">P11/M11</f>
-        <v>0.96063471361808495</v>
+        <v>0.96066731876969891</v>
       </c>
       <c r="R11" s="5">
         <v>44191</v>
@@ -1290,14 +1290,14 @@
       </c>
       <c r="T11" s="6">
         <f t="shared" ref="T11:T48" si="6">U11-S11</f>
-        <v>20719</v>
+        <v>20720</v>
       </c>
       <c r="U11" s="5">
-        <v>41315</v>
+        <v>41316</v>
       </c>
       <c r="V11" s="7">
         <f t="shared" ref="V11:V48" si="7">U11/R11</f>
-        <v>0.93491887488402614</v>
+        <v>0.93494150392613884</v>
       </c>
       <c r="W11" s="5">
         <v>44492</v>
@@ -1307,14 +1307,14 @@
       </c>
       <c r="Y11" s="6">
         <f t="shared" ref="Y11:Y48" si="8">Z11-X11</f>
-        <v>19344</v>
+        <v>19346</v>
       </c>
       <c r="Z11" s="5">
-        <v>42302</v>
+        <v>42304</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" ref="AA11:AA48" si="9">Z11/W11</f>
-        <v>0.95077766789535201</v>
+        <v>0.95082261979681737</v>
       </c>
       <c r="AB11" s="6">
         <v>93894</v>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="AD11" s="6">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>44751</v>
+        <v>44754</v>
       </c>
       <c r="AE11" s="5">
-        <v>90717</v>
+        <v>90720</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.96616397213879479</v>
+        <v>0.9661959230621765</v>
       </c>
       <c r="AG11" s="5">
         <v>43295</v>
@@ -1341,14 +1341,14 @@
       </c>
       <c r="AI11" s="6">
         <f t="shared" ref="AI11:AI48" si="12">AJ11-AH11</f>
-        <v>18713</v>
+        <v>18715</v>
       </c>
       <c r="AJ11" s="5">
-        <v>41346</v>
+        <v>41348</v>
       </c>
       <c r="AK11" s="7">
         <f t="shared" ref="AK11:AK48" si="13">AJ11/AG11</f>
-        <v>0.9549832544173692</v>
+        <v>0.95502944912807486</v>
       </c>
       <c r="AL11" s="5">
         <v>43932</v>
@@ -1358,14 +1358,14 @@
       </c>
       <c r="AN11" s="6">
         <f t="shared" ref="AN11:AN48" si="14">AO11-AM11</f>
-        <v>7075</v>
+        <v>7077</v>
       </c>
       <c r="AO11" s="5">
-        <v>42185</v>
+        <v>42187</v>
       </c>
       <c r="AP11" s="7">
         <f t="shared" ref="AP11:AP48" si="15">AO11/AL11</f>
-        <v>0.96023399799690434</v>
+        <v>0.96027952289902574</v>
       </c>
       <c r="AQ11" s="6">
         <v>95802</v>
@@ -1375,14 +1375,14 @@
       </c>
       <c r="AS11" s="6">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>45943</v>
+        <v>45946</v>
       </c>
       <c r="AT11" s="5">
-        <v>92861</v>
+        <v>92864</v>
       </c>
       <c r="AU11" s="7">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.969301267196927</v>
+        <v>0.96933258178326132</v>
       </c>
       <c r="AV11" s="5">
         <v>43808</v>
@@ -1392,14 +1392,14 @@
       </c>
       <c r="AX11" s="6">
         <f t="shared" ref="AX11:AX48" si="18">AY11-AW11</f>
-        <v>16326</v>
+        <v>16327</v>
       </c>
       <c r="AY11" s="5">
-        <v>41694</v>
+        <v>41695</v>
       </c>
       <c r="AZ11" s="7">
         <f t="shared" ref="AZ11:AZ48" si="19">AY11/AV11</f>
-        <v>0.95174397370343311</v>
+        <v>0.95176680058436813</v>
       </c>
       <c r="BA11" s="5">
         <v>44164</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="BC11" s="6">
         <f t="shared" ref="BC11:BC48" si="20">BD11-BB11</f>
-        <v>15735</v>
+        <v>15737</v>
       </c>
       <c r="BD11" s="5">
-        <v>42468</v>
+        <v>42470</v>
       </c>
       <c r="BE11" s="7">
         <f t="shared" ref="BE11:BE47" si="21">BD11/BA11</f>
-        <v>0.96159768136944113</v>
+        <v>0.96164296712254327</v>
       </c>
       <c r="BF11" s="5">
         <v>97423</v>
@@ -1426,14 +1426,14 @@
       </c>
       <c r="BH11" s="6">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>48801</v>
+        <v>48804</v>
       </c>
       <c r="BI11" s="5">
-        <v>94242</v>
+        <v>94245</v>
       </c>
       <c r="BJ11" s="7">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>0.96734857271896779</v>
+        <v>0.96737936626874554</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1451,14 +1451,14 @@
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>115032</v>
+        <v>115033</v>
       </c>
       <c r="F12" s="5">
-        <v>148730</v>
+        <v>148731</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="1"/>
-        <v>0.92689189273406003</v>
+        <v>0.92689812477798339</v>
       </c>
       <c r="H12" s="3">
         <v>161190</v>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="J12" s="6">
         <f t="shared" si="2"/>
-        <v>124716</v>
+        <v>124717</v>
       </c>
       <c r="K12" s="5">
-        <v>150204</v>
+        <v>150205</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="3"/>
-        <v>0.93184440722129169</v>
+        <v>0.93185061108009182</v>
       </c>
       <c r="M12" s="2">
         <v>320319</v>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="O12" s="6">
         <f t="shared" si="4"/>
-        <v>108838</v>
+        <v>108840</v>
       </c>
       <c r="P12" s="5">
-        <v>307409</v>
+        <v>307411</v>
       </c>
       <c r="Q12" s="7">
         <f t="shared" si="5"/>
-        <v>0.95969642762371266</v>
+        <v>0.95970267139944865</v>
       </c>
       <c r="R12" s="5">
         <v>159828</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="T12" s="6">
         <f t="shared" si="6"/>
-        <v>43226</v>
+        <v>43227</v>
       </c>
       <c r="U12" s="5">
-        <v>148949</v>
+        <v>148950</v>
       </c>
       <c r="V12" s="7">
         <f t="shared" si="7"/>
-        <v>0.93193307805891334</v>
+        <v>0.93193933478489377</v>
       </c>
       <c r="W12" s="5">
         <v>162180</v>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="Y12" s="6">
         <f t="shared" si="8"/>
-        <v>40678</v>
+        <v>40680</v>
       </c>
       <c r="Z12" s="5">
-        <v>151684</v>
+        <v>151686</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="9"/>
-        <v>0.93528178567024289</v>
+        <v>0.93529411764705883</v>
       </c>
       <c r="AB12" s="6">
         <v>327297</v>
@@ -1536,14 +1536,14 @@
       </c>
       <c r="AD12" s="6">
         <f t="shared" si="10"/>
-        <v>85954</v>
+        <v>85956</v>
       </c>
       <c r="AE12" s="5">
-        <v>312378</v>
+        <v>312380</v>
       </c>
       <c r="AF12" s="7">
         <f t="shared" si="11"/>
-        <v>0.9544175473652371</v>
+        <v>0.95442365802314111</v>
       </c>
       <c r="AG12" s="5">
         <v>160729</v>
@@ -1553,14 +1553,14 @@
       </c>
       <c r="AI12" s="6">
         <f t="shared" si="12"/>
-        <v>37723</v>
+        <v>37724</v>
       </c>
       <c r="AJ12" s="5">
-        <v>149542</v>
+        <v>149543</v>
       </c>
       <c r="AK12" s="7">
         <f t="shared" si="13"/>
-        <v>0.93039837241568102</v>
+        <v>0.93040459406827647</v>
       </c>
       <c r="AL12" s="5">
         <v>162572</v>
@@ -1570,14 +1570,14 @@
       </c>
       <c r="AN12" s="6">
         <f t="shared" si="14"/>
-        <v>16148</v>
+        <v>16149</v>
       </c>
       <c r="AO12" s="5">
-        <v>151704</v>
+        <v>151705</v>
       </c>
       <c r="AP12" s="7">
         <f t="shared" si="15"/>
-        <v>0.93314961986073863</v>
+        <v>0.93315577098147284</v>
       </c>
       <c r="AQ12" s="6">
         <v>333129</v>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="AS12" s="6">
         <f t="shared" si="16"/>
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="AT12" s="5">
-        <v>316286</v>
+        <v>316288</v>
       </c>
       <c r="AU12" s="7">
         <f t="shared" si="17"/>
-        <v>0.94944000672412188</v>
+        <v>0.94944601040437793</v>
       </c>
       <c r="AV12" s="5">
         <v>161987</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="AX12" s="6">
         <f t="shared" si="18"/>
-        <v>32305</v>
+        <v>32306</v>
       </c>
       <c r="AY12" s="5">
-        <v>150784</v>
+        <v>150785</v>
       </c>
       <c r="AZ12" s="7">
         <f t="shared" si="19"/>
-        <v>0.9308401291461661</v>
+        <v>0.93084630248106326</v>
       </c>
       <c r="BA12" s="5">
         <v>163270</v>
@@ -1621,14 +1621,14 @@
       </c>
       <c r="BC12" s="6">
         <f t="shared" si="20"/>
-        <v>30964</v>
+        <v>30965</v>
       </c>
       <c r="BD12" s="5">
-        <v>152891</v>
+        <v>152892</v>
       </c>
       <c r="BE12" s="7">
         <f t="shared" si="21"/>
-        <v>0.9364304526244871</v>
+        <v>0.93643657744839837</v>
       </c>
       <c r="BF12" s="5">
         <v>336608</v>
@@ -1638,14 +1638,14 @@
       </c>
       <c r="BH12" s="6">
         <f t="shared" si="22"/>
-        <v>91185</v>
+        <v>91188</v>
       </c>
       <c r="BI12" s="5">
-        <v>319832</v>
+        <v>319835</v>
       </c>
       <c r="BJ12" s="7">
         <f t="shared" si="23"/>
-        <v>0.95016161232056284</v>
+        <v>0.95017052476471142</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1875,14 +1875,14 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>63912</v>
+        <v>63913</v>
       </c>
       <c r="F14" s="5">
-        <v>72490</v>
+        <v>72491</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0.91856000608233968</v>
+        <v>0.91857267762332573</v>
       </c>
       <c r="H14" s="3">
         <v>78856</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="2"/>
-        <v>62768</v>
+        <v>62770</v>
       </c>
       <c r="K14" s="5">
-        <v>72498</v>
+        <v>72500</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" si="3"/>
-        <v>0.91937201988434614</v>
+        <v>0.91939738257076187</v>
       </c>
       <c r="M14" s="2">
         <v>139510</v>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="O14" s="6">
         <f t="shared" si="4"/>
-        <v>84022</v>
+        <v>84029</v>
       </c>
       <c r="P14" s="5">
-        <v>131015</v>
+        <v>131022</v>
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="5"/>
-        <v>0.9391083076481973</v>
+        <v>0.93915848326284856</v>
       </c>
       <c r="R14" s="5">
         <v>78838</v>
@@ -1926,14 +1926,14 @@
       </c>
       <c r="T14" s="6">
         <f t="shared" si="6"/>
-        <v>40329</v>
+        <v>40330</v>
       </c>
       <c r="U14" s="5">
-        <v>72425</v>
+        <v>72426</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="7"/>
-        <v>0.91865597808163579</v>
+        <v>0.91866866232020095</v>
       </c>
       <c r="W14" s="5">
         <v>80553</v>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>38578</v>
+        <v>38581</v>
       </c>
       <c r="Z14" s="5">
-        <v>74210</v>
+        <v>74213</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="9"/>
-        <v>0.92125681228507939</v>
+        <v>0.9212940548458779</v>
       </c>
       <c r="AB14" s="6">
         <v>144082</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>66579</v>
+        <v>66583</v>
       </c>
       <c r="AE14" s="5">
-        <v>135264</v>
+        <v>135268</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="11"/>
-        <v>0.93879873960661286</v>
+        <v>0.93882650157549175</v>
       </c>
       <c r="AG14" s="5">
         <v>79635</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="12"/>
-        <v>36583</v>
+        <v>36584</v>
       </c>
       <c r="AJ14" s="5">
-        <v>73457</v>
+        <v>73458</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="13"/>
-        <v>0.92242104602247754</v>
+        <v>0.92243360331512525</v>
       </c>
       <c r="AL14" s="5">
         <v>81274</v>
@@ -1994,14 +1994,14 @@
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="14"/>
-        <v>16025</v>
+        <v>16026</v>
       </c>
       <c r="AO14" s="5">
-        <v>75078</v>
+        <v>75079</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="15"/>
-        <v>0.92376405738612599</v>
+        <v>0.92377636144400421</v>
       </c>
       <c r="AQ14" s="6">
         <v>148266</v>
@@ -2011,14 +2011,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>68564</v>
+        <v>68569</v>
       </c>
       <c r="AT14" s="5">
-        <v>139137</v>
+        <v>139142</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.93842823034276235</v>
+        <v>0.93846195351597805</v>
       </c>
       <c r="AV14" s="5">
         <v>81291</v>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="AX14" s="6">
         <f t="shared" si="18"/>
-        <v>31967</v>
+        <v>31969</v>
       </c>
       <c r="AY14" s="5">
-        <v>75333</v>
+        <v>75335</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="19"/>
-        <v>0.92670775362586266</v>
+        <v>0.92673235659544106</v>
       </c>
       <c r="BA14" s="5">
         <v>82359</v>
@@ -2045,14 +2045,14 @@
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="20"/>
-        <v>31695</v>
+        <v>31697</v>
       </c>
       <c r="BD14" s="5">
-        <v>76618</v>
+        <v>76620</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="21"/>
-        <v>0.93029298558748896</v>
+        <v>0.93031726951517135</v>
       </c>
       <c r="BF14" s="5">
         <v>151377</v>
@@ -2062,14 +2062,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>71647</v>
+        <v>71657</v>
       </c>
       <c r="BI14" s="5">
-        <v>141666</v>
+        <v>141676</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.93584890703343304</v>
+        <v>0.93591496726715417</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="J15" s="6">
         <f t="shared" si="2"/>
-        <v>195630</v>
+        <v>195631</v>
       </c>
       <c r="K15" s="5">
-        <v>236420</v>
+        <v>236421</v>
       </c>
       <c r="L15" s="7">
         <f t="shared" si="3"/>
-        <v>0.9229207737200632</v>
+        <v>0.92292467745398477</v>
       </c>
       <c r="M15" s="2">
         <v>440788</v>
@@ -2189,14 +2189,14 @@
       </c>
       <c r="AI15" s="6">
         <f t="shared" si="12"/>
-        <v>81626</v>
+        <v>81627</v>
       </c>
       <c r="AJ15" s="5">
-        <v>242435</v>
+        <v>242436</v>
       </c>
       <c r="AK15" s="7">
         <f t="shared" si="13"/>
-        <v>0.92600302511764343</v>
+        <v>0.92600684471062766</v>
       </c>
       <c r="AL15" s="5">
         <v>265773</v>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="E16" s="6">
         <f t="shared" si="0"/>
-        <v>318920</v>
+        <v>318923</v>
       </c>
       <c r="F16" s="5">
-        <v>367103</v>
+        <v>367106</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="1"/>
-        <v>0.90300244012830355</v>
+        <v>0.90300981954857629</v>
       </c>
       <c r="H16" s="3">
         <v>404491</v>
@@ -2316,14 +2316,14 @@
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>311438</v>
+        <v>311441</v>
       </c>
       <c r="K16" s="5">
-        <v>365430</v>
+        <v>365433</v>
       </c>
       <c r="L16" s="7">
         <f t="shared" si="3"/>
-        <v>0.90343172035966191</v>
+        <v>0.90343913708834067</v>
       </c>
       <c r="M16" s="2">
         <v>718779</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>296129</v>
+        <v>296136</v>
       </c>
       <c r="P16" s="5">
-        <v>672230</v>
+        <v>672237</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.9352387868872073</v>
+        <v>0.93524852562470528</v>
       </c>
       <c r="R16" s="5">
         <v>403668</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>139498</v>
+        <v>139501</v>
       </c>
       <c r="U16" s="5">
-        <v>369199</v>
+        <v>369202</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.91461052151768285</v>
+        <v>0.91461795336761897</v>
       </c>
       <c r="W16" s="5">
         <v>406853</v>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>131962</v>
+        <v>131964</v>
       </c>
       <c r="Z16" s="5">
-        <v>376712</v>
+        <v>376714</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.92591673159593268</v>
+        <v>0.9259216473763251</v>
       </c>
       <c r="AB16" s="6">
         <v>722282</v>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>196112</v>
+        <v>196118</v>
       </c>
       <c r="AE16" s="5">
-        <v>689372</v>
+        <v>689378</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.95443607898300109</v>
+        <v>0.95444438598774439</v>
       </c>
       <c r="AG16" s="5">
         <v>397671</v>
@@ -2401,14 +2401,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>116369</v>
+        <v>116372</v>
       </c>
       <c r="AJ16" s="5">
-        <v>374279</v>
+        <v>374282</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.94117750602885297</v>
+        <v>0.94118504995335339</v>
       </c>
       <c r="AL16" s="5">
         <v>400740</v>
@@ -2418,14 +2418,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>48222</v>
+        <v>48226</v>
       </c>
       <c r="AO16" s="5">
-        <v>380502</v>
+        <v>380506</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.94949842790836947</v>
+        <v>0.94950840944253134</v>
       </c>
       <c r="AQ16" s="6">
         <v>730568</v>
@@ -2435,14 +2435,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>198847</v>
+        <v>198854</v>
       </c>
       <c r="AT16" s="5">
-        <v>699684</v>
+        <v>699691</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.95772604329781763</v>
+        <v>0.95773562488365216</v>
       </c>
       <c r="AV16" s="5">
         <v>402711</v>
@@ -2452,14 +2452,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>96434</v>
+        <v>96440</v>
       </c>
       <c r="AY16" s="5">
-        <v>378355</v>
+        <v>378361</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.93951990385164552</v>
+        <v>0.93953480287352464</v>
       </c>
       <c r="BA16" s="5">
         <v>402569</v>
@@ -2469,14 +2469,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>94059</v>
+        <v>94065</v>
       </c>
       <c r="BD16" s="5">
-        <v>384268</v>
+        <v>384274</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.95453947025230457</v>
+        <v>0.95455437452958369</v>
       </c>
       <c r="BF16" s="5">
         <v>736680</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>196433</v>
+        <v>196444</v>
       </c>
       <c r="BI16" s="5">
-        <v>706632</v>
+        <v>706643</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.95921159798012701</v>
+        <v>0.95922652983656409</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>225671</v>
+        <v>225677</v>
       </c>
       <c r="F17" s="5">
-        <v>255287</v>
+        <v>255293</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.96727833496891136</v>
+        <v>0.96730106887236045</v>
       </c>
       <c r="H17" s="3">
         <v>264168</v>
@@ -2528,14 +2528,14 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>221968</v>
+        <v>221973</v>
       </c>
       <c r="K17" s="5">
-        <v>256555</v>
+        <v>256560</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="3"/>
-        <v>0.97118121801277979</v>
+        <v>0.97120014536204236</v>
       </c>
       <c r="M17" s="2">
         <v>591219</v>
@@ -2545,14 +2545,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>323435</v>
+        <v>323446</v>
       </c>
       <c r="P17" s="5">
-        <v>577382</v>
+        <v>577393</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.97659581305742882</v>
+        <v>0.97661441868410859</v>
       </c>
       <c r="R17" s="5">
         <v>261213</v>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>119501</v>
+        <v>119506</v>
       </c>
       <c r="U17" s="5">
-        <v>253295</v>
+        <v>253300</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.9696875729768426</v>
+        <v>0.9697067144437681</v>
       </c>
       <c r="W17" s="5">
         <v>269820</v>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>114735</v>
+        <v>114739</v>
       </c>
       <c r="Z17" s="5">
-        <v>262464</v>
+        <v>262468</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.97273738047587277</v>
+        <v>0.97275220517381955</v>
       </c>
       <c r="AB17" s="6">
         <v>613565</v>
@@ -2596,14 +2596,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>238264</v>
+        <v>238271</v>
       </c>
       <c r="AE17" s="5">
-        <v>597215</v>
+        <v>597222</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.97335245654494629</v>
+        <v>0.97336386527914731</v>
       </c>
       <c r="AG17" s="5">
         <v>263808</v>
@@ -2613,14 +2613,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>102900</v>
+        <v>102907</v>
       </c>
       <c r="AJ17" s="5">
-        <v>255212</v>
+        <v>255219</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.96741569626394952</v>
+        <v>0.96744223071324598</v>
       </c>
       <c r="AL17" s="5">
         <v>270212</v>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>46314</v>
+        <v>46318</v>
       </c>
       <c r="AO17" s="5">
-        <v>262866</v>
+        <v>262870</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.97281393868518051</v>
+        <v>0.97282874187674861</v>
       </c>
       <c r="AQ17" s="6">
         <v>633137</v>
@@ -2647,14 +2647,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>253888</v>
+        <v>253899</v>
       </c>
       <c r="AT17" s="5">
-        <v>612891</v>
+        <v>612902</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.96802271862172007</v>
+        <v>0.96804009242865285</v>
       </c>
       <c r="AV17" s="5">
         <v>270996</v>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>84220</v>
+        <v>84227</v>
       </c>
       <c r="AY17" s="5">
-        <v>261427</v>
+        <v>261434</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.96468951571240902</v>
+        <v>0.96471534635197564</v>
       </c>
       <c r="BA17" s="5">
         <v>277009</v>
@@ -2681,14 +2681,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>81149</v>
+        <v>81156</v>
       </c>
       <c r="BD17" s="5">
-        <v>270944</v>
+        <v>270951</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.9781054045175428</v>
+        <v>0.97813067445462065</v>
       </c>
       <c r="BF17" s="5">
         <v>651560</v>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>264477</v>
+        <v>264488</v>
       </c>
       <c r="BI17" s="5">
-        <v>629089</v>
+        <v>629100</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.96551200196451592</v>
+        <v>0.96552888452329788</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>650560</v>
+        <v>650570</v>
       </c>
       <c r="F18" s="5">
-        <v>716473</v>
+        <v>716483</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="1"/>
-        <v>0.93230786447259184</v>
+        <v>0.93232087693592924</v>
       </c>
       <c r="H18" s="3">
         <v>766983</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="J18" s="6">
         <f t="shared" si="2"/>
-        <v>624792</v>
+        <v>624799</v>
       </c>
       <c r="K18" s="5">
-        <v>716161</v>
+        <v>716168</v>
       </c>
       <c r="L18" s="7">
         <f t="shared" si="3"/>
-        <v>0.9337377751527739</v>
+        <v>0.93374690182181352</v>
       </c>
       <c r="M18" s="2">
         <v>1193073</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="O18" s="6">
         <f t="shared" si="4"/>
-        <v>736262</v>
+        <v>736273</v>
       </c>
       <c r="P18" s="5">
-        <v>1137361</v>
+        <v>1137372</v>
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="5"/>
-        <v>0.95330377939991939</v>
+        <v>0.95331299928839219</v>
       </c>
       <c r="R18" s="5">
         <v>775495</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="T18" s="6">
         <f t="shared" si="6"/>
-        <v>411965</v>
+        <v>411976</v>
       </c>
       <c r="U18" s="5">
-        <v>732679</v>
+        <v>732690</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="7"/>
-        <v>0.94478881230697809</v>
+        <v>0.9448029967955951</v>
       </c>
       <c r="W18" s="5">
         <v>789854</v>
@@ -2791,14 +2791,14 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="8"/>
-        <v>390040</v>
+        <v>390050</v>
       </c>
       <c r="Z18" s="5">
-        <v>748166</v>
+        <v>748176</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="9"/>
-        <v>0.94722062558396869</v>
+        <v>0.94723328615161795</v>
       </c>
       <c r="AB18" s="6">
         <v>1245422</v>
@@ -2808,14 +2808,14 @@
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>569078</v>
+        <v>569093</v>
       </c>
       <c r="AE18" s="5">
-        <v>1175152</v>
+        <v>1175167</v>
       </c>
       <c r="AF18" s="7">
         <f t="shared" si="11"/>
-        <v>0.94357735771489504</v>
+        <v>0.94358940182524476</v>
       </c>
       <c r="AG18" s="5">
         <v>794310</v>
@@ -2825,14 +2825,14 @@
       </c>
       <c r="AI18" s="6">
         <f t="shared" si="12"/>
-        <v>388006</v>
+        <v>388018</v>
       </c>
       <c r="AJ18" s="5">
-        <v>750365</v>
+        <v>750377</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="13"/>
-        <v>0.94467525273507824</v>
+        <v>0.94469036018682884</v>
       </c>
       <c r="AL18" s="5">
         <v>807429</v>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>142051</v>
+        <v>142063</v>
       </c>
       <c r="AO18" s="5">
-        <v>765791</v>
+        <v>765803</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="15"/>
-        <v>0.94843137910577902</v>
+        <v>0.94844624109364417</v>
       </c>
       <c r="AQ18" s="6">
         <v>1285494</v>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AS18" s="6">
         <f t="shared" si="16"/>
-        <v>603833</v>
+        <v>603846</v>
       </c>
       <c r="AT18" s="5">
-        <v>1212023</v>
+        <v>1212036</v>
       </c>
       <c r="AU18" s="7">
         <f t="shared" si="17"/>
-        <v>0.94284609652009266</v>
+        <v>0.94285620936387105</v>
       </c>
       <c r="AV18" s="5">
         <v>820095</v>
@@ -2876,14 +2876,14 @@
       </c>
       <c r="AX18" s="6">
         <f t="shared" si="18"/>
-        <v>349458</v>
+        <v>349468</v>
       </c>
       <c r="AY18" s="5">
-        <v>773526</v>
+        <v>773536</v>
       </c>
       <c r="AZ18" s="7">
         <f t="shared" si="19"/>
-        <v>0.94321511532200542</v>
+        <v>0.94322730903127072</v>
       </c>
       <c r="BA18" s="5">
         <v>829968</v>
@@ -2893,14 +2893,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>340725</v>
+        <v>340736</v>
       </c>
       <c r="BD18" s="5">
-        <v>785678</v>
+        <v>785689</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.94663649682879336</v>
+        <v>0.94664975035182075</v>
       </c>
       <c r="BF18" s="5">
         <v>1319511</v>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>631874</v>
+        <v>631893</v>
       </c>
       <c r="BI18" s="5">
-        <v>1235548</v>
+        <v>1235567</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.93636809393783005</v>
+        <v>0.93638249321150036</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="E19" s="6">
         <f t="shared" si="0"/>
-        <v>188016</v>
+        <v>188019</v>
       </c>
       <c r="F19" s="5">
-        <v>203910</v>
+        <v>203913</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="1"/>
-        <v>0.8307462905473123</v>
+        <v>0.8307585127966951</v>
       </c>
       <c r="H19" s="3">
         <v>247965</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="J19" s="6">
         <f t="shared" si="2"/>
-        <v>185920</v>
+        <v>185924</v>
       </c>
       <c r="K19" s="5">
-        <v>204603</v>
+        <v>204607</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="3"/>
-        <v>0.82512854636743094</v>
+        <v>0.82514467767628497</v>
       </c>
       <c r="M19" s="2">
         <v>387570</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="O19" s="6">
         <f t="shared" si="4"/>
-        <v>259986</v>
+        <v>259994</v>
       </c>
       <c r="P19" s="5">
-        <v>337551</v>
+        <v>337559</v>
       </c>
       <c r="Q19" s="7">
         <f t="shared" si="5"/>
-        <v>0.87094202337642235</v>
+        <v>0.87096266480893769</v>
       </c>
       <c r="R19" s="5">
         <v>254467</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="T19" s="6">
         <f t="shared" si="6"/>
-        <v>158280</v>
+        <v>158284</v>
       </c>
       <c r="U19" s="5">
-        <v>216792</v>
+        <v>216796</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="7"/>
-        <v>0.85194543889777452</v>
+        <v>0.85196115802834949</v>
       </c>
       <c r="W19" s="5">
         <v>263449</v>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>162767</v>
+        <v>162772</v>
       </c>
       <c r="Z19" s="5">
-        <v>229832</v>
+        <v>229837</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="9"/>
-        <v>0.87239655493093538</v>
+        <v>0.87241553393635962</v>
       </c>
       <c r="AB19" s="6">
         <v>418128</v>
@@ -3020,14 +3020,14 @@
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="10"/>
-        <v>231548</v>
+        <v>231553</v>
       </c>
       <c r="AE19" s="5">
-        <v>372436</v>
+        <v>372441</v>
       </c>
       <c r="AF19" s="7">
         <f t="shared" si="11"/>
-        <v>0.89072245819461981</v>
+        <v>0.89073441625530936</v>
       </c>
       <c r="AG19" s="5">
         <v>259213</v>
@@ -3037,14 +3037,14 @@
       </c>
       <c r="AI19" s="6">
         <f t="shared" si="12"/>
-        <v>162932</v>
+        <v>162936</v>
       </c>
       <c r="AJ19" s="5">
-        <v>221038</v>
+        <v>221042</v>
       </c>
       <c r="AK19" s="7">
         <f t="shared" si="13"/>
-        <v>0.85272729376998835</v>
+        <v>0.8527427250948062</v>
       </c>
       <c r="AL19" s="5">
         <v>262802</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="AN19" s="6">
         <f t="shared" si="14"/>
-        <v>63210</v>
+        <v>63214</v>
       </c>
       <c r="AO19" s="5">
-        <v>224984</v>
+        <v>224988</v>
       </c>
       <c r="AP19" s="7">
         <f t="shared" si="15"/>
-        <v>0.85609698556327574</v>
+        <v>0.85611220614759398</v>
       </c>
       <c r="AQ19" s="6">
         <v>437396</v>
@@ -3071,14 +3071,14 @@
       </c>
       <c r="AS19" s="6">
         <f t="shared" si="16"/>
-        <v>254078</v>
+        <v>254084</v>
       </c>
       <c r="AT19" s="5">
-        <v>381161</v>
+        <v>381167</v>
       </c>
       <c r="AU19" s="7">
         <f t="shared" si="17"/>
-        <v>0.87143229476264072</v>
+        <v>0.87144601230921181</v>
       </c>
       <c r="AV19" s="5">
         <v>265429</v>
@@ -3088,14 +3088,14 @@
       </c>
       <c r="AX19" s="6">
         <f t="shared" si="18"/>
-        <v>145059</v>
+        <v>145062</v>
       </c>
       <c r="AY19" s="5">
-        <v>226863</v>
+        <v>226866</v>
       </c>
       <c r="AZ19" s="7">
         <f t="shared" si="19"/>
-        <v>0.85470314095294786</v>
+        <v>0.85471444341047886</v>
       </c>
       <c r="BA19" s="5">
         <v>272122</v>
@@ -3105,14 +3105,14 @@
       </c>
       <c r="BC19" s="6">
         <f t="shared" si="20"/>
-        <v>142879</v>
+        <v>142882</v>
       </c>
       <c r="BD19" s="5">
-        <v>232929</v>
+        <v>232932</v>
       </c>
       <c r="BE19" s="7">
         <f t="shared" si="21"/>
-        <v>0.85597268872050036</v>
+        <v>0.85598371318746735</v>
       </c>
       <c r="BF19" s="5">
         <v>456786</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="BH19" s="6">
         <f t="shared" si="22"/>
-        <v>273291</v>
+        <v>273297</v>
       </c>
       <c r="BI19" s="5">
-        <v>393739</v>
+        <v>393745</v>
       </c>
       <c r="BJ19" s="7">
         <f t="shared" si="23"/>
-        <v>0.86197694325132557</v>
+        <v>0.86199007850503295</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3181,14 +3181,14 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="4"/>
-        <v>5339</v>
+        <v>5343</v>
       </c>
       <c r="P20" s="5">
-        <v>7026</v>
+        <v>7030</v>
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="5"/>
-        <v>0.87312041754691194</v>
+        <v>0.8736174972039269</v>
       </c>
       <c r="R20" s="5">
         <v>5619</v>
@@ -3232,14 +3232,14 @@
       </c>
       <c r="AD20" s="6">
         <f t="shared" si="10"/>
-        <v>3881</v>
+        <v>3885</v>
       </c>
       <c r="AE20" s="5">
-        <v>7229</v>
+        <v>7233</v>
       </c>
       <c r="AF20" s="7">
         <f t="shared" si="11"/>
-        <v>0.86949723358191</v>
+        <v>0.86997834977146982</v>
       </c>
       <c r="AG20" s="5">
         <v>5709</v>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AI20" s="6">
         <f t="shared" si="12"/>
-        <v>2990</v>
+        <v>2991</v>
       </c>
       <c r="AJ20" s="5">
-        <v>4681</v>
+        <v>4682</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="13"/>
-        <v>0.81993343843054822</v>
+        <v>0.82010860045542122</v>
       </c>
       <c r="AL20" s="5">
         <v>5805</v>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AN20" s="6">
         <f t="shared" si="14"/>
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="AO20" s="5">
-        <v>4852</v>
+        <v>4853</v>
       </c>
       <c r="AP20" s="7">
         <f t="shared" si="15"/>
-        <v>0.83583118001722656</v>
+        <v>0.83600344530577086</v>
       </c>
       <c r="AQ20" s="6">
         <v>8632</v>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="AS20" s="6">
         <f t="shared" si="16"/>
-        <v>4686</v>
+        <v>4691</v>
       </c>
       <c r="AT20" s="5">
-        <v>7625</v>
+        <v>7630</v>
       </c>
       <c r="AU20" s="7">
         <f t="shared" si="17"/>
-        <v>0.88334105653382766</v>
+        <v>0.88392029657089899</v>
       </c>
       <c r="AV20" s="5">
         <v>5837</v>
@@ -3300,14 +3300,14 @@
       </c>
       <c r="AX20" s="6">
         <f t="shared" si="18"/>
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="AY20" s="5">
-        <v>4828</v>
+        <v>4830</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="19"/>
-        <v>0.82713722802809664</v>
+        <v>0.8274798697961282</v>
       </c>
       <c r="BA20" s="5">
         <v>5912</v>
@@ -3317,14 +3317,14 @@
       </c>
       <c r="BC20" s="6">
         <f t="shared" si="20"/>
-        <v>2703</v>
+        <v>2705</v>
       </c>
       <c r="BD20" s="5">
-        <v>4955</v>
+        <v>4957</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="21"/>
-        <v>0.83812584573748306</v>
+        <v>0.83846414073071718</v>
       </c>
       <c r="BF20" s="5">
         <v>8941</v>
@@ -3334,14 +3334,14 @@
       </c>
       <c r="BH20" s="6">
         <f t="shared" si="22"/>
-        <v>5006</v>
+        <v>5010</v>
       </c>
       <c r="BI20" s="5">
-        <v>7872</v>
+        <v>7876</v>
       </c>
       <c r="BJ20" s="7">
         <f t="shared" si="23"/>
-        <v>0.88043842970584951</v>
+        <v>0.88088580695671626</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="E21" s="6">
         <f t="shared" si="0"/>
-        <v>6576</v>
+        <v>6577</v>
       </c>
       <c r="F21" s="5">
-        <v>7373</v>
+        <v>7374</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="1"/>
-        <v>0.72935008408349</v>
+        <v>0.72944900583638339</v>
       </c>
       <c r="H21" s="3">
         <v>10163</v>
@@ -3393,14 +3393,14 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="4"/>
-        <v>8007</v>
+        <v>8008</v>
       </c>
       <c r="P21" s="5">
-        <v>9964</v>
+        <v>9965</v>
       </c>
       <c r="Q21" s="7">
         <f t="shared" si="5"/>
-        <v>0.7668154532861321</v>
+        <v>0.76689241188240731</v>
       </c>
       <c r="R21" s="5">
         <v>10237</v>
@@ -3410,14 +3410,14 @@
       </c>
       <c r="T21" s="6">
         <f t="shared" si="6"/>
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="U21" s="5">
-        <v>7501</v>
+        <v>7502</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="7"/>
-        <v>0.73273419947250173</v>
+        <v>0.73283188434111557</v>
       </c>
       <c r="W21" s="5">
         <v>10162</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>5827</v>
+        <v>5828</v>
       </c>
       <c r="Z21" s="5">
-        <v>7607</v>
+        <v>7608</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.7485731155284393</v>
+        <v>0.74867152135406412</v>
       </c>
       <c r="AB21" s="6">
         <v>13196</v>
@@ -3444,14 +3444,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>7177</v>
+        <v>7180</v>
       </c>
       <c r="AE21" s="5">
-        <v>10277</v>
+        <v>10280</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.77879660503182779</v>
+        <v>0.77902394665050012</v>
       </c>
       <c r="AG21" s="5">
         <v>10295</v>
@@ -3461,14 +3461,14 @@
       </c>
       <c r="AI21" s="6">
         <f t="shared" si="12"/>
-        <v>5353</v>
+        <v>5355</v>
       </c>
       <c r="AJ21" s="5">
-        <v>7688</v>
+        <v>7690</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="13"/>
-        <v>0.74677027683341424</v>
+        <v>0.74696454589606609</v>
       </c>
       <c r="AL21" s="5">
         <v>10459</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2949</v>
+        <v>2951</v>
       </c>
       <c r="AO21" s="5">
-        <v>7782</v>
+        <v>7784</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.74404818816330431</v>
+        <v>0.74423941103355962</v>
       </c>
       <c r="AQ21" s="6">
         <v>13595</v>
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS21" s="6">
         <f t="shared" si="16"/>
-        <v>7427</v>
+        <v>7429</v>
       </c>
       <c r="AT21" s="5">
-        <v>10590</v>
+        <v>10592</v>
       </c>
       <c r="AU21" s="7">
         <f t="shared" si="17"/>
-        <v>0.77896285399043763</v>
+        <v>0.77910996689959544</v>
       </c>
       <c r="AV21" s="5">
         <v>10391</v>
@@ -3512,14 +3512,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>5185</v>
+        <v>5187</v>
       </c>
       <c r="AY21" s="5">
-        <v>7906</v>
+        <v>7908</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.76085073621403132</v>
+        <v>0.76104321047059953</v>
       </c>
       <c r="BA21" s="5">
         <v>10525</v>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="BC21" s="6">
         <f t="shared" si="20"/>
-        <v>5271</v>
+        <v>5273</v>
       </c>
       <c r="BD21" s="5">
-        <v>8046</v>
+        <v>8048</v>
       </c>
       <c r="BE21" s="7">
         <f t="shared" si="21"/>
-        <v>0.76446555819477435</v>
+        <v>0.76465558194774352</v>
       </c>
       <c r="BF21" s="5">
         <v>13618</v>
@@ -3546,14 +3546,14 @@
       </c>
       <c r="BH21" s="6">
         <f t="shared" si="22"/>
-        <v>8332</v>
+        <v>8334</v>
       </c>
       <c r="BI21" s="5">
-        <v>10965</v>
+        <v>10967</v>
       </c>
       <c r="BJ21" s="7">
         <f t="shared" si="23"/>
-        <v>0.80518431487736819</v>
+        <v>0.80533117932148623</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="E22" s="6">
         <f t="shared" si="0"/>
-        <v>4322</v>
+        <v>4325</v>
       </c>
       <c r="F22" s="5">
-        <v>4984</v>
+        <v>4987</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="1"/>
-        <v>0.84174970444181729</v>
+        <v>0.84225637561222766</v>
       </c>
       <c r="H22" s="3">
         <v>5940</v>
@@ -3588,14 +3588,14 @@
       </c>
       <c r="J22" s="6">
         <f t="shared" si="2"/>
-        <v>4474</v>
+        <v>4477</v>
       </c>
       <c r="K22" s="5">
-        <v>4994</v>
+        <v>4997</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="3"/>
-        <v>0.84074074074074079</v>
+        <v>0.84124579124579124</v>
       </c>
       <c r="M22" s="2">
         <v>7004</v>
@@ -3605,14 +3605,14 @@
       </c>
       <c r="O22" s="6">
         <f t="shared" si="4"/>
-        <v>4752</v>
+        <v>4754</v>
       </c>
       <c r="P22" s="5">
-        <v>5947</v>
+        <v>5949</v>
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="5"/>
-        <v>0.84908623643632208</v>
+        <v>0.84937178754997145</v>
       </c>
       <c r="R22" s="5">
         <v>5966</v>
@@ -3622,14 +3622,14 @@
       </c>
       <c r="T22" s="6">
         <f t="shared" si="6"/>
-        <v>3622</v>
+        <v>3624</v>
       </c>
       <c r="U22" s="5">
-        <v>4987</v>
+        <v>4989</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="7"/>
-        <v>0.83590345289976531</v>
+        <v>0.83623868588669126</v>
       </c>
       <c r="W22" s="5">
         <v>5920</v>
@@ -3639,14 +3639,14 @@
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="8"/>
-        <v>3529</v>
+        <v>3531</v>
       </c>
       <c r="Z22" s="5">
-        <v>5046</v>
+        <v>5048</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="9"/>
-        <v>0.85236486486486485</v>
+        <v>0.85270270270270265</v>
       </c>
       <c r="AB22" s="6">
         <v>7073</v>
@@ -3656,14 +3656,14 @@
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="10"/>
-        <v>4009</v>
+        <v>4011</v>
       </c>
       <c r="AE22" s="5">
-        <v>6136</v>
+        <v>6138</v>
       </c>
       <c r="AF22" s="7">
         <f t="shared" si="11"/>
-        <v>0.86752438851972291</v>
+        <v>0.86780715396578534</v>
       </c>
       <c r="AG22" s="5">
         <v>5998</v>
@@ -3673,14 +3673,14 @@
       </c>
       <c r="AI22" s="6">
         <f t="shared" si="12"/>
-        <v>3337</v>
+        <v>3339</v>
       </c>
       <c r="AJ22" s="5">
-        <v>5167</v>
+        <v>5169</v>
       </c>
       <c r="AK22" s="7">
         <f t="shared" si="13"/>
-        <v>0.86145381793931308</v>
+        <v>0.86178726242080694</v>
       </c>
       <c r="AL22" s="5">
         <v>5988</v>
@@ -3690,14 +3690,14 @@
       </c>
       <c r="AN22" s="6">
         <f t="shared" si="14"/>
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="AO22" s="5">
-        <v>5257</v>
+        <v>5259</v>
       </c>
       <c r="AP22" s="7">
         <f t="shared" si="15"/>
-        <v>0.87792251169004676</v>
+        <v>0.87825651302605212</v>
       </c>
       <c r="AQ22" s="6">
         <v>7036</v>
@@ -3707,14 +3707,14 @@
       </c>
       <c r="AS22" s="6">
         <f t="shared" si="16"/>
-        <v>4192</v>
+        <v>4194</v>
       </c>
       <c r="AT22" s="5">
-        <v>6314</v>
+        <v>6316</v>
       </c>
       <c r="AU22" s="7">
         <f t="shared" si="17"/>
-        <v>0.89738487777146103</v>
+        <v>0.89766913018760663</v>
       </c>
       <c r="AV22" s="5">
         <v>5943</v>
@@ -3724,14 +3724,14 @@
       </c>
       <c r="AX22" s="6">
         <f t="shared" si="18"/>
-        <v>3448</v>
+        <v>3450</v>
       </c>
       <c r="AY22" s="5">
-        <v>5317</v>
+        <v>5319</v>
       </c>
       <c r="AZ22" s="7">
         <f t="shared" si="19"/>
-        <v>0.89466599360592292</v>
+        <v>0.89500252397778901</v>
       </c>
       <c r="BA22" s="5">
         <v>5997</v>
@@ -3741,14 +3741,14 @@
       </c>
       <c r="BC22" s="6">
         <f t="shared" si="20"/>
-        <v>3442</v>
+        <v>3444</v>
       </c>
       <c r="BD22" s="5">
-        <v>5366</v>
+        <v>5368</v>
       </c>
       <c r="BE22" s="7">
         <f t="shared" si="21"/>
-        <v>0.89478072369518091</v>
+        <v>0.89511422377855598</v>
       </c>
       <c r="BF22" s="5">
         <v>7214</v>
@@ -3758,14 +3758,14 @@
       </c>
       <c r="BH22" s="6">
         <f t="shared" si="22"/>
-        <v>4613</v>
+        <v>4616</v>
       </c>
       <c r="BI22" s="5">
-        <v>6506</v>
+        <v>6509</v>
       </c>
       <c r="BJ22" s="7">
         <f t="shared" si="23"/>
-        <v>0.90185749930690329</v>
+        <v>0.90227335736068759</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4343,14 +4343,14 @@
       </c>
       <c r="AS25" s="6">
         <f t="shared" si="16"/>
-        <v>11305</v>
+        <v>11307</v>
       </c>
       <c r="AT25" s="5">
-        <v>23457</v>
+        <v>23459</v>
       </c>
       <c r="AU25" s="7">
         <f t="shared" si="17"/>
-        <v>0.91031511952809685</v>
+        <v>0.91039273517541142</v>
       </c>
       <c r="AV25" s="5">
         <v>18472</v>
@@ -4394,14 +4394,14 @@
       </c>
       <c r="BH25" s="6">
         <f t="shared" si="22"/>
-        <v>13560</v>
+        <v>13562</v>
       </c>
       <c r="BI25" s="5">
-        <v>24025</v>
+        <v>24027</v>
       </c>
       <c r="BJ25" s="7">
         <f t="shared" si="23"/>
-        <v>0.91940606941946346</v>
+        <v>0.91948260686540895</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4419,14 +4419,14 @@
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>10107</v>
+        <v>10110</v>
       </c>
       <c r="F26" s="5">
-        <v>11370</v>
+        <v>11373</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>0.68651129090689533</v>
+        <v>0.68669242845067024</v>
       </c>
       <c r="H26" s="3">
         <v>16580</v>
@@ -4436,14 +4436,14 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>10066</v>
+        <v>10068</v>
       </c>
       <c r="K26" s="5">
-        <v>11292</v>
+        <v>11294</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>0.68106151990349817</v>
+        <v>0.68118214716525938</v>
       </c>
       <c r="M26" s="2">
         <v>25396</v>
@@ -4453,14 +4453,14 @@
       </c>
       <c r="O26" s="6">
         <f t="shared" si="4"/>
-        <v>14643</v>
+        <v>14651</v>
       </c>
       <c r="P26" s="5">
-        <v>18709</v>
+        <v>18717</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="5"/>
-        <v>0.73669081745156717</v>
+        <v>0.73700582768939993</v>
       </c>
       <c r="R26" s="5">
         <v>16475</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>8443</v>
+        <v>8445</v>
       </c>
       <c r="U26" s="5">
-        <v>11295</v>
+        <v>11297</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.6855842185128983</v>
+        <v>0.68570561456752654</v>
       </c>
       <c r="W26" s="5">
         <v>16675</v>
@@ -4487,14 +4487,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>7983</v>
+        <v>7986</v>
       </c>
       <c r="Z26" s="5">
-        <v>11447</v>
+        <v>11450</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.68647676161919036</v>
+        <v>0.68665667166416788</v>
       </c>
       <c r="AB26" s="6">
         <v>25656</v>
@@ -4504,14 +4504,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>12756</v>
+        <v>12763</v>
       </c>
       <c r="AE26" s="5">
-        <v>19346</v>
+        <v>19353</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.75405363267851577</v>
+        <v>0.7543264733395697</v>
       </c>
       <c r="AG26" s="5">
         <v>15844</v>
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>7382</v>
+        <v>7383</v>
       </c>
       <c r="AJ26" s="5">
-        <v>11192</v>
+        <v>11193</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.70638727594041906</v>
+        <v>0.70645039131532439</v>
       </c>
       <c r="AL26" s="5">
         <v>16081</v>
@@ -4538,14 +4538,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="AO26" s="5">
-        <v>11421</v>
+        <v>11422</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.71021702630433425</v>
+        <v>0.7102792114918226</v>
       </c>
       <c r="AQ26" s="6">
         <v>26317</v>
@@ -4555,14 +4555,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>13370</v>
+        <v>13376</v>
       </c>
       <c r="AT26" s="5">
-        <v>20096</v>
+        <v>20102</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.76361287380780485</v>
+        <v>0.76384086332028722</v>
       </c>
       <c r="AV26" s="5">
         <v>15987</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>7190</v>
+        <v>7191</v>
       </c>
       <c r="AY26" s="5">
-        <v>11378</v>
+        <v>11379</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71170325889785446</v>
+        <v>0.71176580972039782</v>
       </c>
       <c r="BA26" s="5">
         <v>16133</v>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>7244</v>
+        <v>7245</v>
       </c>
       <c r="BD26" s="5">
-        <v>11566</v>
+        <v>11567</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.71691563875286679</v>
+        <v>0.71697762350461791</v>
       </c>
       <c r="BF26" s="5">
         <v>26642</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>13806</v>
+        <v>13810</v>
       </c>
       <c r="BI26" s="5">
-        <v>20660</v>
+        <v>20664</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.77546730725921476</v>
+        <v>0.77561744613767736</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>85601</v>
+        <v>85609</v>
       </c>
       <c r="F27" s="5">
-        <v>97148</v>
+        <v>97156</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>0.86095872807678331</v>
+        <v>0.86102962680680983</v>
       </c>
       <c r="H27" s="3">
         <v>111842</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="J27" s="6">
         <f t="shared" si="2"/>
-        <v>89138</v>
+        <v>89147</v>
       </c>
       <c r="K27" s="5">
-        <v>96997</v>
+        <v>97006</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="3"/>
-        <v>0.86726811036998619</v>
+        <v>0.86734858103395862</v>
       </c>
       <c r="M27" s="2">
         <v>156288</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>107158</v>
+        <v>107171</v>
       </c>
       <c r="P27" s="5">
-        <v>138405</v>
+        <v>138418</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.88557662776412771</v>
+        <v>0.88565980753480755</v>
       </c>
       <c r="R27" s="5">
         <v>113087</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="T27" s="6">
         <f t="shared" si="6"/>
-        <v>70946</v>
+        <v>70956</v>
       </c>
       <c r="U27" s="5">
-        <v>99644</v>
+        <v>99654</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="7"/>
-        <v>0.8811269199819608</v>
+        <v>0.88121534747583719</v>
       </c>
       <c r="W27" s="5">
         <v>116164</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>68620</v>
+        <v>68631</v>
       </c>
       <c r="Z27" s="5">
-        <v>102885</v>
+        <v>102896</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.88568747632657274</v>
+        <v>0.88578217003546711</v>
       </c>
       <c r="AB27" s="6">
         <v>165468</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>87036</v>
+        <v>87049</v>
       </c>
       <c r="AE27" s="5">
-        <v>147877</v>
+        <v>147890</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.89368941426741122</v>
+        <v>0.89376797930717722</v>
       </c>
       <c r="AG27" s="5">
         <v>116084</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>63637</v>
+        <v>63650</v>
       </c>
       <c r="AJ27" s="5">
-        <v>102252</v>
+        <v>102265</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.88084490541332139</v>
+        <v>0.88095689328417348</v>
       </c>
       <c r="AL27" s="5">
         <v>117992</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="14"/>
-        <v>33214</v>
+        <v>33227</v>
       </c>
       <c r="AO27" s="5">
-        <v>104330</v>
+        <v>104343</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="15"/>
-        <v>0.88421248898230387</v>
+        <v>0.88432266594345377</v>
       </c>
       <c r="AQ27" s="6">
         <v>170879</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>94795</v>
+        <v>94812</v>
       </c>
       <c r="AT27" s="5">
-        <v>153074</v>
+        <v>153091</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.89580346326933091</v>
+        <v>0.89590294887025324</v>
       </c>
       <c r="AV27" s="5">
         <v>116485</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>62225</v>
+        <v>62238</v>
       </c>
       <c r="AY27" s="5">
-        <v>105062</v>
+        <v>105075</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.90193587157144695</v>
+        <v>0.90204747392368112</v>
       </c>
       <c r="BA27" s="5">
         <v>117017</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>62142</v>
+        <v>62155</v>
       </c>
       <c r="BD27" s="5">
-        <v>106724</v>
+        <v>106737</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.91203842176777739</v>
+        <v>0.91214951673688438</v>
       </c>
       <c r="BF27" s="5">
         <v>172738</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>103514</v>
+        <v>103532</v>
       </c>
       <c r="BI27" s="5">
-        <v>156618</v>
+        <v>156636</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.90667947990598474</v>
+        <v>0.90678368396068032</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="E28" s="6">
         <f t="shared" si="0"/>
-        <v>250541</v>
+        <v>250548</v>
       </c>
       <c r="F28" s="5">
-        <v>316182</v>
+        <v>316189</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="1"/>
-        <v>0.83925116060550564</v>
+        <v>0.83926974091091278</v>
       </c>
       <c r="H28" s="3">
         <v>377506</v>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="J28" s="6">
         <f t="shared" si="2"/>
-        <v>278953</v>
+        <v>278959</v>
       </c>
       <c r="K28" s="5">
-        <v>316479</v>
+        <v>316485</v>
       </c>
       <c r="L28" s="7">
         <f t="shared" si="3"/>
-        <v>0.83834164225204366</v>
+        <v>0.8383575360391623</v>
       </c>
       <c r="M28" s="2">
         <v>622937</v>
@@ -4877,14 +4877,14 @@
       </c>
       <c r="O28" s="6">
         <f t="shared" si="4"/>
-        <v>331104</v>
+        <v>331111</v>
       </c>
       <c r="P28" s="5">
-        <v>549572</v>
+        <v>549579</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="5"/>
-        <v>0.88222725572569938</v>
+        <v>0.88223849281709066</v>
       </c>
       <c r="R28" s="5">
         <v>379798</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="T28" s="6">
         <f t="shared" si="6"/>
-        <v>170709</v>
+        <v>170715</v>
       </c>
       <c r="U28" s="5">
-        <v>318459</v>
+        <v>318465</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="7"/>
-        <v>0.83849572667575922</v>
+        <v>0.8385115245472593</v>
       </c>
       <c r="W28" s="5">
         <v>378910</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>163220</v>
+        <v>163226</v>
       </c>
       <c r="Z28" s="5">
-        <v>322465</v>
+        <v>322471</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="9"/>
-        <v>0.85103322688765137</v>
+        <v>0.8510490617824813</v>
       </c>
       <c r="AB28" s="6">
         <v>628364</v>
@@ -4928,14 +4928,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>254349</v>
+        <v>254357</v>
       </c>
       <c r="AE28" s="5">
-        <v>559981</v>
+        <v>559989</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.89117295071009794</v>
+        <v>0.89118568218421168</v>
       </c>
       <c r="AG28" s="5">
         <v>375124</v>
@@ -4945,14 +4945,14 @@
       </c>
       <c r="AI28" s="6">
         <f t="shared" si="12"/>
-        <v>152969</v>
+        <v>152974</v>
       </c>
       <c r="AJ28" s="5">
-        <v>323056</v>
+        <v>323061</v>
       </c>
       <c r="AK28" s="7">
         <f t="shared" si="13"/>
-        <v>0.8611978972286497</v>
+        <v>0.86121122615455159</v>
       </c>
       <c r="AL28" s="5">
         <v>368781</v>
@@ -4962,14 +4962,14 @@
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="14"/>
-        <v>60402</v>
+        <v>60407</v>
       </c>
       <c r="AO28" s="5">
-        <v>328461</v>
+        <v>328466</v>
       </c>
       <c r="AP28" s="7">
         <f t="shared" si="15"/>
-        <v>0.89066681851830765</v>
+        <v>0.89068037670053501</v>
       </c>
       <c r="AQ28" s="6">
         <v>617418</v>
@@ -4979,14 +4979,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>275494</v>
+        <v>275501</v>
       </c>
       <c r="AT28" s="5">
-        <v>571893</v>
+        <v>571900</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.92626551218137465</v>
+        <v>0.9262768497193149</v>
       </c>
       <c r="AV28" s="5">
         <v>357852</v>
@@ -4996,14 +4996,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>144534</v>
+        <v>144539</v>
       </c>
       <c r="AY28" s="5">
-        <v>331097</v>
+        <v>331102</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.92523445446720987</v>
+        <v>0.92524842672389707</v>
       </c>
       <c r="BA28" s="5">
         <v>359943</v>
@@ -5013,14 +5013,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>140357</v>
+        <v>140361</v>
       </c>
       <c r="BD28" s="5">
-        <v>335589</v>
+        <v>335593</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.93233928705378355</v>
+        <v>0.93235039992443247</v>
       </c>
       <c r="BF28" s="5">
         <v>622234</v>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>281137</v>
+        <v>281144</v>
       </c>
       <c r="BI28" s="5">
-        <v>582327</v>
+        <v>582334</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.93586496398461028</v>
+        <v>0.93587621377166785</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="0"/>
-        <v>120381</v>
+        <v>120391</v>
       </c>
       <c r="F30" s="5">
-        <v>135136</v>
+        <v>135146</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="1"/>
-        <v>0.90502755881781716</v>
+        <v>0.90509453042855137</v>
       </c>
       <c r="H30" s="3">
         <v>149659</v>
@@ -5284,14 +5284,14 @@
       </c>
       <c r="J30" s="6">
         <f t="shared" si="2"/>
-        <v>122995</v>
+        <v>123005</v>
       </c>
       <c r="K30" s="5">
-        <v>135773</v>
+        <v>135783</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="3"/>
-        <v>0.90721573710902781</v>
+        <v>0.90728255567657146</v>
       </c>
       <c r="M30" s="2">
         <v>249952</v>
@@ -5301,14 +5301,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>169113</v>
+        <v>169127</v>
       </c>
       <c r="P30" s="5">
-        <v>226878</v>
+        <v>226892</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.90768627576494687</v>
+        <v>0.90774228651901168</v>
       </c>
       <c r="R30" s="5">
         <v>151431</v>
@@ -5318,14 +5318,14 @@
       </c>
       <c r="T30" s="6">
         <f t="shared" si="6"/>
-        <v>94120</v>
+        <v>94129</v>
       </c>
       <c r="U30" s="5">
-        <v>135543</v>
+        <v>135552</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="7"/>
-        <v>0.89508092794738192</v>
+        <v>0.8951403609564752</v>
       </c>
       <c r="W30" s="5">
         <v>154416</v>
@@ -5335,14 +5335,14 @@
       </c>
       <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>93944</v>
+        <v>93955</v>
       </c>
       <c r="Z30" s="5">
-        <v>138524</v>
+        <v>138535</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="9"/>
-        <v>0.89708320381307638</v>
+        <v>0.89715443995440891</v>
       </c>
       <c r="AB30" s="6">
         <v>259264</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>140039</v>
+        <v>140053</v>
       </c>
       <c r="AE30" s="5">
-        <v>234110</v>
+        <v>234124</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.9029792026660084</v>
+        <v>0.90303320167859791</v>
       </c>
       <c r="AG30" s="5">
         <v>153178</v>
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>82951</v>
+        <v>82961</v>
       </c>
       <c r="AJ30" s="5">
-        <v>137355</v>
+        <v>137365</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.89670187624854747</v>
+        <v>0.8967671597749024</v>
       </c>
       <c r="AL30" s="5">
         <v>156106</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>37347</v>
+        <v>37356</v>
       </c>
       <c r="AO30" s="5">
-        <v>141039</v>
+        <v>141048</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.90348224924090037</v>
+        <v>0.90353990237402793</v>
       </c>
       <c r="AQ30" s="6">
         <v>266513</v>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>145533</v>
+        <v>145547</v>
       </c>
       <c r="AT30" s="5">
-        <v>242489</v>
+        <v>242503</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.90985805570459977</v>
+        <v>0.90991058597516816</v>
       </c>
       <c r="AV30" s="5">
         <v>155103</v>
@@ -5420,14 +5420,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>81266</v>
+        <v>81274</v>
       </c>
       <c r="AY30" s="5">
-        <v>142126</v>
+        <v>142134</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.91633301741423445</v>
+        <v>0.91638459604262978</v>
       </c>
       <c r="BA30" s="5">
         <v>156855</v>
@@ -5437,14 +5437,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>80535</v>
+        <v>80543</v>
       </c>
       <c r="BD30" s="5">
-        <v>144567</v>
+        <v>144575</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.92166013196901597</v>
+        <v>0.92171113448726527</v>
       </c>
       <c r="BF30" s="5">
         <v>270589</v>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>155884</v>
+        <v>155901</v>
       </c>
       <c r="BI30" s="5">
-        <v>247593</v>
+        <v>247610</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.91501502278363123</v>
+        <v>0.91507784869303632</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>59913</v>
+        <v>59918</v>
       </c>
       <c r="F31" s="5">
-        <v>66612</v>
+        <v>66617</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>0.92726589362027922</v>
+        <v>0.92733549563595363</v>
       </c>
       <c r="H31" s="3">
         <v>72505</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>57735</v>
+        <v>57740</v>
       </c>
       <c r="K31" s="5">
-        <v>66718</v>
+        <v>66723</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.92018481484035586</v>
+        <v>0.92025377560168264</v>
       </c>
       <c r="M31" s="2">
         <v>118891</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="O31" s="6">
         <f t="shared" si="4"/>
-        <v>80419</v>
+        <v>80422</v>
       </c>
       <c r="P31" s="5">
-        <v>111874</v>
+        <v>111877</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="5"/>
-        <v>0.94097955269953149</v>
+        <v>0.94100478589632519</v>
       </c>
       <c r="R31" s="5">
         <v>72813</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>42978</v>
+        <v>42982</v>
       </c>
       <c r="U31" s="5">
-        <v>67147</v>
+        <v>67151</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.92218422534437527</v>
+        <v>0.92223916058945521</v>
       </c>
       <c r="W31" s="5">
         <v>74776</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>41997</v>
+        <v>42002</v>
       </c>
       <c r="Z31" s="5">
-        <v>68801</v>
+        <v>68806</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.92009468278592066</v>
+        <v>0.92016154916015835</v>
       </c>
       <c r="AB31" s="6">
         <v>124489</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>65116</v>
+        <v>65119</v>
       </c>
       <c r="AE31" s="5">
-        <v>116342</v>
+        <v>116345</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.93455646683642735</v>
+        <v>0.93458056535115552</v>
       </c>
       <c r="AG31" s="5">
         <v>73552</v>
@@ -5581,14 +5581,14 @@
       </c>
       <c r="AI31" s="6">
         <f t="shared" si="12"/>
-        <v>38798</v>
+        <v>38801</v>
       </c>
       <c r="AJ31" s="5">
-        <v>67164</v>
+        <v>67167</v>
       </c>
       <c r="AK31" s="7">
         <f t="shared" si="13"/>
-        <v>0.91314988035675437</v>
+        <v>0.91319066782684355</v>
       </c>
       <c r="AL31" s="5">
         <v>74464</v>
@@ -5598,14 +5598,14 @@
       </c>
       <c r="AN31" s="6">
         <f t="shared" si="14"/>
-        <v>20744</v>
+        <v>20747</v>
       </c>
       <c r="AO31" s="5">
-        <v>68247</v>
+        <v>68250</v>
       </c>
       <c r="AP31" s="7">
         <f t="shared" si="15"/>
-        <v>0.91650999140524281</v>
+        <v>0.91655027932960897</v>
       </c>
       <c r="AQ31" s="6">
         <v>126646</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>67765</v>
+        <v>67768</v>
       </c>
       <c r="AT31" s="5">
-        <v>119007</v>
+        <v>119010</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.93968226394832843</v>
+        <v>0.93970595202375129</v>
       </c>
       <c r="AV31" s="5">
         <v>72827</v>
@@ -5632,14 +5632,14 @@
       </c>
       <c r="AX31" s="6">
         <f t="shared" si="18"/>
-        <v>33464</v>
+        <v>33467</v>
       </c>
       <c r="AY31" s="5">
-        <v>68016</v>
+        <v>68019</v>
       </c>
       <c r="AZ31" s="7">
         <f t="shared" si="19"/>
-        <v>0.93393933568594067</v>
+        <v>0.93398052919933539</v>
       </c>
       <c r="BA31" s="5">
         <v>73978</v>
@@ -5649,14 +5649,14 @@
       </c>
       <c r="BC31" s="6">
         <f t="shared" si="20"/>
-        <v>32843</v>
+        <v>32847</v>
       </c>
       <c r="BD31" s="5">
-        <v>69842</v>
+        <v>69846</v>
       </c>
       <c r="BE31" s="7">
         <f t="shared" si="21"/>
-        <v>0.94409148665819564</v>
+        <v>0.94414555678715295</v>
       </c>
       <c r="BF31" s="5">
         <v>129555</v>
@@ -5666,14 +5666,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>72565</v>
+        <v>72569</v>
       </c>
       <c r="BI31" s="5">
-        <v>121943</v>
+        <v>121947</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.94124503106788626</v>
+        <v>0.94127590598587474</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5691,14 +5691,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>159901</v>
+        <v>159903</v>
       </c>
       <c r="F32" s="5">
-        <v>176168</v>
+        <v>176170</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.94886917554036654</v>
+        <v>0.9488799478619635</v>
       </c>
       <c r="H32" s="3">
         <v>186389</v>
@@ -5708,14 +5708,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>154548</v>
+        <v>154551</v>
       </c>
       <c r="K32" s="5">
-        <v>176547</v>
+        <v>176550</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.94719645472640557</v>
+        <v>0.94721255009684047</v>
       </c>
       <c r="M32" s="2">
         <v>382231</v>
@@ -5725,14 +5725,14 @@
       </c>
       <c r="O32" s="6">
         <f t="shared" si="4"/>
-        <v>258303</v>
+        <v>258309</v>
       </c>
       <c r="P32" s="5">
-        <v>364173</v>
+        <v>364179</v>
       </c>
       <c r="Q32" s="7">
         <f t="shared" si="5"/>
-        <v>0.95275631751480128</v>
+        <v>0.9527720148287292</v>
       </c>
       <c r="R32" s="5">
         <v>184231</v>
@@ -5742,14 +5742,14 @@
       </c>
       <c r="T32" s="6">
         <f t="shared" si="6"/>
-        <v>109773</v>
+        <v>109774</v>
       </c>
       <c r="U32" s="5">
-        <v>173280</v>
+        <v>173281</v>
       </c>
       <c r="V32" s="7">
         <f t="shared" si="7"/>
-        <v>0.94055832080377355</v>
+        <v>0.94056374877192217</v>
       </c>
       <c r="W32" s="5">
         <v>187639</v>
@@ -5759,14 +5759,14 @@
       </c>
       <c r="Y32" s="6">
         <f t="shared" si="8"/>
-        <v>107224</v>
+        <v>107226</v>
       </c>
       <c r="Z32" s="5">
-        <v>177606</v>
+        <v>177608</v>
       </c>
       <c r="AA32" s="7">
         <f t="shared" si="9"/>
-        <v>0.94653030553349782</v>
+        <v>0.94654096429846679</v>
       </c>
       <c r="AB32" s="6">
         <v>392348</v>
@@ -5776,14 +5776,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>213228</v>
+        <v>213232</v>
       </c>
       <c r="AE32" s="5">
-        <v>373025</v>
+        <v>373029</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.95075035427732524</v>
+        <v>0.95076054930826714</v>
       </c>
       <c r="AG32" s="5">
         <v>183147</v>
@@ -5793,14 +5793,14 @@
       </c>
       <c r="AI32" s="6">
         <f t="shared" si="12"/>
-        <v>99025</v>
+        <v>99027</v>
       </c>
       <c r="AJ32" s="5">
-        <v>174269</v>
+        <v>174271</v>
       </c>
       <c r="AK32" s="7">
         <f t="shared" si="13"/>
-        <v>0.95152527750932314</v>
+        <v>0.95153619769911602</v>
       </c>
       <c r="AL32" s="5">
         <v>187303</v>
@@ -5810,14 +5810,14 @@
       </c>
       <c r="AN32" s="6">
         <f t="shared" si="14"/>
-        <v>44649</v>
+        <v>44652</v>
       </c>
       <c r="AO32" s="5">
-        <v>178172</v>
+        <v>178175</v>
       </c>
       <c r="AP32" s="7">
         <f t="shared" si="15"/>
-        <v>0.95125011345253407</v>
+        <v>0.95126613028088181</v>
       </c>
       <c r="AQ32" s="6">
         <v>402574</v>
@@ -5827,14 +5827,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>213483</v>
+        <v>213493</v>
       </c>
       <c r="AT32" s="5">
-        <v>382370</v>
+        <v>382380</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.94981295364330531</v>
+        <v>0.9498377937969168</v>
       </c>
       <c r="AV32" s="5">
         <v>187080</v>
@@ -5844,14 +5844,14 @@
       </c>
       <c r="AX32" s="6">
         <f t="shared" si="18"/>
-        <v>80101</v>
+        <v>80104</v>
       </c>
       <c r="AY32" s="5">
-        <v>178092</v>
+        <v>178095</v>
       </c>
       <c r="AZ32" s="7">
         <f t="shared" si="19"/>
-        <v>0.95195638229634383</v>
+        <v>0.95197241821680567</v>
       </c>
       <c r="BA32" s="5">
         <v>189893</v>
@@ -5861,14 +5861,14 @@
       </c>
       <c r="BC32" s="6">
         <f t="shared" si="20"/>
-        <v>79046</v>
+        <v>79049</v>
       </c>
       <c r="BD32" s="5">
-        <v>182596</v>
+        <v>182599</v>
       </c>
       <c r="BE32" s="7">
         <f t="shared" si="21"/>
-        <v>0.96157309642798838</v>
+        <v>0.96158889479864973</v>
       </c>
       <c r="BF32" s="5">
         <v>410654</v>
@@ -5878,14 +5878,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>227756</v>
+        <v>227767</v>
       </c>
       <c r="BI32" s="5">
-        <v>388837</v>
+        <v>388848</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94687254964032985</v>
+        <v>0.94689933618082378</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="E33" s="6">
         <f t="shared" si="0"/>
-        <v>398255</v>
+        <v>398259</v>
       </c>
       <c r="F33" s="5">
-        <v>534837</v>
+        <v>534841</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="1"/>
-        <v>0.96450443626920579</v>
+        <v>0.96451164971506886</v>
       </c>
       <c r="H33" s="3">
         <v>558618</v>
@@ -5920,14 +5920,14 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" si="2"/>
-        <v>412267</v>
+        <v>412272</v>
       </c>
       <c r="K33" s="5">
-        <v>539923</v>
+        <v>539928</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="3"/>
-        <v>0.9665334808402164</v>
+        <v>0.96654243150059616</v>
       </c>
       <c r="M33" s="2">
         <v>943614</v>
@@ -5937,14 +5937,14 @@
       </c>
       <c r="O33" s="6">
         <f t="shared" si="4"/>
-        <v>332779</v>
+        <v>332784</v>
       </c>
       <c r="P33" s="5">
-        <v>926013</v>
+        <v>926018</v>
       </c>
       <c r="Q33" s="7">
         <f t="shared" si="5"/>
-        <v>0.98134724580177912</v>
+        <v>0.98135254457860943</v>
       </c>
       <c r="R33" s="5">
         <v>563773</v>
@@ -5954,14 +5954,14 @@
       </c>
       <c r="T33" s="6">
         <f t="shared" si="6"/>
-        <v>150530</v>
+        <v>150534</v>
       </c>
       <c r="U33" s="5">
-        <v>549195</v>
+        <v>549199</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="7"/>
-        <v>0.97414207491312998</v>
+        <v>0.97414916996734502</v>
       </c>
       <c r="W33" s="5">
         <v>571583</v>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="Y33" s="6">
         <f t="shared" si="8"/>
-        <v>139892</v>
+        <v>139896</v>
       </c>
       <c r="Z33" s="5">
-        <v>554795</v>
+        <v>554799</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="9"/>
-        <v>0.97062893752963264</v>
+        <v>0.97063593563839368</v>
       </c>
       <c r="AB33" s="6">
         <v>961057</v>
@@ -5988,14 +5988,14 @@
       </c>
       <c r="AD33" s="6">
         <f t="shared" si="10"/>
-        <v>220228</v>
+        <v>220234</v>
       </c>
       <c r="AE33" s="5">
-        <v>941293</v>
+        <v>941299</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="11"/>
-        <v>0.97943514276468513</v>
+        <v>0.97944138589074325</v>
       </c>
       <c r="AG33" s="5">
         <v>565645</v>
@@ -6005,14 +6005,14 @@
       </c>
       <c r="AI33" s="6">
         <f t="shared" si="12"/>
-        <v>154551</v>
+        <v>154554</v>
       </c>
       <c r="AJ33" s="5">
-        <v>550816</v>
+        <v>550819</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="13"/>
-        <v>0.97378391040316803</v>
+        <v>0.97378921408303798</v>
       </c>
       <c r="AL33" s="5">
         <v>569536</v>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="AN33" s="6">
         <f t="shared" si="14"/>
-        <v>52845</v>
+        <v>52849</v>
       </c>
       <c r="AO33" s="5">
-        <v>556508</v>
+        <v>556512</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="15"/>
-        <v>0.97712523879087543</v>
+        <v>0.97713226205191595</v>
       </c>
       <c r="AQ33" s="6">
         <v>971221</v>
@@ -6039,14 +6039,14 @@
       </c>
       <c r="AS33" s="6">
         <f t="shared" si="16"/>
-        <v>215716</v>
+        <v>215722</v>
       </c>
       <c r="AT33" s="5">
-        <v>953005</v>
+        <v>953011</v>
       </c>
       <c r="AU33" s="7">
         <f t="shared" si="17"/>
-        <v>0.9812442276268738</v>
+        <v>0.98125040541751052</v>
       </c>
       <c r="AV33" s="5">
         <v>571074</v>
@@ -6056,14 +6056,14 @@
       </c>
       <c r="AX33" s="6">
         <f t="shared" si="18"/>
-        <v>101109</v>
+        <v>101111</v>
       </c>
       <c r="AY33" s="5">
-        <v>560628</v>
+        <v>560630</v>
       </c>
       <c r="AZ33" s="7">
         <f t="shared" si="19"/>
-        <v>0.98170814990701727</v>
+        <v>0.98171165208011568</v>
       </c>
       <c r="BA33" s="5">
         <v>575700</v>
@@ -6073,14 +6073,14 @@
       </c>
       <c r="BC33" s="6">
         <f t="shared" si="20"/>
-        <v>95009</v>
+        <v>95011</v>
       </c>
       <c r="BD33" s="5">
-        <v>570881</v>
+        <v>570883</v>
       </c>
       <c r="BE33" s="7">
         <f t="shared" si="21"/>
-        <v>0.99162932082681954</v>
+        <v>0.99163279485843325</v>
       </c>
       <c r="BF33" s="5">
         <v>986775</v>
@@ -6090,14 +6090,14 @@
       </c>
       <c r="BH33" s="6">
         <f t="shared" si="22"/>
-        <v>221368</v>
+        <v>221377</v>
       </c>
       <c r="BI33" s="5">
-        <v>972668</v>
+        <v>972677</v>
       </c>
       <c r="BJ33" s="7">
         <f t="shared" si="23"/>
-        <v>0.98570393453421501</v>
+        <v>0.98571305515441721</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>564933</v>
+        <v>564952</v>
       </c>
       <c r="F36" s="5">
-        <v>708774</v>
+        <v>708793</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.94803283994938647</v>
+        <v>0.94805825372579333</v>
       </c>
       <c r="H36" s="3">
         <v>754952</v>
@@ -6532,14 +6532,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>589811</v>
+        <v>589828</v>
       </c>
       <c r="K36" s="5">
-        <v>714375</v>
+        <v>714392</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.94625221206116417</v>
+        <v>0.94627473004906271</v>
       </c>
       <c r="M36" s="2">
         <v>1378095</v>
@@ -6549,14 +6549,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>749514</v>
+        <v>749531</v>
       </c>
       <c r="P36" s="5">
-        <v>1322826</v>
+        <v>1322843</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.9598946371621695</v>
+        <v>0.95990697303161243</v>
       </c>
       <c r="R36" s="5">
         <v>758000</v>
@@ -6566,14 +6566,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>349387</v>
+        <v>349401</v>
       </c>
       <c r="U36" s="5">
-        <v>717573</v>
+        <v>717587</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.94666622691292879</v>
+        <v>0.94668469656992082</v>
       </c>
       <c r="W36" s="5">
         <v>766789</v>
@@ -6583,14 +6583,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>352510</v>
+        <v>352528</v>
       </c>
       <c r="Z36" s="5">
-        <v>731770</v>
+        <v>731788</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.9543303307689599</v>
+        <v>0.9543538052841134</v>
       </c>
       <c r="AB36" s="6">
         <v>1410553</v>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>580330</v>
+        <v>580353</v>
       </c>
       <c r="AE36" s="5">
-        <v>1353279</v>
+        <v>1353302</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.95939606664903765</v>
+        <v>0.95941237231071785</v>
       </c>
       <c r="AG36" s="5">
         <v>767229</v>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>321672</v>
+        <v>321688</v>
       </c>
       <c r="AJ36" s="5">
-        <v>729709</v>
+        <v>729725</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.95109673904401426</v>
+        <v>0.95111759331307866</v>
       </c>
       <c r="AL36" s="5">
         <v>779513</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>158998</v>
+        <v>159012</v>
       </c>
       <c r="AO36" s="5">
-        <v>741630</v>
+        <v>741644</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.95140170850261641</v>
+        <v>0.95141966843400949</v>
       </c>
       <c r="AQ36" s="6">
         <v>1443943</v>
@@ -6651,14 +6651,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>553748</v>
+        <v>553770</v>
       </c>
       <c r="AT36" s="5">
-        <v>1380615</v>
+        <v>1380637</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.95614231309684661</v>
+        <v>0.95615754915533369</v>
       </c>
       <c r="AV36" s="5">
         <v>783108</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>259318</v>
+        <v>259332</v>
       </c>
       <c r="AY36" s="5">
-        <v>745616</v>
+        <v>745630</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.95212410037951345</v>
+        <v>0.95214197786256816</v>
       </c>
       <c r="BA36" s="5">
         <v>793830</v>
@@ -6685,14 +6685,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>252854</v>
+        <v>252868</v>
       </c>
       <c r="BD36" s="5">
-        <v>759200</v>
+        <v>759214</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.956376050287845</v>
+        <v>0.95639368630563215</v>
       </c>
       <c r="BF36" s="5">
         <v>1468416</v>
@@ -6702,14 +6702,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="24"/>
-        <v>554428</v>
+        <v>554453</v>
       </c>
       <c r="BI36" s="5">
-        <v>1403599</v>
+        <v>1403624</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="25"/>
-        <v>0.95585923879881451</v>
+        <v>0.95587626394700143</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
-        <v>483603</v>
+        <v>483613</v>
       </c>
       <c r="F37" s="5">
-        <v>547998</v>
+        <v>548008</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="1"/>
-        <v>0.92502072020215487</v>
+        <v>0.92503760020391046</v>
       </c>
       <c r="H37" s="3">
         <v>593173</v>
@@ -6744,14 +6744,14 @@
       </c>
       <c r="J37" s="6">
         <f t="shared" si="2"/>
-        <v>489486</v>
+        <v>489494</v>
       </c>
       <c r="K37" s="5">
-        <v>547532</v>
+        <v>547540</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="3"/>
-        <v>0.9230561741684129</v>
+        <v>0.92306966095894449</v>
       </c>
       <c r="M37" s="2">
         <v>768378</v>
@@ -6761,14 +6761,14 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="4"/>
-        <v>455255</v>
+        <v>455268</v>
       </c>
       <c r="P37" s="5">
-        <v>713662</v>
+        <v>713675</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="5"/>
-        <v>0.92879025687877581</v>
+        <v>0.92880717563490889</v>
       </c>
       <c r="R37" s="5">
         <v>601605</v>
@@ -6778,14 +6778,14 @@
       </c>
       <c r="T37" s="6">
         <f t="shared" si="6"/>
-        <v>294894</v>
+        <v>294902</v>
       </c>
       <c r="U37" s="5">
-        <v>556538</v>
+        <v>556546</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="7"/>
-        <v>0.9250887210046459</v>
+        <v>0.92510201876646636</v>
       </c>
       <c r="W37" s="5">
         <v>609453</v>
@@ -6795,14 +6795,14 @@
       </c>
       <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>298777</v>
+        <v>298786</v>
       </c>
       <c r="Z37" s="5">
-        <v>564814</v>
+        <v>564823</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="9"/>
-        <v>0.92675563168940012</v>
+        <v>0.92677039902994984</v>
       </c>
       <c r="AB37" s="6">
         <v>790568</v>
@@ -6812,14 +6812,14 @@
       </c>
       <c r="AD37" s="6">
         <f t="shared" si="10"/>
-        <v>341997</v>
+        <v>342009</v>
       </c>
       <c r="AE37" s="5">
-        <v>735772</v>
+        <v>735784</v>
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="11"/>
-        <v>0.93068780927130867</v>
+        <v>0.93070298823124642</v>
       </c>
       <c r="AG37" s="5">
         <v>617773</v>
@@ -6829,14 +6829,14 @@
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="12"/>
-        <v>268078</v>
+        <v>268086</v>
       </c>
       <c r="AJ37" s="5">
-        <v>572914</v>
+        <v>572922</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="13"/>
-        <v>0.92738594920788053</v>
+        <v>0.92739889894831917</v>
       </c>
       <c r="AL37" s="5">
         <v>624724</v>
@@ -6846,14 +6846,14 @@
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="14"/>
-        <v>101149</v>
+        <v>101156</v>
       </c>
       <c r="AO37" s="5">
-        <v>581003</v>
+        <v>581010</v>
       </c>
       <c r="AP37" s="7">
         <f t="shared" si="15"/>
-        <v>0.93001549484252244</v>
+        <v>0.93002669979062758</v>
       </c>
       <c r="AQ37" s="6">
         <v>810789</v>
@@ -6863,14 +6863,14 @@
       </c>
       <c r="AS37" s="6">
         <f t="shared" si="16"/>
-        <v>350612</v>
+        <v>350623</v>
       </c>
       <c r="AT37" s="5">
-        <v>756805</v>
+        <v>756816</v>
       </c>
       <c r="AU37" s="7">
         <f t="shared" si="17"/>
-        <v>0.93341794227598052</v>
+        <v>0.93343150930760033</v>
       </c>
       <c r="AV37" s="5">
         <v>633338</v>
@@ -6880,14 +6880,14 @@
       </c>
       <c r="AX37" s="6">
         <f t="shared" si="18"/>
-        <v>242750</v>
+        <v>242757</v>
       </c>
       <c r="AY37" s="5">
-        <v>591815</v>
+        <v>591822</v>
       </c>
       <c r="AZ37" s="7">
         <f t="shared" si="19"/>
-        <v>0.9344378515105678</v>
+        <v>0.93444890406070691</v>
       </c>
       <c r="BA37" s="5">
         <v>640933</v>
@@ -6897,14 +6897,14 @@
       </c>
       <c r="BC37" s="6">
         <f t="shared" si="20"/>
-        <v>236685</v>
+        <v>236695</v>
       </c>
       <c r="BD37" s="5">
-        <v>600797</v>
+        <v>600807</v>
       </c>
       <c r="BE37" s="7">
         <f t="shared" si="21"/>
-        <v>0.93737878998272828</v>
+        <v>0.93739439223756615</v>
       </c>
       <c r="BF37" s="5">
         <v>830528</v>
@@ -6914,14 +6914,14 @@
       </c>
       <c r="BH37" s="6">
         <f t="shared" si="24"/>
-        <v>361752</v>
+        <v>361770</v>
       </c>
       <c r="BI37" s="5">
-        <v>776569</v>
+        <v>776587</v>
       </c>
       <c r="BJ37" s="7">
         <f t="shared" si="25"/>
-        <v>0.93503048663019184</v>
+        <v>0.93505215959004395</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="AI38" s="6">
         <f t="shared" si="12"/>
-        <v>9949</v>
+        <v>9950</v>
       </c>
       <c r="AJ38" s="5">
-        <v>20031</v>
+        <v>20032</v>
       </c>
       <c r="AK38" s="7">
         <f t="shared" si="13"/>
-        <v>0.82718037661050547</v>
+        <v>0.82722167162206806</v>
       </c>
       <c r="AL38" s="5">
         <v>24425</v>
@@ -7058,14 +7058,14 @@
       </c>
       <c r="AN38" s="6">
         <f t="shared" si="14"/>
-        <v>5304</v>
+        <v>5305</v>
       </c>
       <c r="AO38" s="5">
-        <v>20348</v>
+        <v>20349</v>
       </c>
       <c r="AP38" s="7">
         <f t="shared" si="15"/>
-        <v>0.83308085977482083</v>
+        <v>0.833121801432958</v>
       </c>
       <c r="AQ38" s="6">
         <v>36434</v>
@@ -7075,14 +7075,14 @@
       </c>
       <c r="AS38" s="6">
         <f t="shared" si="16"/>
-        <v>15504</v>
+        <v>15505</v>
       </c>
       <c r="AT38" s="5">
-        <v>32161</v>
+        <v>32162</v>
       </c>
       <c r="AU38" s="7">
         <f t="shared" si="17"/>
-        <v>0.88271943788768736</v>
+        <v>0.88274688477795471</v>
       </c>
       <c r="AV38" s="5">
         <v>24471</v>
@@ -7092,14 +7092,14 @@
       </c>
       <c r="AX38" s="6">
         <f t="shared" si="18"/>
-        <v>9184</v>
+        <v>9185</v>
       </c>
       <c r="AY38" s="5">
-        <v>20440</v>
+        <v>20441</v>
       </c>
       <c r="AZ38" s="7">
         <f t="shared" si="19"/>
-        <v>0.83527440644027628</v>
+        <v>0.83531527113726456</v>
       </c>
       <c r="BA38" s="5">
         <v>24769</v>
@@ -7109,14 +7109,14 @@
       </c>
       <c r="BC38" s="6">
         <f t="shared" si="20"/>
-        <v>9160</v>
+        <v>9161</v>
       </c>
       <c r="BD38" s="5">
-        <v>20701</v>
+        <v>20702</v>
       </c>
       <c r="BE38" s="7">
         <f t="shared" si="21"/>
-        <v>0.83576244499172347</v>
+        <v>0.8358028180386774</v>
       </c>
       <c r="BF38" s="5">
         <v>37269</v>
@@ -7126,14 +7126,14 @@
       </c>
       <c r="BH38" s="6">
         <f t="shared" si="24"/>
-        <v>15817</v>
+        <v>15818</v>
       </c>
       <c r="BI38" s="5">
-        <v>32736</v>
+        <v>32737</v>
       </c>
       <c r="BJ38" s="7">
         <f t="shared" si="25"/>
-        <v>0.87837076390565882</v>
+        <v>0.87839759585714672</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7363,14 +7363,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>214672</v>
+        <v>214677</v>
       </c>
       <c r="F40" s="5">
-        <v>240181</v>
+        <v>240186</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.94169055059144569</v>
+        <v>0.94171015436007421</v>
       </c>
       <c r="H40" s="3">
         <v>254802</v>
@@ -7380,14 +7380,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>221357</v>
+        <v>221359</v>
       </c>
       <c r="K40" s="5">
-        <v>240313</v>
+        <v>240315</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.94313623911900224</v>
+        <v>0.94314408835095487</v>
       </c>
       <c r="M40" s="2">
         <v>315837</v>
@@ -7397,14 +7397,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>210325</v>
+        <v>210331</v>
       </c>
       <c r="P40" s="5">
-        <v>299296</v>
+        <v>299302</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.94762804864534556</v>
+        <v>0.94764704578627579</v>
       </c>
       <c r="R40" s="5">
         <v>257348</v>
@@ -7414,14 +7414,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>121895</v>
+        <v>121899</v>
       </c>
       <c r="U40" s="5">
-        <v>242353</v>
+        <v>242357</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.94173259555154887</v>
+        <v>0.94174813870712037</v>
       </c>
       <c r="W40" s="5">
         <v>259512</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>111084</v>
+        <v>111088</v>
       </c>
       <c r="Z40" s="5">
-        <v>244307</v>
+        <v>244311</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.94140926045809059</v>
+        <v>0.94142467400351426</v>
       </c>
       <c r="AB40" s="6">
         <v>322067</v>
@@ -7448,14 +7448,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>125317</v>
+        <v>125320</v>
       </c>
       <c r="AE40" s="5">
-        <v>305013</v>
+        <v>305016</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.94704828498418026</v>
+        <v>0.94705759981618731</v>
       </c>
       <c r="AG40" s="5">
         <v>262041</v>
@@ -7465,14 +7465,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>92322</v>
+        <v>92325</v>
       </c>
       <c r="AJ40" s="5">
-        <v>247105</v>
+        <v>247108</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.94300128605828859</v>
+        <v>0.94301273464839475</v>
       </c>
       <c r="AL40" s="5">
         <v>264607</v>
@@ -7482,14 +7482,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>39736</v>
+        <v>39742</v>
       </c>
       <c r="AO40" s="5">
-        <v>250037</v>
+        <v>250043</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.94493720876620801</v>
+        <v>0.9449598839032981</v>
       </c>
       <c r="AQ40" s="6">
         <v>328683</v>
@@ -7499,14 +7499,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>125213</v>
+        <v>125217</v>
       </c>
       <c r="AT40" s="5">
-        <v>312594</v>
+        <v>312598</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.95105009994432321</v>
+        <v>0.95106226972493257</v>
       </c>
       <c r="AV40" s="5">
         <v>267796</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>91418</v>
+        <v>91422</v>
       </c>
       <c r="AY40" s="5">
-        <v>253318</v>
+        <v>253322</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.94593645909572954</v>
+        <v>0.94595139583862342</v>
       </c>
       <c r="BA40" s="5">
         <v>270158</v>
@@ -7533,14 +7533,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>92566</v>
+        <v>92569</v>
       </c>
       <c r="BD40" s="5">
-        <v>256017</v>
+        <v>256020</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.94765655653358405</v>
+        <v>0.94766766114644019</v>
       </c>
       <c r="BF40" s="5">
         <v>335514</v>
@@ -7550,14 +7550,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="24"/>
-        <v>137565</v>
+        <v>137571</v>
       </c>
       <c r="BI40" s="5">
-        <v>318071</v>
+        <v>318077</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="25"/>
-        <v>0.94801111130981119</v>
+        <v>0.94802899431916399</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7575,14 +7575,14 @@
       </c>
       <c r="E41" s="6">
         <f t="shared" si="0"/>
-        <v>580269</v>
+        <v>580304</v>
       </c>
       <c r="F41" s="5">
-        <v>764116</v>
+        <v>764151</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="1"/>
-        <v>0.95142966714978006</v>
+        <v>0.95147324697057989</v>
       </c>
       <c r="H41" s="3">
         <v>805681</v>
@@ -7592,14 +7592,14 @@
       </c>
       <c r="J41" s="6">
         <f t="shared" si="2"/>
-        <v>690143</v>
+        <v>690178</v>
       </c>
       <c r="K41" s="5">
-        <v>764207</v>
+        <v>764242</v>
       </c>
       <c r="L41" s="7">
         <f t="shared" si="3"/>
-        <v>0.94852305068631382</v>
+        <v>0.94856649219728406</v>
       </c>
       <c r="M41" s="2">
         <v>924274</v>
@@ -7609,14 +7609,14 @@
       </c>
       <c r="O41" s="6">
         <f t="shared" si="4"/>
-        <v>505836</v>
+        <v>505875</v>
       </c>
       <c r="P41" s="5">
-        <v>874712</v>
+        <v>874751</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" si="5"/>
-        <v>0.94637737294352109</v>
+        <v>0.94641956822327578</v>
       </c>
       <c r="R41" s="5">
         <v>822173</v>
@@ -7626,14 +7626,14 @@
       </c>
       <c r="T41" s="6">
         <f t="shared" si="6"/>
-        <v>371831</v>
+        <v>371870</v>
       </c>
       <c r="U41" s="5">
-        <v>778551</v>
+        <v>778590</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="7"/>
-        <v>0.94694303996847384</v>
+        <v>0.94699047524061242</v>
       </c>
       <c r="W41" s="5">
         <v>833879</v>
@@ -7643,14 +7643,14 @@
       </c>
       <c r="Y41" s="6">
         <f t="shared" si="8"/>
-        <v>376150</v>
+        <v>376185</v>
       </c>
       <c r="Z41" s="5">
-        <v>785996</v>
+        <v>786031</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="9"/>
-        <v>0.94257799992564872</v>
+        <v>0.94261997244204498</v>
       </c>
       <c r="AB41" s="6">
         <v>956956</v>
@@ -7660,14 +7660,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>367768</v>
+        <v>367815</v>
       </c>
       <c r="AE41" s="5">
-        <v>899889</v>
+        <v>899936</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.94036611923641211</v>
+        <v>0.94041523330226262</v>
       </c>
       <c r="AG41" s="5">
         <v>851169</v>
@@ -7677,14 +7677,14 @@
       </c>
       <c r="AI41" s="6">
         <f t="shared" si="12"/>
-        <v>370315</v>
+        <v>370351</v>
       </c>
       <c r="AJ41" s="5">
-        <v>798448</v>
+        <v>798484</v>
       </c>
       <c r="AK41" s="7">
         <f t="shared" si="13"/>
-        <v>0.93806047917628577</v>
+        <v>0.9381027739497092</v>
       </c>
       <c r="AL41" s="5">
         <v>859964</v>
@@ -7694,14 +7694,14 @@
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="14"/>
-        <v>117910</v>
+        <v>117954</v>
       </c>
       <c r="AO41" s="5">
-        <v>806933</v>
+        <v>806977</v>
       </c>
       <c r="AP41" s="7">
         <f t="shared" si="15"/>
-        <v>0.93833346512179583</v>
+        <v>0.9383846300542813</v>
       </c>
       <c r="AQ41" s="6">
         <v>982238</v>
@@ -7711,14 +7711,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>370178</v>
+        <v>370228</v>
       </c>
       <c r="AT41" s="5">
-        <v>921053</v>
+        <v>921103</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.93770857979430644</v>
+        <v>0.93775948395399078</v>
       </c>
       <c r="AV41" s="5">
         <v>867973</v>
@@ -7728,14 +7728,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>303431</v>
+        <v>303473</v>
       </c>
       <c r="AY41" s="5">
-        <v>816628</v>
+        <v>816670</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.94084493411661418</v>
+        <v>0.94089332271856385</v>
       </c>
       <c r="BA41" s="5">
         <v>869274</v>
@@ -7745,14 +7745,14 @@
       </c>
       <c r="BC41" s="6">
         <f t="shared" si="20"/>
-        <v>301995</v>
+        <v>302041</v>
       </c>
       <c r="BD41" s="5">
-        <v>822855</v>
+        <v>822901</v>
       </c>
       <c r="BE41" s="7">
         <f t="shared" si="21"/>
-        <v>0.94660026642922712</v>
+        <v>0.94665318415137234</v>
       </c>
       <c r="BF41" s="5">
         <v>986817</v>
@@ -7762,14 +7762,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="24"/>
-        <v>395280</v>
+        <v>395350</v>
       </c>
       <c r="BI41" s="5">
-        <v>937097</v>
+        <v>937167</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="25"/>
-        <v>0.9496157848922343</v>
+        <v>0.94968672003015753</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7804,14 +7804,14 @@
       </c>
       <c r="J42" s="6">
         <f t="shared" si="2"/>
-        <v>13736</v>
+        <v>13737</v>
       </c>
       <c r="K42" s="5">
-        <v>15849</v>
+        <v>15850</v>
       </c>
       <c r="L42" s="7">
         <f t="shared" si="3"/>
-        <v>0.91485800046178711</v>
+        <v>0.9149157238513046</v>
       </c>
       <c r="M42" s="2">
         <v>19854</v>
@@ -7923,14 +7923,14 @@
       </c>
       <c r="AS42" s="6">
         <f t="shared" si="16"/>
-        <v>8678</v>
+        <v>8679</v>
       </c>
       <c r="AT42" s="5">
-        <v>18712</v>
+        <v>18713</v>
       </c>
       <c r="AU42" s="7">
         <f t="shared" si="17"/>
-        <v>0.92523734177215189</v>
+        <v>0.92528678797468356</v>
       </c>
       <c r="AV42" s="5">
         <v>17809</v>
@@ -7940,14 +7940,14 @@
       </c>
       <c r="AX42" s="6">
         <f t="shared" si="18"/>
-        <v>7434</v>
+        <v>7435</v>
       </c>
       <c r="AY42" s="5">
-        <v>16742</v>
+        <v>16743</v>
       </c>
       <c r="AZ42" s="7">
         <f t="shared" si="19"/>
-        <v>0.94008647313156268</v>
+        <v>0.9401426245156943</v>
       </c>
       <c r="BA42" s="5">
         <v>17859</v>
@@ -7957,14 +7957,14 @@
       </c>
       <c r="BC42" s="6">
         <f t="shared" si="20"/>
-        <v>7289</v>
+        <v>7291</v>
       </c>
       <c r="BD42" s="5">
-        <v>16814</v>
+        <v>16816</v>
       </c>
       <c r="BE42" s="7">
         <f t="shared" si="21"/>
-        <v>0.94148608544711354</v>
+        <v>0.94159807380032479</v>
       </c>
       <c r="BF42" s="5">
         <v>20264</v>
@@ -7974,14 +7974,14 @@
       </c>
       <c r="BH42" s="6">
         <f t="shared" si="24"/>
-        <v>9061</v>
+        <v>9062</v>
       </c>
       <c r="BI42" s="5">
-        <v>19055</v>
+        <v>19056</v>
       </c>
       <c r="BJ42" s="7">
         <f t="shared" si="25"/>
-        <v>0.94033754441373862</v>
+        <v>0.94038689301223843</v>
       </c>
     </row>
     <row r="43" spans="1:62" x14ac:dyDescent="0.3">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="E44" s="6">
         <f t="shared" si="0"/>
-        <v>213006</v>
+        <v>213008</v>
       </c>
       <c r="F44" s="5">
-        <v>265077</v>
+        <v>265079</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="1"/>
-        <v>0.84536000280641777</v>
+        <v>0.84536638102861594</v>
       </c>
       <c r="H44" s="3">
         <v>315037</v>
@@ -8228,14 +8228,14 @@
       </c>
       <c r="J44" s="6">
         <f t="shared" si="2"/>
-        <v>230418</v>
+        <v>230420</v>
       </c>
       <c r="K44" s="5">
-        <v>265478</v>
+        <v>265480</v>
       </c>
       <c r="L44" s="7">
         <f t="shared" si="3"/>
-        <v>0.84268831914981412</v>
+        <v>0.84269466761047118</v>
       </c>
       <c r="M44" s="2">
         <v>378050</v>
@@ -8245,14 +8245,14 @@
       </c>
       <c r="O44" s="6">
         <f t="shared" si="4"/>
-        <v>207280</v>
+        <v>207283</v>
       </c>
       <c r="P44" s="5">
-        <v>325452</v>
+        <v>325455</v>
       </c>
       <c r="Q44" s="7">
         <f t="shared" si="5"/>
-        <v>0.86087025525724115</v>
+        <v>0.86087819071551386</v>
       </c>
       <c r="R44" s="5">
         <v>322476</v>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="T44" s="6">
         <f t="shared" si="6"/>
-        <v>156951</v>
+        <v>156955</v>
       </c>
       <c r="U44" s="5">
-        <v>272180</v>
+        <v>272184</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="7"/>
-        <v>0.84403180391719068</v>
+        <v>0.84404420794105606</v>
       </c>
       <c r="W44" s="5">
         <v>327345</v>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>161070</v>
+        <v>161075</v>
       </c>
       <c r="Z44" s="5">
-        <v>275327</v>
+        <v>275332</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>0.84109120347034472</v>
+        <v>0.84110647787502479</v>
       </c>
       <c r="AB44" s="6">
         <v>393681</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="AD44" s="6">
         <f t="shared" si="10"/>
-        <v>175089</v>
+        <v>175093</v>
       </c>
       <c r="AE44" s="5">
-        <v>336169</v>
+        <v>336173</v>
       </c>
       <c r="AF44" s="7">
         <f t="shared" si="11"/>
-        <v>0.85391217762604743</v>
+        <v>0.8539223381367147</v>
       </c>
       <c r="AG44" s="5">
         <v>333199</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>145818</v>
+        <v>145822</v>
       </c>
       <c r="AJ44" s="5">
-        <v>279556</v>
+        <v>279560</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.8390061194661449</v>
+        <v>0.8390181243040945</v>
       </c>
       <c r="AL44" s="5">
         <v>336893</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>65075</v>
+        <v>65079</v>
       </c>
       <c r="AO44" s="5">
-        <v>284661</v>
+        <v>284665</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.8449596756240112</v>
+        <v>0.84497154883004399</v>
       </c>
       <c r="AQ44" s="6">
         <v>406157</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>177437</v>
+        <v>177441</v>
       </c>
       <c r="AT44" s="5">
-        <v>347540</v>
+        <v>347544</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.85567896158382106</v>
+        <v>0.8556888099921951</v>
       </c>
       <c r="AV44" s="5">
         <v>341214</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>140154</v>
+        <v>140158</v>
       </c>
       <c r="AY44" s="5">
-        <v>288746</v>
+        <v>288750</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.84623139730491714</v>
+        <v>0.8462431201533348</v>
       </c>
       <c r="BA44" s="5">
         <v>343859</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="BC44" s="6">
         <f t="shared" si="20"/>
-        <v>138775</v>
+        <v>138780</v>
       </c>
       <c r="BD44" s="5">
-        <v>292336</v>
+        <v>292341</v>
       </c>
       <c r="BE44" s="7">
         <f t="shared" si="21"/>
-        <v>0.85016242122497887</v>
+        <v>0.85017696206875493</v>
       </c>
       <c r="BF44" s="5">
         <v>410714</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="BH44" s="6">
         <f t="shared" si="24"/>
-        <v>190885</v>
+        <v>190894</v>
       </c>
       <c r="BI44" s="5">
-        <v>354684</v>
+        <v>354693</v>
       </c>
       <c r="BJ44" s="7">
         <f t="shared" si="25"/>
-        <v>0.86357903553324211</v>
+        <v>0.86360094859196423</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8423,14 +8423,14 @@
       </c>
       <c r="E45" s="6">
         <f t="shared" si="0"/>
-        <v>180640</v>
+        <v>180643</v>
       </c>
       <c r="F45" s="5">
-        <v>214268</v>
+        <v>214271</v>
       </c>
       <c r="G45" s="7">
         <f t="shared" si="1"/>
-        <v>0.90113763011250136</v>
+        <v>0.90115024708232572</v>
       </c>
       <c r="H45" s="3">
         <v>238690</v>
@@ -8440,14 +8440,14 @@
       </c>
       <c r="J45" s="6">
         <f t="shared" si="2"/>
-        <v>187330</v>
+        <v>187334</v>
       </c>
       <c r="K45" s="5">
-        <v>214933</v>
+        <v>214937</v>
       </c>
       <c r="L45" s="7">
         <f t="shared" si="3"/>
-        <v>0.90046922786878381</v>
+        <v>0.90048598600695462</v>
       </c>
       <c r="M45" s="2">
         <v>292586</v>
@@ -8457,14 +8457,14 @@
       </c>
       <c r="O45" s="6">
         <f t="shared" si="4"/>
-        <v>152349</v>
+        <v>152354</v>
       </c>
       <c r="P45" s="5">
-        <v>266639</v>
+        <v>266644</v>
       </c>
       <c r="Q45" s="7">
         <f t="shared" si="5"/>
-        <v>0.91131838160404122</v>
+        <v>0.9113354705966793</v>
       </c>
       <c r="R45" s="5">
         <v>242899</v>
@@ -8474,14 +8474,14 @@
       </c>
       <c r="T45" s="6">
         <f t="shared" si="6"/>
-        <v>110250</v>
+        <v>110253</v>
       </c>
       <c r="U45" s="5">
-        <v>218690</v>
+        <v>218693</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="7"/>
-        <v>0.9003330602431463</v>
+        <v>0.90034541105562393</v>
       </c>
       <c r="W45" s="5">
         <v>244806</v>
@@ -8491,14 +8491,14 @@
       </c>
       <c r="Y45" s="6">
         <f t="shared" si="8"/>
-        <v>113525</v>
+        <v>113528</v>
       </c>
       <c r="Z45" s="5">
-        <v>220496</v>
+        <v>220499</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="9"/>
-        <v>0.90069687834448497</v>
+        <v>0.9007091329460879</v>
       </c>
       <c r="AB45" s="6">
         <v>299772</v>
@@ -8508,14 +8508,14 @@
       </c>
       <c r="AD45" s="6">
         <f t="shared" si="10"/>
-        <v>124967</v>
+        <v>124970</v>
       </c>
       <c r="AE45" s="5">
-        <v>271297</v>
+        <v>271300</v>
       </c>
       <c r="AF45" s="7">
         <f t="shared" si="11"/>
-        <v>0.9050111418011022</v>
+        <v>0.90502114940688261</v>
       </c>
       <c r="AG45" s="5">
         <v>246243</v>
@@ -8525,14 +8525,14 @@
       </c>
       <c r="AI45" s="6">
         <f t="shared" si="12"/>
-        <v>101037</v>
+        <v>101042</v>
       </c>
       <c r="AJ45" s="5">
-        <v>222562</v>
+        <v>222567</v>
       </c>
       <c r="AK45" s="7">
         <f t="shared" si="13"/>
-        <v>0.90383076879342761</v>
+        <v>0.90385107393915765</v>
       </c>
       <c r="AL45" s="5">
         <v>247584</v>
@@ -8542,14 +8542,14 @@
       </c>
       <c r="AN45" s="6">
         <f t="shared" si="14"/>
-        <v>40244</v>
+        <v>40250</v>
       </c>
       <c r="AO45" s="5">
-        <v>225191</v>
+        <v>225197</v>
       </c>
       <c r="AP45" s="7">
         <f t="shared" si="15"/>
-        <v>0.90955392917151345</v>
+        <v>0.90957816337081554</v>
       </c>
       <c r="AQ45" s="6">
         <v>303759</v>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="AS45" s="6">
         <f t="shared" si="16"/>
-        <v>134132</v>
+        <v>134138</v>
       </c>
       <c r="AT45" s="5">
-        <v>277025</v>
+        <v>277031</v>
       </c>
       <c r="AU45" s="7">
         <f t="shared" si="17"/>
-        <v>0.91198943899604623</v>
+        <v>0.91200919149720672</v>
       </c>
       <c r="AV45" s="5">
         <v>248547</v>
@@ -8576,14 +8576,14 @@
       </c>
       <c r="AX45" s="6">
         <f t="shared" si="18"/>
-        <v>101068</v>
+        <v>101075</v>
       </c>
       <c r="AY45" s="5">
-        <v>227075</v>
+        <v>227082</v>
       </c>
       <c r="AZ45" s="7">
         <f t="shared" si="19"/>
-        <v>0.91360990074311899</v>
+        <v>0.91363806443046991</v>
       </c>
       <c r="BA45" s="5">
         <v>248925</v>
@@ -8593,14 +8593,14 @@
       </c>
       <c r="BC45" s="6">
         <f t="shared" si="20"/>
-        <v>98861</v>
+        <v>98868</v>
       </c>
       <c r="BD45" s="5">
-        <v>229241</v>
+        <v>229248</v>
       </c>
       <c r="BE45" s="7">
         <f t="shared" si="21"/>
-        <v>0.92092397308426233</v>
+        <v>0.92095209400421818</v>
       </c>
       <c r="BF45" s="5">
         <v>305535</v>
@@ -8610,14 +8610,14 @@
       </c>
       <c r="BH45" s="6">
         <f t="shared" si="24"/>
-        <v>145871</v>
+        <v>145880</v>
       </c>
       <c r="BI45" s="5">
-        <v>281584</v>
+        <v>281593</v>
       </c>
       <c r="BJ45" s="7">
         <f t="shared" si="25"/>
-        <v>0.92160963555730113</v>
+        <v>0.92163909208437655</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9059,15 +9059,15 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" si="0"/>
-        <v>5347874</v>
+        <v>5348017</v>
       </c>
       <c r="F48" s="9">
         <f>SUM(F10:F47)</f>
-        <v>6383604</v>
+        <v>6383747</v>
       </c>
       <c r="G48" s="8">
         <f t="shared" si="1"/>
-        <v>0.92079622657838933</v>
+        <v>0.92081685346257591</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9079,15 +9079,15 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="2"/>
-        <v>5526758</v>
+        <v>5526896</v>
       </c>
       <c r="K48" s="9">
         <f>SUM(K10:K47)</f>
-        <v>6398495</v>
+        <v>6398633</v>
       </c>
       <c r="L48" s="8">
         <f t="shared" si="3"/>
-        <v>0.92054901220561036</v>
+        <v>0.92056886621247991</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="O48" s="10">
         <f t="shared" si="4"/>
-        <v>5889752</v>
+        <v>5889949</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>10190690</v>
+        <v>10190887</v>
       </c>
       <c r="Q48" s="8">
         <f t="shared" si="5"/>
-        <v>0.93869311999268989</v>
+        <v>0.93871126621680612</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="T48" s="10">
         <f t="shared" si="6"/>
-        <v>3238659</v>
+        <v>3238796</v>
       </c>
       <c r="U48" s="9">
         <f>SUM(U10:U47)</f>
-        <v>6483716</v>
+        <v>6483853</v>
       </c>
       <c r="V48" s="8">
         <f t="shared" si="7"/>
-        <v>0.92383130363664079</v>
+        <v>0.92385082406113173</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="8"/>
-        <v>3177000</v>
+        <v>3177147</v>
       </c>
       <c r="Z48" s="9">
         <f>SUM(Z10:Z47)</f>
-        <v>6602621</v>
+        <v>6602768</v>
       </c>
       <c r="AA48" s="8">
         <f t="shared" si="9"/>
-        <v>0.92657181027974167</v>
+        <v>0.92659243936872182</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="AD48" s="10">
         <f t="shared" si="10"/>
-        <v>4486359</v>
+        <v>4486559</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>10491929</v>
+        <v>10492129</v>
       </c>
       <c r="AF48" s="8">
         <f t="shared" si="11"/>
-        <v>0.93835631630227156</v>
+        <v>0.93837420350521206</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="AI48" s="10">
         <f t="shared" si="12"/>
-        <v>2995767</v>
+        <v>2995913</v>
       </c>
       <c r="AJ48" s="9">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6600479</v>
+        <v>6600625</v>
       </c>
       <c r="AK48" s="8">
         <f t="shared" si="13"/>
-        <v>0.92608666980952059</v>
+        <v>0.92610715448249548</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AN48" s="10">
         <f t="shared" si="14"/>
-        <v>1213132</v>
+        <v>1213285</v>
       </c>
       <c r="AO48" s="9">
         <f>SUM(AO10:AO47)</f>
-        <v>6708301</v>
+        <v>6708454</v>
       </c>
       <c r="AP48" s="8">
         <f t="shared" si="15"/>
-        <v>0.93054154727356486</v>
+        <v>0.93056277065885018</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AS48" s="10">
         <f t="shared" si="16"/>
-        <v>4624399</v>
+        <v>4624621</v>
       </c>
       <c r="AT48" s="9">
         <f>SUM(AT10:AT47)</f>
-        <v>10740226</v>
+        <v>10740448</v>
       </c>
       <c r="AU48" s="8">
         <f t="shared" si="17"/>
-        <v>0.93972573710264506</v>
+        <v>0.9397451611923836</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AX48" s="10">
         <f t="shared" si="18"/>
-        <v>2609687</v>
+        <v>2609839</v>
       </c>
       <c r="AY48" s="9">
         <f>SUM(AY10:AY47)</f>
-        <v>6760759</v>
+        <v>6760911</v>
       </c>
       <c r="AZ48" s="8">
         <f t="shared" si="19"/>
-        <v>0.93344987260391954</v>
+        <v>0.93347085906130334</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="BC48" s="10">
         <f t="shared" si="20"/>
-        <v>2558699</v>
+        <v>2558861</v>
       </c>
       <c r="BD48" s="9">
         <f>SUM(BD10:BD47)</f>
-        <v>6870237</v>
+        <v>6870399</v>
       </c>
       <c r="BE48" s="8">
         <f t="shared" ref="BE48" si="26">BD48/BA48</f>
-        <v>0.93961724568980842</v>
+        <v>0.93963940183868677</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="BH48" s="10">
         <f t="shared" si="24"/>
-        <v>4818931</v>
+        <v>4819218</v>
       </c>
       <c r="BI48" s="9">
         <f>SUM(BI10:BI47)</f>
-        <v>10950596</v>
+        <v>10950883</v>
       </c>
       <c r="BJ48" s="8">
         <f t="shared" si="25"/>
-        <v>0.94148406094053694</v>
+        <v>0.94150873593772344</v>
       </c>
     </row>
   </sheetData>

--- a/gstdatabase/GSTR-1-2021-2022.xlsx
+++ b/gstdatabase/GSTR-1-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AA19BE-B423-4876-9872-E5559D341374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20391D09-2A22-4381-9045-C36B4D442838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,10 +179,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 31st May 2026</t>
+    <t>Data Considered upto 30th Jun 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st May 2026</t>
+    <t>Filing %age as on 30th Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -1816,14 +1816,14 @@
       </c>
       <c r="AX13" s="6">
         <f t="shared" si="18"/>
-        <v>3355</v>
+        <v>3356</v>
       </c>
       <c r="AY13" s="5">
-        <v>15465</v>
+        <v>15466</v>
       </c>
       <c r="AZ13" s="7">
         <f t="shared" si="19"/>
-        <v>0.98121946576993846</v>
+        <v>0.98128291352071573</v>
       </c>
       <c r="BA13" s="5">
         <v>15831</v>
@@ -1833,14 +1833,14 @@
       </c>
       <c r="BC13" s="6">
         <f t="shared" si="20"/>
-        <v>3222</v>
+        <v>3223</v>
       </c>
       <c r="BD13" s="5">
-        <v>15588</v>
+        <v>15589</v>
       </c>
       <c r="BE13" s="7">
         <f t="shared" si="21"/>
-        <v>0.984650369528141</v>
+        <v>0.9847135367317289</v>
       </c>
       <c r="BF13" s="5">
         <v>27469</v>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="O14" s="6">
         <f t="shared" si="4"/>
-        <v>84029</v>
+        <v>84030</v>
       </c>
       <c r="P14" s="5">
-        <v>131022</v>
+        <v>131023</v>
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="5"/>
-        <v>0.93915848326284856</v>
+        <v>0.93916565120779871</v>
       </c>
       <c r="R14" s="5">
         <v>78838</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>66583</v>
+        <v>66585</v>
       </c>
       <c r="AE14" s="5">
-        <v>135268</v>
+        <v>135270</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="11"/>
-        <v>0.93882650157549175</v>
+        <v>0.93884038255993119</v>
       </c>
       <c r="AG14" s="5">
         <v>79635</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="12"/>
-        <v>36584</v>
+        <v>36585</v>
       </c>
       <c r="AJ14" s="5">
-        <v>73458</v>
+        <v>73459</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="13"/>
-        <v>0.92243360331512525</v>
+        <v>0.92244616060777296</v>
       </c>
       <c r="AL14" s="5">
         <v>81274</v>
@@ -1994,14 +1994,14 @@
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="14"/>
-        <v>16026</v>
+        <v>16027</v>
       </c>
       <c r="AO14" s="5">
-        <v>75079</v>
+        <v>75080</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="15"/>
-        <v>0.92377636144400421</v>
+        <v>0.92378866550188254</v>
       </c>
       <c r="AQ14" s="6">
         <v>148266</v>
@@ -2011,14 +2011,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>68569</v>
+        <v>68571</v>
       </c>
       <c r="AT14" s="5">
-        <v>139142</v>
+        <v>139144</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.93846195351597805</v>
+        <v>0.93847544278526429</v>
       </c>
       <c r="AV14" s="5">
         <v>81291</v>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="AX14" s="6">
         <f t="shared" si="18"/>
-        <v>31969</v>
+        <v>31970</v>
       </c>
       <c r="AY14" s="5">
-        <v>75335</v>
+        <v>75336</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="19"/>
-        <v>0.92673235659544106</v>
+        <v>0.92674465808023032</v>
       </c>
       <c r="BA14" s="5">
         <v>82359</v>
@@ -2045,14 +2045,14 @@
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="20"/>
-        <v>31697</v>
+        <v>31699</v>
       </c>
       <c r="BD14" s="5">
-        <v>76620</v>
+        <v>76622</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="21"/>
-        <v>0.93031726951517135</v>
+        <v>0.93034155344285385</v>
       </c>
       <c r="BF14" s="5">
         <v>151377</v>
@@ -2062,14 +2062,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>71657</v>
+        <v>71660</v>
       </c>
       <c r="BI14" s="5">
-        <v>141676</v>
+        <v>141679</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.93591496726715417</v>
+        <v>0.93593478533727048</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2223,14 +2223,14 @@
       </c>
       <c r="AS15" s="6">
         <f t="shared" si="16"/>
-        <v>147626</v>
+        <v>147627</v>
       </c>
       <c r="AT15" s="5">
-        <v>439655</v>
+        <v>439656</v>
       </c>
       <c r="AU15" s="7">
         <f t="shared" si="17"/>
-        <v>0.94699556070589297</v>
+        <v>0.94699771465742477</v>
       </c>
       <c r="AV15" s="5">
         <v>264802</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>296136</v>
+        <v>296138</v>
       </c>
       <c r="P16" s="5">
-        <v>672237</v>
+        <v>672239</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.93524852562470528</v>
+        <v>0.93525130812113322</v>
       </c>
       <c r="R16" s="5">
         <v>403668</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="T16" s="6">
         <f t="shared" si="6"/>
-        <v>139501</v>
+        <v>139503</v>
       </c>
       <c r="U16" s="5">
-        <v>369202</v>
+        <v>369204</v>
       </c>
       <c r="V16" s="7">
         <f t="shared" si="7"/>
-        <v>0.91461795336761897</v>
+        <v>0.91462290793424295</v>
       </c>
       <c r="W16" s="5">
         <v>406853</v>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>131964</v>
+        <v>131967</v>
       </c>
       <c r="Z16" s="5">
-        <v>376714</v>
+        <v>376717</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.9259216473763251</v>
+        <v>0.92592902104691377</v>
       </c>
       <c r="AB16" s="6">
         <v>722282</v>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="10"/>
-        <v>196118</v>
+        <v>196122</v>
       </c>
       <c r="AE16" s="5">
-        <v>689378</v>
+        <v>689382</v>
       </c>
       <c r="AF16" s="7">
         <f t="shared" si="11"/>
-        <v>0.95444438598774439</v>
+        <v>0.95444992399090656</v>
       </c>
       <c r="AG16" s="5">
         <v>397671</v>
@@ -2401,14 +2401,14 @@
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="12"/>
-        <v>116372</v>
+        <v>116375</v>
       </c>
       <c r="AJ16" s="5">
-        <v>374282</v>
+        <v>374285</v>
       </c>
       <c r="AK16" s="7">
         <f t="shared" si="13"/>
-        <v>0.94118504995335339</v>
+        <v>0.94119259387785381</v>
       </c>
       <c r="AL16" s="5">
         <v>400740</v>
@@ -2418,14 +2418,14 @@
       </c>
       <c r="AN16" s="6">
         <f t="shared" si="14"/>
-        <v>48226</v>
+        <v>48229</v>
       </c>
       <c r="AO16" s="5">
-        <v>380506</v>
+        <v>380509</v>
       </c>
       <c r="AP16" s="7">
         <f t="shared" si="15"/>
-        <v>0.94950840944253134</v>
+        <v>0.94951589559315264</v>
       </c>
       <c r="AQ16" s="6">
         <v>730568</v>
@@ -2435,14 +2435,14 @@
       </c>
       <c r="AS16" s="6">
         <f t="shared" si="16"/>
-        <v>198854</v>
+        <v>198857</v>
       </c>
       <c r="AT16" s="5">
-        <v>699691</v>
+        <v>699694</v>
       </c>
       <c r="AU16" s="7">
         <f t="shared" si="17"/>
-        <v>0.95773562488365216</v>
+        <v>0.95773973127758127</v>
       </c>
       <c r="AV16" s="5">
         <v>402711</v>
@@ -2452,14 +2452,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="AY16" s="5">
-        <v>378361</v>
+        <v>378363</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.93953480287352464</v>
+        <v>0.93953976921415105</v>
       </c>
       <c r="BA16" s="5">
         <v>402569</v>
@@ -2469,14 +2469,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>94065</v>
+        <v>94067</v>
       </c>
       <c r="BD16" s="5">
-        <v>384274</v>
+        <v>384276</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.95455437452958369</v>
+        <v>0.95455934262201014</v>
       </c>
       <c r="BF16" s="5">
         <v>736680</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>196444</v>
+        <v>196447</v>
       </c>
       <c r="BI16" s="5">
-        <v>706643</v>
+        <v>706646</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.95922652983656409</v>
+        <v>0.95923060216104683</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>225677</v>
+        <v>225678</v>
       </c>
       <c r="F17" s="5">
-        <v>255293</v>
+        <v>255294</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.96730106887236045</v>
+        <v>0.96730485785626863</v>
       </c>
       <c r="H17" s="3">
         <v>264168</v>
@@ -2545,14 +2545,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>323446</v>
+        <v>323448</v>
       </c>
       <c r="P17" s="5">
-        <v>577393</v>
+        <v>577395</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.97661441868410859</v>
+        <v>0.97661780152532307</v>
       </c>
       <c r="R17" s="5">
         <v>261213</v>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>119506</v>
+        <v>119509</v>
       </c>
       <c r="U17" s="5">
-        <v>253300</v>
+        <v>253303</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.9697067144437681</v>
+        <v>0.96971819932392334</v>
       </c>
       <c r="W17" s="5">
         <v>269820</v>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>114739</v>
+        <v>114743</v>
       </c>
       <c r="Z17" s="5">
-        <v>262468</v>
+        <v>262472</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.97275220517381955</v>
+        <v>0.97276702987176633</v>
       </c>
       <c r="AB17" s="6">
         <v>613565</v>
@@ -2596,14 +2596,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>238271</v>
+        <v>238276</v>
       </c>
       <c r="AE17" s="5">
-        <v>597222</v>
+        <v>597227</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.97336386527914731</v>
+        <v>0.97337201437500509</v>
       </c>
       <c r="AG17" s="5">
         <v>263808</v>
@@ -2613,14 +2613,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>102907</v>
+        <v>102911</v>
       </c>
       <c r="AJ17" s="5">
-        <v>255219</v>
+        <v>255223</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.96744223071324598</v>
+        <v>0.96745739325570113</v>
       </c>
       <c r="AL17" s="5">
         <v>270212</v>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="AO17" s="5">
-        <v>262870</v>
+        <v>262873</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.97282874187674861</v>
+        <v>0.97283984427042469</v>
       </c>
       <c r="AQ17" s="6">
         <v>633137</v>
@@ -2647,14 +2647,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>253899</v>
+        <v>253905</v>
       </c>
       <c r="AT17" s="5">
-        <v>612902</v>
+        <v>612908</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.96804009242865285</v>
+        <v>0.96804956905061623</v>
       </c>
       <c r="AV17" s="5">
         <v>270996</v>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>84227</v>
+        <v>84230</v>
       </c>
       <c r="AY17" s="5">
-        <v>261434</v>
+        <v>261437</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.96471534635197564</v>
+        <v>0.96472641662607561</v>
       </c>
       <c r="BA17" s="5">
         <v>277009</v>
@@ -2681,14 +2681,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>81156</v>
+        <v>81160</v>
       </c>
       <c r="BD17" s="5">
-        <v>270951</v>
+        <v>270955</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.97813067445462065</v>
+        <v>0.97814511441866514</v>
       </c>
       <c r="BF17" s="5">
         <v>651560</v>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>264488</v>
+        <v>264498</v>
       </c>
       <c r="BI17" s="5">
-        <v>629100</v>
+        <v>629110</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.96552888452329788</v>
+        <v>0.96554423230400888</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>650570</v>
+        <v>650573</v>
       </c>
       <c r="F18" s="5">
-        <v>716483</v>
+        <v>716486</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="1"/>
-        <v>0.93232087693592924</v>
+        <v>0.93232478067493041</v>
       </c>
       <c r="H18" s="3">
         <v>766983</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="J18" s="6">
         <f t="shared" si="2"/>
-        <v>624799</v>
+        <v>624802</v>
       </c>
       <c r="K18" s="5">
-        <v>716168</v>
+        <v>716171</v>
       </c>
       <c r="L18" s="7">
         <f t="shared" si="3"/>
-        <v>0.93374690182181352</v>
+        <v>0.93375081325140197</v>
       </c>
       <c r="M18" s="2">
         <v>1193073</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="O18" s="6">
         <f t="shared" si="4"/>
-        <v>736273</v>
+        <v>736277</v>
       </c>
       <c r="P18" s="5">
-        <v>1137372</v>
+        <v>1137376</v>
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="5"/>
-        <v>0.95331299928839219</v>
+        <v>0.95331635197510967</v>
       </c>
       <c r="R18" s="5">
         <v>775495</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="T18" s="6">
         <f t="shared" si="6"/>
-        <v>411976</v>
+        <v>411978</v>
       </c>
       <c r="U18" s="5">
-        <v>732690</v>
+        <v>732692</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="7"/>
-        <v>0.9448029967955951</v>
+        <v>0.94480557579352542</v>
       </c>
       <c r="W18" s="5">
         <v>789854</v>
@@ -2791,14 +2791,14 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="8"/>
-        <v>390050</v>
+        <v>390052</v>
       </c>
       <c r="Z18" s="5">
-        <v>748176</v>
+        <v>748178</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="9"/>
-        <v>0.94723328615161795</v>
+        <v>0.94723581826514769</v>
       </c>
       <c r="AB18" s="6">
         <v>1245422</v>
@@ -2808,14 +2808,14 @@
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>569093</v>
+        <v>569097</v>
       </c>
       <c r="AE18" s="5">
-        <v>1175167</v>
+        <v>1175171</v>
       </c>
       <c r="AF18" s="7">
         <f t="shared" si="11"/>
-        <v>0.94358940182524476</v>
+        <v>0.94359261358800472</v>
       </c>
       <c r="AG18" s="5">
         <v>794310</v>
@@ -2825,14 +2825,14 @@
       </c>
       <c r="AI18" s="6">
         <f t="shared" si="12"/>
-        <v>388018</v>
+        <v>388020</v>
       </c>
       <c r="AJ18" s="5">
-        <v>750377</v>
+        <v>750379</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="13"/>
-        <v>0.94469036018682884</v>
+        <v>0.94469287809545388</v>
       </c>
       <c r="AL18" s="5">
         <v>807429</v>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>142063</v>
+        <v>142065</v>
       </c>
       <c r="AO18" s="5">
-        <v>765803</v>
+        <v>765805</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="15"/>
-        <v>0.94844624109364417</v>
+        <v>0.94844871809162168</v>
       </c>
       <c r="AQ18" s="6">
         <v>1285494</v>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AS18" s="6">
         <f t="shared" si="16"/>
-        <v>603846</v>
+        <v>603852</v>
       </c>
       <c r="AT18" s="5">
-        <v>1212036</v>
+        <v>1212042</v>
       </c>
       <c r="AU18" s="7">
         <f t="shared" si="17"/>
-        <v>0.94285620936387105</v>
+        <v>0.94286087683023023</v>
       </c>
       <c r="AV18" s="5">
         <v>820095</v>
@@ -2876,14 +2876,14 @@
       </c>
       <c r="AX18" s="6">
         <f t="shared" si="18"/>
-        <v>349468</v>
+        <v>349471</v>
       </c>
       <c r="AY18" s="5">
-        <v>773536</v>
+        <v>773539</v>
       </c>
       <c r="AZ18" s="7">
         <f t="shared" si="19"/>
-        <v>0.94322730903127072</v>
+        <v>0.94323096714405041</v>
       </c>
       <c r="BA18" s="5">
         <v>829968</v>
@@ -2893,14 +2893,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>340736</v>
+        <v>340739</v>
       </c>
       <c r="BD18" s="5">
-        <v>785689</v>
+        <v>785692</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.94664975035182075</v>
+        <v>0.94665336494901009</v>
       </c>
       <c r="BF18" s="5">
         <v>1319511</v>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>631893</v>
+        <v>631897</v>
       </c>
       <c r="BI18" s="5">
-        <v>1235567</v>
+        <v>1235571</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.93638249321150036</v>
+        <v>0.93638552463753622</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="E19" s="6">
         <f t="shared" si="0"/>
-        <v>188019</v>
+        <v>188020</v>
       </c>
       <c r="F19" s="5">
-        <v>203913</v>
+        <v>203914</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="1"/>
-        <v>0.8307585127966951</v>
+        <v>0.83076258687982274</v>
       </c>
       <c r="H19" s="3">
         <v>247965</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="J19" s="6">
         <f t="shared" si="2"/>
-        <v>185924</v>
+        <v>185925</v>
       </c>
       <c r="K19" s="5">
-        <v>204607</v>
+        <v>204608</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="3"/>
-        <v>0.82514467767628497</v>
+        <v>0.82514871050349847</v>
       </c>
       <c r="M19" s="2">
         <v>387570</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="O19" s="6">
         <f t="shared" si="4"/>
-        <v>259994</v>
+        <v>259996</v>
       </c>
       <c r="P19" s="5">
-        <v>337559</v>
+        <v>337561</v>
       </c>
       <c r="Q19" s="7">
         <f t="shared" si="5"/>
-        <v>0.87096266480893769</v>
+        <v>0.87096782516706661</v>
       </c>
       <c r="R19" s="5">
         <v>254467</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="T19" s="6">
         <f t="shared" si="6"/>
-        <v>158284</v>
+        <v>158287</v>
       </c>
       <c r="U19" s="5">
-        <v>216796</v>
+        <v>216799</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="7"/>
-        <v>0.85196115802834949</v>
+        <v>0.8519729473762806</v>
       </c>
       <c r="W19" s="5">
         <v>263449</v>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>162772</v>
+        <v>162774</v>
       </c>
       <c r="Z19" s="5">
-        <v>229837</v>
+        <v>229839</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="9"/>
-        <v>0.87241553393635962</v>
+        <v>0.8724231255385293</v>
       </c>
       <c r="AB19" s="6">
         <v>418128</v>
@@ -3020,14 +3020,14 @@
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="10"/>
-        <v>231553</v>
+        <v>231557</v>
       </c>
       <c r="AE19" s="5">
-        <v>372441</v>
+        <v>372445</v>
       </c>
       <c r="AF19" s="7">
         <f t="shared" si="11"/>
-        <v>0.89073441625530936</v>
+        <v>0.89074398270386101</v>
       </c>
       <c r="AG19" s="5">
         <v>259213</v>
@@ -3037,14 +3037,14 @@
       </c>
       <c r="AI19" s="6">
         <f t="shared" si="12"/>
-        <v>162936</v>
+        <v>162938</v>
       </c>
       <c r="AJ19" s="5">
-        <v>221042</v>
+        <v>221044</v>
       </c>
       <c r="AK19" s="7">
         <f t="shared" si="13"/>
-        <v>0.8527427250948062</v>
+        <v>0.85275044075721507</v>
       </c>
       <c r="AL19" s="5">
         <v>262802</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="AN19" s="6">
         <f t="shared" si="14"/>
-        <v>63214</v>
+        <v>63217</v>
       </c>
       <c r="AO19" s="5">
-        <v>224988</v>
+        <v>224991</v>
       </c>
       <c r="AP19" s="7">
         <f t="shared" si="15"/>
-        <v>0.85611220614759398</v>
+        <v>0.85612362158583266</v>
       </c>
       <c r="AQ19" s="6">
         <v>437396</v>
@@ -3071,14 +3071,14 @@
       </c>
       <c r="AS19" s="6">
         <f t="shared" si="16"/>
-        <v>254084</v>
+        <v>254088</v>
       </c>
       <c r="AT19" s="5">
-        <v>381167</v>
+        <v>381171</v>
       </c>
       <c r="AU19" s="7">
         <f t="shared" si="17"/>
-        <v>0.87144601230921181</v>
+        <v>0.87145515734025913</v>
       </c>
       <c r="AV19" s="5">
         <v>265429</v>
@@ -3088,14 +3088,14 @@
       </c>
       <c r="AX19" s="6">
         <f t="shared" si="18"/>
-        <v>145062</v>
+        <v>145065</v>
       </c>
       <c r="AY19" s="5">
-        <v>226866</v>
+        <v>226869</v>
       </c>
       <c r="AZ19" s="7">
         <f t="shared" si="19"/>
-        <v>0.85471444341047886</v>
+        <v>0.85472574586800987</v>
       </c>
       <c r="BA19" s="5">
         <v>272122</v>
@@ -3105,14 +3105,14 @@
       </c>
       <c r="BC19" s="6">
         <f t="shared" si="20"/>
-        <v>142882</v>
+        <v>142887</v>
       </c>
       <c r="BD19" s="5">
-        <v>232932</v>
+        <v>232937</v>
       </c>
       <c r="BE19" s="7">
         <f t="shared" si="21"/>
-        <v>0.85598371318746735</v>
+        <v>0.85600208729907912</v>
       </c>
       <c r="BF19" s="5">
         <v>456786</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="BH19" s="6">
         <f t="shared" si="22"/>
-        <v>273297</v>
+        <v>273306</v>
       </c>
       <c r="BI19" s="5">
-        <v>393745</v>
+        <v>393754</v>
       </c>
       <c r="BJ19" s="7">
         <f t="shared" si="23"/>
-        <v>0.86199007850503295</v>
+        <v>0.86200978138559414</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3147,14 +3147,14 @@
       </c>
       <c r="E20" s="6">
         <f t="shared" si="0"/>
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="F20" s="5">
-        <v>4633</v>
+        <v>4634</v>
       </c>
       <c r="G20" s="7">
         <f t="shared" si="1"/>
-        <v>0.84559226136156229</v>
+        <v>0.84577477641905452</v>
       </c>
       <c r="H20" s="3">
         <v>5462</v>
@@ -3164,14 +3164,14 @@
       </c>
       <c r="J20" s="6">
         <f t="shared" si="2"/>
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="K20" s="5">
-        <v>4615</v>
+        <v>4616</v>
       </c>
       <c r="L20" s="7">
         <f t="shared" si="3"/>
-        <v>0.84492859758330285</v>
+        <v>0.84511168070303921</v>
       </c>
       <c r="M20" s="2">
         <v>8047</v>
@@ -3181,14 +3181,14 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="4"/>
-        <v>5343</v>
+        <v>5344</v>
       </c>
       <c r="P20" s="5">
-        <v>7030</v>
+        <v>7031</v>
       </c>
       <c r="Q20" s="7">
         <f t="shared" si="5"/>
-        <v>0.8736174972039269</v>
+        <v>0.87374176711818063</v>
       </c>
       <c r="R20" s="5">
         <v>5619</v>
@@ -3198,14 +3198,14 @@
       </c>
       <c r="T20" s="6">
         <f t="shared" si="6"/>
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="U20" s="5">
-        <v>4647</v>
+        <v>4648</v>
       </c>
       <c r="V20" s="7">
         <f t="shared" si="7"/>
-        <v>0.82701548318206086</v>
+        <v>0.82719345079195583</v>
       </c>
       <c r="W20" s="5">
         <v>5711</v>
@@ -3215,14 +3215,14 @@
       </c>
       <c r="Y20" s="6">
         <f t="shared" si="8"/>
-        <v>2783</v>
+        <v>2784</v>
       </c>
       <c r="Z20" s="5">
-        <v>4688</v>
+        <v>4689</v>
       </c>
       <c r="AA20" s="7">
         <f t="shared" si="9"/>
-        <v>0.82087200140080552</v>
+        <v>0.82104710208369813</v>
       </c>
       <c r="AB20" s="6">
         <v>8314</v>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AI20" s="6">
         <f t="shared" si="12"/>
-        <v>2991</v>
+        <v>2992</v>
       </c>
       <c r="AJ20" s="5">
-        <v>4682</v>
+        <v>4683</v>
       </c>
       <c r="AK20" s="7">
         <f t="shared" si="13"/>
-        <v>0.82010860045542122</v>
+        <v>0.82028376248029422</v>
       </c>
       <c r="AL20" s="5">
         <v>5805</v>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AN20" s="6">
         <f t="shared" si="14"/>
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="AO20" s="5">
-        <v>4853</v>
+        <v>4854</v>
       </c>
       <c r="AP20" s="7">
         <f t="shared" si="15"/>
-        <v>0.83600344530577086</v>
+        <v>0.83617571059431528</v>
       </c>
       <c r="AQ20" s="6">
         <v>8632</v>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="AS20" s="6">
         <f t="shared" si="16"/>
-        <v>4691</v>
+        <v>4692</v>
       </c>
       <c r="AT20" s="5">
-        <v>7630</v>
+        <v>7631</v>
       </c>
       <c r="AU20" s="7">
         <f t="shared" si="17"/>
-        <v>0.88392029657089899</v>
+        <v>0.88403614457831325</v>
       </c>
       <c r="AV20" s="5">
         <v>5837</v>
@@ -3300,14 +3300,14 @@
       </c>
       <c r="AX20" s="6">
         <f t="shared" si="18"/>
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="AY20" s="5">
-        <v>4830</v>
+        <v>4831</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="19"/>
-        <v>0.8274798697961282</v>
+        <v>0.82765119068014392</v>
       </c>
       <c r="BA20" s="5">
         <v>5912</v>
@@ -3317,14 +3317,14 @@
       </c>
       <c r="BC20" s="6">
         <f t="shared" si="20"/>
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="BD20" s="5">
-        <v>4957</v>
+        <v>4958</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="21"/>
-        <v>0.83846414073071718</v>
+        <v>0.83863328822733418</v>
       </c>
       <c r="BF20" s="5">
         <v>8941</v>
@@ -3334,14 +3334,14 @@
       </c>
       <c r="BH20" s="6">
         <f t="shared" si="22"/>
-        <v>5010</v>
+        <v>5011</v>
       </c>
       <c r="BI20" s="5">
-        <v>7876</v>
+        <v>7877</v>
       </c>
       <c r="BJ20" s="7">
         <f t="shared" si="23"/>
-        <v>0.88088580695671626</v>
+        <v>0.88099765126943297</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3410,14 +3410,14 @@
       </c>
       <c r="T21" s="6">
         <f t="shared" si="6"/>
-        <v>5830</v>
+        <v>5831</v>
       </c>
       <c r="U21" s="5">
-        <v>7502</v>
+        <v>7503</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="7"/>
-        <v>0.73283188434111557</v>
+        <v>0.7329295692097294</v>
       </c>
       <c r="W21" s="5">
         <v>10162</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>5828</v>
+        <v>5829</v>
       </c>
       <c r="Z21" s="5">
-        <v>7608</v>
+        <v>7609</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.74867152135406412</v>
+        <v>0.74876992717968904</v>
       </c>
       <c r="AB21" s="6">
         <v>13196</v>
@@ -3444,14 +3444,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>7180</v>
+        <v>7181</v>
       </c>
       <c r="AE21" s="5">
-        <v>10280</v>
+        <v>10281</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.77902394665050012</v>
+        <v>0.7790997271900576</v>
       </c>
       <c r="AG21" s="5">
         <v>10295</v>
@@ -3461,14 +3461,14 @@
       </c>
       <c r="AI21" s="6">
         <f t="shared" si="12"/>
-        <v>5355</v>
+        <v>5356</v>
       </c>
       <c r="AJ21" s="5">
-        <v>7690</v>
+        <v>7691</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="13"/>
-        <v>0.74696454589606609</v>
+        <v>0.74706168042739196</v>
       </c>
       <c r="AL21" s="5">
         <v>10459</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="AO21" s="5">
-        <v>7784</v>
+        <v>7785</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.74423941103355962</v>
+        <v>0.74433502246868721</v>
       </c>
       <c r="AQ21" s="6">
         <v>13595</v>
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS21" s="6">
         <f t="shared" si="16"/>
-        <v>7429</v>
+        <v>7430</v>
       </c>
       <c r="AT21" s="5">
-        <v>10592</v>
+        <v>10593</v>
       </c>
       <c r="AU21" s="7">
         <f t="shared" si="17"/>
-        <v>0.77910996689959544</v>
+        <v>0.77918352335417429</v>
       </c>
       <c r="AV21" s="5">
         <v>10391</v>
@@ -3512,14 +3512,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>5187</v>
+        <v>5188</v>
       </c>
       <c r="AY21" s="5">
-        <v>7908</v>
+        <v>7909</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.76104321047059953</v>
+        <v>0.76113944759888363</v>
       </c>
       <c r="BA21" s="5">
         <v>10525</v>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="BC21" s="6">
         <f t="shared" si="20"/>
-        <v>5273</v>
+        <v>5274</v>
       </c>
       <c r="BD21" s="5">
-        <v>8048</v>
+        <v>8049</v>
       </c>
       <c r="BE21" s="7">
         <f t="shared" si="21"/>
-        <v>0.76465558194774352</v>
+        <v>0.76475059382422805</v>
       </c>
       <c r="BF21" s="5">
         <v>13618</v>
@@ -3546,14 +3546,14 @@
       </c>
       <c r="BH21" s="6">
         <f t="shared" si="22"/>
-        <v>8334</v>
+        <v>8335</v>
       </c>
       <c r="BI21" s="5">
-        <v>10967</v>
+        <v>10968</v>
       </c>
       <c r="BJ21" s="7">
         <f t="shared" si="23"/>
-        <v>0.80533117932148623</v>
+        <v>0.80540461154354526</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3571,14 +3571,14 @@
       </c>
       <c r="E22" s="6">
         <f t="shared" si="0"/>
-        <v>4325</v>
+        <v>4326</v>
       </c>
       <c r="F22" s="5">
-        <v>4987</v>
+        <v>4988</v>
       </c>
       <c r="G22" s="7">
         <f t="shared" si="1"/>
-        <v>0.84225637561222766</v>
+        <v>0.84242526600236445</v>
       </c>
       <c r="H22" s="3">
         <v>5940</v>
@@ -3588,14 +3588,14 @@
       </c>
       <c r="J22" s="6">
         <f t="shared" si="2"/>
-        <v>4477</v>
+        <v>4478</v>
       </c>
       <c r="K22" s="5">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" si="3"/>
-        <v>0.84124579124579124</v>
+        <v>0.84141414141414139</v>
       </c>
       <c r="M22" s="2">
         <v>7004</v>
@@ -3605,14 +3605,14 @@
       </c>
       <c r="O22" s="6">
         <f t="shared" si="4"/>
-        <v>4754</v>
+        <v>4755</v>
       </c>
       <c r="P22" s="5">
-        <v>5949</v>
+        <v>5950</v>
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="5"/>
-        <v>0.84937178754997145</v>
+        <v>0.84951456310679607</v>
       </c>
       <c r="R22" s="5">
         <v>5966</v>
@@ -3622,14 +3622,14 @@
       </c>
       <c r="T22" s="6">
         <f t="shared" si="6"/>
-        <v>3624</v>
+        <v>3625</v>
       </c>
       <c r="U22" s="5">
-        <v>4989</v>
+        <v>4990</v>
       </c>
       <c r="V22" s="7">
         <f t="shared" si="7"/>
-        <v>0.83623868588669126</v>
+        <v>0.83640630238015423</v>
       </c>
       <c r="W22" s="5">
         <v>5920</v>
@@ -3639,14 +3639,14 @@
       </c>
       <c r="Y22" s="6">
         <f t="shared" si="8"/>
-        <v>3531</v>
+        <v>3532</v>
       </c>
       <c r="Z22" s="5">
-        <v>5048</v>
+        <v>5049</v>
       </c>
       <c r="AA22" s="7">
         <f t="shared" si="9"/>
-        <v>0.85270270270270265</v>
+        <v>0.85287162162162167</v>
       </c>
       <c r="AB22" s="6">
         <v>7073</v>
@@ -3656,14 +3656,14 @@
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="10"/>
-        <v>4011</v>
+        <v>4012</v>
       </c>
       <c r="AE22" s="5">
-        <v>6138</v>
+        <v>6139</v>
       </c>
       <c r="AF22" s="7">
         <f t="shared" si="11"/>
-        <v>0.86780715396578534</v>
+        <v>0.86794853668881666</v>
       </c>
       <c r="AG22" s="5">
         <v>5998</v>
@@ -3673,14 +3673,14 @@
       </c>
       <c r="AI22" s="6">
         <f t="shared" si="12"/>
-        <v>3339</v>
+        <v>3340</v>
       </c>
       <c r="AJ22" s="5">
-        <v>5169</v>
+        <v>5170</v>
       </c>
       <c r="AK22" s="7">
         <f t="shared" si="13"/>
-        <v>0.86178726242080694</v>
+        <v>0.86195398466155382</v>
       </c>
       <c r="AL22" s="5">
         <v>5988</v>
@@ -3690,14 +3690,14 @@
       </c>
       <c r="AN22" s="6">
         <f t="shared" si="14"/>
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="AO22" s="5">
-        <v>5259</v>
+        <v>5260</v>
       </c>
       <c r="AP22" s="7">
         <f t="shared" si="15"/>
-        <v>0.87825651302605212</v>
+        <v>0.8784235136940548</v>
       </c>
       <c r="AQ22" s="6">
         <v>7036</v>
@@ -3707,14 +3707,14 @@
       </c>
       <c r="AS22" s="6">
         <f t="shared" si="16"/>
-        <v>4194</v>
+        <v>4195</v>
       </c>
       <c r="AT22" s="5">
-        <v>6316</v>
+        <v>6317</v>
       </c>
       <c r="AU22" s="7">
         <f t="shared" si="17"/>
-        <v>0.89766913018760663</v>
+        <v>0.89781125639567938</v>
       </c>
       <c r="AV22" s="5">
         <v>5943</v>
@@ -3724,14 +3724,14 @@
       </c>
       <c r="AX22" s="6">
         <f t="shared" si="18"/>
-        <v>3450</v>
+        <v>3451</v>
       </c>
       <c r="AY22" s="5">
-        <v>5319</v>
+        <v>5320</v>
       </c>
       <c r="AZ22" s="7">
         <f t="shared" si="19"/>
-        <v>0.89500252397778901</v>
+        <v>0.89517078916372206</v>
       </c>
       <c r="BA22" s="5">
         <v>5997</v>
@@ -3741,14 +3741,14 @@
       </c>
       <c r="BC22" s="6">
         <f t="shared" si="20"/>
-        <v>3444</v>
+        <v>3445</v>
       </c>
       <c r="BD22" s="5">
-        <v>5368</v>
+        <v>5369</v>
       </c>
       <c r="BE22" s="7">
         <f t="shared" si="21"/>
-        <v>0.89511422377855598</v>
+        <v>0.89528097382024341</v>
       </c>
       <c r="BF22" s="5">
         <v>7214</v>
@@ -3758,14 +3758,14 @@
       </c>
       <c r="BH22" s="6">
         <f t="shared" si="22"/>
-        <v>4616</v>
+        <v>4617</v>
       </c>
       <c r="BI22" s="5">
-        <v>6509</v>
+        <v>6510</v>
       </c>
       <c r="BJ22" s="7">
         <f t="shared" si="23"/>
-        <v>0.90227335736068759</v>
+        <v>0.90241197671194895</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -4419,14 +4419,14 @@
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>10110</v>
+        <v>10112</v>
       </c>
       <c r="F26" s="5">
-        <v>11373</v>
+        <v>11375</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>0.68669242845067024</v>
+        <v>0.68681318681318682</v>
       </c>
       <c r="H26" s="3">
         <v>16580</v>
@@ -4436,14 +4436,14 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>10068</v>
+        <v>10070</v>
       </c>
       <c r="K26" s="5">
-        <v>11294</v>
+        <v>11296</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>0.68118214716525938</v>
+        <v>0.68130277442702047</v>
       </c>
       <c r="M26" s="2">
         <v>25396</v>
@@ -4453,14 +4453,14 @@
       </c>
       <c r="O26" s="6">
         <f t="shared" si="4"/>
-        <v>14651</v>
+        <v>14654</v>
       </c>
       <c r="P26" s="5">
-        <v>18717</v>
+        <v>18720</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="5"/>
-        <v>0.73700582768939993</v>
+        <v>0.7371239565285872</v>
       </c>
       <c r="R26" s="5">
         <v>16475</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="U26" s="5">
-        <v>11297</v>
+        <v>11299</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.68570561456752654</v>
+        <v>0.68582701062215479</v>
       </c>
       <c r="W26" s="5">
         <v>16675</v>
@@ -4487,14 +4487,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>7986</v>
+        <v>7988</v>
       </c>
       <c r="Z26" s="5">
-        <v>11450</v>
+        <v>11452</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.68665667166416788</v>
+        <v>0.68677661169415294</v>
       </c>
       <c r="AB26" s="6">
         <v>25656</v>
@@ -4504,14 +4504,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>12763</v>
+        <v>12766</v>
       </c>
       <c r="AE26" s="5">
-        <v>19353</v>
+        <v>19356</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.7543264733395697</v>
+        <v>0.75444340505144991</v>
       </c>
       <c r="AG26" s="5">
         <v>15844</v>
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>7383</v>
+        <v>7385</v>
       </c>
       <c r="AJ26" s="5">
-        <v>11193</v>
+        <v>11195</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.70645039131532439</v>
+        <v>0.70657662206513505</v>
       </c>
       <c r="AL26" s="5">
         <v>16081</v>
@@ -4538,14 +4538,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>3582</v>
+        <v>3584</v>
       </c>
       <c r="AO26" s="5">
-        <v>11422</v>
+        <v>11424</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.7102792114918226</v>
+        <v>0.71040358186679931</v>
       </c>
       <c r="AQ26" s="6">
         <v>26317</v>
@@ -4555,14 +4555,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>13376</v>
+        <v>13379</v>
       </c>
       <c r="AT26" s="5">
-        <v>20102</v>
+        <v>20105</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.76384086332028722</v>
+        <v>0.76395485807652852</v>
       </c>
       <c r="AV26" s="5">
         <v>15987</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>7191</v>
+        <v>7194</v>
       </c>
       <c r="AY26" s="5">
-        <v>11379</v>
+        <v>11382</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.71176580972039782</v>
+        <v>0.7119534621880278</v>
       </c>
       <c r="BA26" s="5">
         <v>16133</v>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>7245</v>
+        <v>7246</v>
       </c>
       <c r="BD26" s="5">
-        <v>11567</v>
+        <v>11568</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.71697762350461791</v>
+        <v>0.71703960825636892</v>
       </c>
       <c r="BF26" s="5">
         <v>26642</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>13810</v>
+        <v>13813</v>
       </c>
       <c r="BI26" s="5">
-        <v>20664</v>
+        <v>20667</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.77561744613767736</v>
+        <v>0.77573005029652431</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>85609</v>
+        <v>85615</v>
       </c>
       <c r="F27" s="5">
-        <v>97156</v>
+        <v>97162</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>0.86102962680680983</v>
+        <v>0.86108280085432964</v>
       </c>
       <c r="H27" s="3">
         <v>111842</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="J27" s="6">
         <f t="shared" si="2"/>
-        <v>89147</v>
+        <v>89152</v>
       </c>
       <c r="K27" s="5">
-        <v>97006</v>
+        <v>97011</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="3"/>
-        <v>0.86734858103395862</v>
+        <v>0.86739328695838769</v>
       </c>
       <c r="M27" s="2">
         <v>156288</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>107171</v>
+        <v>107176</v>
       </c>
       <c r="P27" s="5">
-        <v>138418</v>
+        <v>138423</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.88565980753480755</v>
+        <v>0.88569179975429979</v>
       </c>
       <c r="R27" s="5">
         <v>113087</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="T27" s="6">
         <f t="shared" si="6"/>
-        <v>70956</v>
+        <v>70961</v>
       </c>
       <c r="U27" s="5">
-        <v>99654</v>
+        <v>99659</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="7"/>
-        <v>0.88121534747583719</v>
+        <v>0.88125956122277538</v>
       </c>
       <c r="W27" s="5">
         <v>116164</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>68631</v>
+        <v>68635</v>
       </c>
       <c r="Z27" s="5">
-        <v>102896</v>
+        <v>102900</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.88578217003546711</v>
+        <v>0.88581660411142871</v>
       </c>
       <c r="AB27" s="6">
         <v>165468</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>87049</v>
+        <v>87053</v>
       </c>
       <c r="AE27" s="5">
-        <v>147890</v>
+        <v>147894</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.89376797930717722</v>
+        <v>0.89379215316556671</v>
       </c>
       <c r="AG27" s="5">
         <v>116084</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>63650</v>
+        <v>63654</v>
       </c>
       <c r="AJ27" s="5">
-        <v>102265</v>
+        <v>102269</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.88095689328417348</v>
+        <v>0.88099135109058957</v>
       </c>
       <c r="AL27" s="5">
         <v>117992</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="14"/>
-        <v>33227</v>
+        <v>33231</v>
       </c>
       <c r="AO27" s="5">
-        <v>104343</v>
+        <v>104347</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="15"/>
-        <v>0.88432266594345377</v>
+        <v>0.88435656654688455</v>
       </c>
       <c r="AQ27" s="6">
         <v>170879</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>94812</v>
+        <v>94816</v>
       </c>
       <c r="AT27" s="5">
-        <v>153091</v>
+        <v>153095</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.89590294887025324</v>
+        <v>0.89592635724694081</v>
       </c>
       <c r="AV27" s="5">
         <v>116485</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>62238</v>
+        <v>62243</v>
       </c>
       <c r="AY27" s="5">
-        <v>105075</v>
+        <v>105080</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.90204747392368112</v>
+        <v>0.90209039790530965</v>
       </c>
       <c r="BA27" s="5">
         <v>117017</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>62155</v>
+        <v>62160</v>
       </c>
       <c r="BD27" s="5">
-        <v>106737</v>
+        <v>106742</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.91214951673688438</v>
+        <v>0.9121922455711563</v>
       </c>
       <c r="BF27" s="5">
         <v>172738</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>103532</v>
+        <v>103538</v>
       </c>
       <c r="BI27" s="5">
-        <v>156636</v>
+        <v>156642</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.90678368396068032</v>
+        <v>0.90681841864557888</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="E28" s="6">
         <f t="shared" si="0"/>
-        <v>250548</v>
+        <v>250550</v>
       </c>
       <c r="F28" s="5">
-        <v>316189</v>
+        <v>316191</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="1"/>
-        <v>0.83926974091091278</v>
+        <v>0.83927504956960053</v>
       </c>
       <c r="H28" s="3">
         <v>377506</v>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="J28" s="6">
         <f t="shared" si="2"/>
-        <v>278959</v>
+        <v>278960</v>
       </c>
       <c r="K28" s="5">
-        <v>316485</v>
+        <v>316486</v>
       </c>
       <c r="L28" s="7">
         <f t="shared" si="3"/>
-        <v>0.8383575360391623</v>
+        <v>0.83836018500368203</v>
       </c>
       <c r="M28" s="2">
         <v>622937</v>
@@ -4877,14 +4877,14 @@
       </c>
       <c r="O28" s="6">
         <f t="shared" si="4"/>
-        <v>331111</v>
+        <v>331112</v>
       </c>
       <c r="P28" s="5">
-        <v>549579</v>
+        <v>549580</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="5"/>
-        <v>0.88223849281709066</v>
+        <v>0.88224009811586079</v>
       </c>
       <c r="R28" s="5">
         <v>379798</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="T28" s="6">
         <f t="shared" si="6"/>
-        <v>170715</v>
+        <v>170717</v>
       </c>
       <c r="U28" s="5">
-        <v>318465</v>
+        <v>318467</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="7"/>
-        <v>0.8385115245472593</v>
+        <v>0.83851679050442607</v>
       </c>
       <c r="W28" s="5">
         <v>378910</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>163226</v>
+        <v>163230</v>
       </c>
       <c r="Z28" s="5">
-        <v>322471</v>
+        <v>322475</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="9"/>
-        <v>0.8510490617824813</v>
+        <v>0.85105961837903465</v>
       </c>
       <c r="AB28" s="6">
         <v>628364</v>
@@ -4928,14 +4928,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>254357</v>
+        <v>254359</v>
       </c>
       <c r="AE28" s="5">
-        <v>559989</v>
+        <v>559991</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.89118568218421168</v>
+        <v>0.89118886505274009</v>
       </c>
       <c r="AG28" s="5">
         <v>375124</v>
@@ -4945,14 +4945,14 @@
       </c>
       <c r="AI28" s="6">
         <f t="shared" si="12"/>
-        <v>152974</v>
+        <v>152976</v>
       </c>
       <c r="AJ28" s="5">
-        <v>323061</v>
+        <v>323063</v>
       </c>
       <c r="AK28" s="7">
         <f t="shared" si="13"/>
-        <v>0.86121122615455159</v>
+        <v>0.86121655772491235</v>
       </c>
       <c r="AL28" s="5">
         <v>368781</v>
@@ -4962,14 +4962,14 @@
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="14"/>
-        <v>60407</v>
+        <v>60408</v>
       </c>
       <c r="AO28" s="5">
-        <v>328466</v>
+        <v>328467</v>
       </c>
       <c r="AP28" s="7">
         <f t="shared" si="15"/>
-        <v>0.89068037670053501</v>
+        <v>0.89068308833698051</v>
       </c>
       <c r="AQ28" s="6">
         <v>617418</v>
@@ -4979,14 +4979,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>275501</v>
+        <v>275502</v>
       </c>
       <c r="AT28" s="5">
-        <v>571900</v>
+        <v>571901</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.9262768497193149</v>
+        <v>0.92627846936759217</v>
       </c>
       <c r="AV28" s="5">
         <v>357852</v>
@@ -4996,14 +4996,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>144539</v>
+        <v>144540</v>
       </c>
       <c r="AY28" s="5">
-        <v>331102</v>
+        <v>331103</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.92524842672389707</v>
+        <v>0.92525122117523451</v>
       </c>
       <c r="BA28" s="5">
         <v>359943</v>
@@ -5013,14 +5013,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>140361</v>
+        <v>140363</v>
       </c>
       <c r="BD28" s="5">
-        <v>335593</v>
+        <v>335595</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.93235039992443247</v>
+        <v>0.93235595635975699</v>
       </c>
       <c r="BF28" s="5">
         <v>622234</v>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>281144</v>
+        <v>281147</v>
       </c>
       <c r="BI28" s="5">
-        <v>582334</v>
+        <v>582337</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.93587621377166785</v>
+        <v>0.93588103510897824</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5089,14 +5089,14 @@
       </c>
       <c r="O29" s="6">
         <f t="shared" si="4"/>
-        <v>99079</v>
+        <v>99080</v>
       </c>
       <c r="P29" s="5">
-        <v>145429</v>
+        <v>145430</v>
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="5"/>
-        <v>0.93668644007754787</v>
+        <v>0.93669288092799774</v>
       </c>
       <c r="R29" s="5">
         <v>111838</v>
@@ -5140,14 +5140,14 @@
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>76482</v>
+        <v>76483</v>
       </c>
       <c r="AE29" s="5">
-        <v>149209</v>
+        <v>149210</v>
       </c>
       <c r="AF29" s="7">
         <f t="shared" si="11"/>
-        <v>0.93164207621271622</v>
+        <v>0.93164832008591569</v>
       </c>
       <c r="AG29" s="5">
         <v>115309</v>
@@ -5191,14 +5191,14 @@
       </c>
       <c r="AS29" s="6">
         <f t="shared" si="16"/>
-        <v>81641</v>
+        <v>81642</v>
       </c>
       <c r="AT29" s="5">
-        <v>153097</v>
+        <v>153098</v>
       </c>
       <c r="AU29" s="7">
         <f t="shared" si="17"/>
-        <v>0.93130927251823414</v>
+        <v>0.9313153556503172</v>
       </c>
       <c r="AV29" s="5">
         <v>118862</v>
@@ -5242,14 +5242,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>89125</v>
+        <v>89126</v>
       </c>
       <c r="BI29" s="5">
-        <v>156294</v>
+        <v>156295</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.93447651163207834</v>
+        <v>0.93448249059807598</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5267,14 +5267,14 @@
       </c>
       <c r="E30" s="6">
         <f t="shared" si="0"/>
-        <v>120391</v>
+        <v>120393</v>
       </c>
       <c r="F30" s="5">
-        <v>135146</v>
+        <v>135148</v>
       </c>
       <c r="G30" s="7">
         <f t="shared" si="1"/>
-        <v>0.90509453042855137</v>
+        <v>0.90510792475069823</v>
       </c>
       <c r="H30" s="3">
         <v>149659</v>
@@ -5284,14 +5284,14 @@
       </c>
       <c r="J30" s="6">
         <f t="shared" si="2"/>
-        <v>123005</v>
+        <v>123006</v>
       </c>
       <c r="K30" s="5">
-        <v>135783</v>
+        <v>135784</v>
       </c>
       <c r="L30" s="7">
         <f t="shared" si="3"/>
-        <v>0.90728255567657146</v>
+        <v>0.9072892375333258</v>
       </c>
       <c r="M30" s="2">
         <v>249952</v>
@@ -5301,14 +5301,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>169127</v>
+        <v>169129</v>
       </c>
       <c r="P30" s="5">
-        <v>226892</v>
+        <v>226894</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.90774228651901168</v>
+        <v>0.90775028805530666</v>
       </c>
       <c r="R30" s="5">
         <v>151431</v>
@@ -5318,14 +5318,14 @@
       </c>
       <c r="T30" s="6">
         <f t="shared" si="6"/>
-        <v>94129</v>
+        <v>94131</v>
       </c>
       <c r="U30" s="5">
-        <v>135552</v>
+        <v>135554</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="7"/>
-        <v>0.8951403609564752</v>
+        <v>0.89515356829182924</v>
       </c>
       <c r="W30" s="5">
         <v>154416</v>
@@ -5335,14 +5335,14 @@
       </c>
       <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>93955</v>
+        <v>93957</v>
       </c>
       <c r="Z30" s="5">
-        <v>138535</v>
+        <v>138537</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="9"/>
-        <v>0.89715443995440891</v>
+        <v>0.89716739198010564</v>
       </c>
       <c r="AB30" s="6">
         <v>259264</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>140053</v>
+        <v>140055</v>
       </c>
       <c r="AE30" s="5">
-        <v>234124</v>
+        <v>234126</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.90303320167859791</v>
+        <v>0.90304091582325352</v>
       </c>
       <c r="AG30" s="5">
         <v>153178</v>
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>82961</v>
+        <v>82963</v>
       </c>
       <c r="AJ30" s="5">
-        <v>137365</v>
+        <v>137367</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.8967671597749024</v>
+        <v>0.89678021648017336</v>
       </c>
       <c r="AL30" s="5">
         <v>156106</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>37356</v>
+        <v>37358</v>
       </c>
       <c r="AO30" s="5">
-        <v>141048</v>
+        <v>141050</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.90353990237402793</v>
+        <v>0.9035527141813896</v>
       </c>
       <c r="AQ30" s="6">
         <v>266513</v>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>145547</v>
+        <v>145548</v>
       </c>
       <c r="AT30" s="5">
-        <v>242503</v>
+        <v>242504</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.90991058597516816</v>
+        <v>0.90991433813735167</v>
       </c>
       <c r="AV30" s="5">
         <v>155103</v>
@@ -5420,14 +5420,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>81274</v>
+        <v>81275</v>
       </c>
       <c r="AY30" s="5">
-        <v>142134</v>
+        <v>142135</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.91638459604262978</v>
+        <v>0.91639104337117916</v>
       </c>
       <c r="BA30" s="5">
         <v>156855</v>
@@ -5437,14 +5437,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>80543</v>
+        <v>80544</v>
       </c>
       <c r="BD30" s="5">
-        <v>144575</v>
+        <v>144576</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.92171113448726527</v>
+        <v>0.92171750980204648</v>
       </c>
       <c r="BF30" s="5">
         <v>270589</v>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>155901</v>
+        <v>155903</v>
       </c>
       <c r="BI30" s="5">
-        <v>247610</v>
+        <v>247612</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.91507784869303632</v>
+        <v>0.91508523997649571</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>59918</v>
+        <v>59919</v>
       </c>
       <c r="F31" s="5">
-        <v>66617</v>
+        <v>66618</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>0.92733549563595363</v>
+        <v>0.92734941603908849</v>
       </c>
       <c r="H31" s="3">
         <v>72505</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>57740</v>
+        <v>57741</v>
       </c>
       <c r="K31" s="5">
-        <v>66723</v>
+        <v>66724</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.92025377560168264</v>
+        <v>0.92026756775394802</v>
       </c>
       <c r="M31" s="2">
         <v>118891</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="O31" s="6">
         <f t="shared" si="4"/>
-        <v>80422</v>
+        <v>80423</v>
       </c>
       <c r="P31" s="5">
-        <v>111877</v>
+        <v>111878</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="5"/>
-        <v>0.94100478589632519</v>
+        <v>0.94101319696192309</v>
       </c>
       <c r="R31" s="5">
         <v>72813</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>42982</v>
+        <v>42983</v>
       </c>
       <c r="U31" s="5">
-        <v>67151</v>
+        <v>67152</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.92223916058945521</v>
+        <v>0.92225289440072511</v>
       </c>
       <c r="W31" s="5">
         <v>74776</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>42002</v>
+        <v>42003</v>
       </c>
       <c r="Z31" s="5">
-        <v>68806</v>
+        <v>68807</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.92016154916015835</v>
+        <v>0.92017492243500587</v>
       </c>
       <c r="AB31" s="6">
         <v>124489</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>65119</v>
+        <v>65121</v>
       </c>
       <c r="AE31" s="5">
-        <v>116345</v>
+        <v>116347</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.93458056535115552</v>
+        <v>0.93459663102764101</v>
       </c>
       <c r="AG31" s="5">
         <v>73552</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>67768</v>
+        <v>67772</v>
       </c>
       <c r="AT31" s="5">
-        <v>119010</v>
+        <v>119014</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.93970595202375129</v>
+        <v>0.93973753612431499</v>
       </c>
       <c r="AV31" s="5">
         <v>72827</v>
@@ -5666,14 +5666,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>72569</v>
+        <v>72573</v>
       </c>
       <c r="BI31" s="5">
-        <v>121947</v>
+        <v>121951</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.94127590598587474</v>
+        <v>0.94130678090386322</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5776,14 +5776,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>213232</v>
+        <v>213235</v>
       </c>
       <c r="AE32" s="5">
-        <v>373029</v>
+        <v>373032</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.95076054930826714</v>
+        <v>0.95076819558147363</v>
       </c>
       <c r="AG32" s="5">
         <v>183147</v>
@@ -5827,14 +5827,14 @@
       </c>
       <c r="AS32" s="6">
         <f t="shared" si="16"/>
-        <v>213493</v>
+        <v>213496</v>
       </c>
       <c r="AT32" s="5">
-        <v>382380</v>
+        <v>382383</v>
       </c>
       <c r="AU32" s="7">
         <f t="shared" si="17"/>
-        <v>0.9498377937969168</v>
+        <v>0.94984524584300034</v>
       </c>
       <c r="AV32" s="5">
         <v>187080</v>
@@ -5878,14 +5878,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>227767</v>
+        <v>227770</v>
       </c>
       <c r="BI32" s="5">
-        <v>388848</v>
+        <v>388851</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.94689933618082378</v>
+        <v>0.9469066416009585</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="E33" s="6">
         <f t="shared" si="0"/>
-        <v>398259</v>
+        <v>398262</v>
       </c>
       <c r="F33" s="5">
-        <v>534841</v>
+        <v>534844</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="1"/>
-        <v>0.96451164971506886</v>
+        <v>0.96451705979946623</v>
       </c>
       <c r="H33" s="3">
         <v>558618</v>
@@ -5920,14 +5920,14 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" si="2"/>
-        <v>412272</v>
+        <v>412276</v>
       </c>
       <c r="K33" s="5">
-        <v>539928</v>
+        <v>539932</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="3"/>
-        <v>0.96654243150059616</v>
+        <v>0.9665495920288999</v>
       </c>
       <c r="M33" s="2">
         <v>943614</v>
@@ -5937,14 +5937,14 @@
       </c>
       <c r="O33" s="6">
         <f t="shared" si="4"/>
-        <v>332784</v>
+        <v>332787</v>
       </c>
       <c r="P33" s="5">
-        <v>926018</v>
+        <v>926021</v>
       </c>
       <c r="Q33" s="7">
         <f t="shared" si="5"/>
-        <v>0.98135254457860943</v>
+        <v>0.98135572384470771</v>
       </c>
       <c r="R33" s="5">
         <v>563773</v>
@@ -5954,14 +5954,14 @@
       </c>
       <c r="T33" s="6">
         <f t="shared" si="6"/>
-        <v>150534</v>
+        <v>150537</v>
       </c>
       <c r="U33" s="5">
-        <v>549199</v>
+        <v>549202</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="7"/>
-        <v>0.97414916996734502</v>
+        <v>0.97415449125800635</v>
       </c>
       <c r="W33" s="5">
         <v>571583</v>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="Y33" s="6">
         <f t="shared" si="8"/>
-        <v>139896</v>
+        <v>139901</v>
       </c>
       <c r="Z33" s="5">
-        <v>554799</v>
+        <v>554804</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="9"/>
-        <v>0.97063593563839368</v>
+        <v>0.97064468327434505</v>
       </c>
       <c r="AB33" s="6">
         <v>961057</v>
@@ -5988,14 +5988,14 @@
       </c>
       <c r="AD33" s="6">
         <f t="shared" si="10"/>
-        <v>220234</v>
+        <v>220237</v>
       </c>
       <c r="AE33" s="5">
-        <v>941299</v>
+        <v>941302</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="11"/>
-        <v>0.97944138589074325</v>
+        <v>0.97944450745377221</v>
       </c>
       <c r="AG33" s="5">
         <v>565645</v>
@@ -6005,14 +6005,14 @@
       </c>
       <c r="AI33" s="6">
         <f t="shared" si="12"/>
-        <v>154554</v>
+        <v>154556</v>
       </c>
       <c r="AJ33" s="5">
-        <v>550819</v>
+        <v>550821</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="13"/>
-        <v>0.97378921408303798</v>
+        <v>0.97379274986961784</v>
       </c>
       <c r="AL33" s="5">
         <v>569536</v>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="AN33" s="6">
         <f t="shared" si="14"/>
-        <v>52849</v>
+        <v>52851</v>
       </c>
       <c r="AO33" s="5">
-        <v>556512</v>
+        <v>556514</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="15"/>
-        <v>0.97713226205191595</v>
+        <v>0.9771357736824362</v>
       </c>
       <c r="AQ33" s="6">
         <v>971221</v>
@@ -6039,14 +6039,14 @@
       </c>
       <c r="AS33" s="6">
         <f t="shared" si="16"/>
-        <v>215722</v>
+        <v>215724</v>
       </c>
       <c r="AT33" s="5">
-        <v>953011</v>
+        <v>953013</v>
       </c>
       <c r="AU33" s="7">
         <f t="shared" si="17"/>
-        <v>0.98125040541751052</v>
+        <v>0.98125246468105609</v>
       </c>
       <c r="AV33" s="5">
         <v>571074</v>
@@ -6056,14 +6056,14 @@
       </c>
       <c r="AX33" s="6">
         <f t="shared" si="18"/>
-        <v>101111</v>
+        <v>101112</v>
       </c>
       <c r="AY33" s="5">
-        <v>560630</v>
+        <v>560631</v>
       </c>
       <c r="AZ33" s="7">
         <f t="shared" si="19"/>
-        <v>0.98171165208011568</v>
+        <v>0.98171340316666489</v>
       </c>
       <c r="BA33" s="5">
         <v>575700</v>
@@ -6073,14 +6073,14 @@
       </c>
       <c r="BC33" s="6">
         <f t="shared" si="20"/>
-        <v>95011</v>
+        <v>95012</v>
       </c>
       <c r="BD33" s="5">
-        <v>570883</v>
+        <v>570884</v>
       </c>
       <c r="BE33" s="7">
         <f t="shared" si="21"/>
-        <v>0.99163279485843325</v>
+        <v>0.99163453187424011</v>
       </c>
       <c r="BF33" s="5">
         <v>986775</v>
@@ -6090,14 +6090,14 @@
       </c>
       <c r="BH33" s="6">
         <f t="shared" si="22"/>
-        <v>221377</v>
+        <v>221379</v>
       </c>
       <c r="BI33" s="5">
-        <v>972677</v>
+        <v>972679</v>
       </c>
       <c r="BJ33" s="7">
         <f t="shared" si="23"/>
-        <v>0.98571305515441721</v>
+        <v>0.98571508195890656</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>564952</v>
+        <v>564959</v>
       </c>
       <c r="F36" s="5">
-        <v>708793</v>
+        <v>708800</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.94805825372579333</v>
+        <v>0.94806761669604855</v>
       </c>
       <c r="H36" s="3">
         <v>754952</v>
@@ -6532,14 +6532,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>589828</v>
+        <v>589835</v>
       </c>
       <c r="K36" s="5">
-        <v>714392</v>
+        <v>714399</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.94627473004906271</v>
+        <v>0.94628400216172681</v>
       </c>
       <c r="M36" s="2">
         <v>1378095</v>
@@ -6549,14 +6549,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>749531</v>
+        <v>749540</v>
       </c>
       <c r="P36" s="5">
-        <v>1322843</v>
+        <v>1322852</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.95990697303161243</v>
+        <v>0.95991350378602347</v>
       </c>
       <c r="R36" s="5">
         <v>758000</v>
@@ -6566,14 +6566,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>349401</v>
+        <v>349411</v>
       </c>
       <c r="U36" s="5">
-        <v>717587</v>
+        <v>717597</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.94668469656992082</v>
+        <v>0.94669788918205799</v>
       </c>
       <c r="W36" s="5">
         <v>766789</v>
@@ -6583,14 +6583,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>352528</v>
+        <v>352536</v>
       </c>
       <c r="Z36" s="5">
-        <v>731788</v>
+        <v>731796</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.9543538052841134</v>
+        <v>0.95436423840195939</v>
       </c>
       <c r="AB36" s="6">
         <v>1410553</v>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>580353</v>
+        <v>580365</v>
       </c>
       <c r="AE36" s="5">
-        <v>1353302</v>
+        <v>1353314</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.95941237231071785</v>
+        <v>0.95942087961246403</v>
       </c>
       <c r="AG36" s="5">
         <v>767229</v>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>321688</v>
+        <v>321696</v>
       </c>
       <c r="AJ36" s="5">
-        <v>729725</v>
+        <v>729733</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.95111759331307866</v>
+        <v>0.9511280204476108</v>
       </c>
       <c r="AL36" s="5">
         <v>779513</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>159012</v>
+        <v>159019</v>
       </c>
       <c r="AO36" s="5">
-        <v>741644</v>
+        <v>741651</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.95141966843400949</v>
+        <v>0.95142864839970598</v>
       </c>
       <c r="AQ36" s="6">
         <v>1443943</v>
@@ -6651,14 +6651,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>553770</v>
+        <v>553783</v>
       </c>
       <c r="AT36" s="5">
-        <v>1380637</v>
+        <v>1380650</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.95615754915533369</v>
+        <v>0.95616655228080338</v>
       </c>
       <c r="AV36" s="5">
         <v>783108</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>259332</v>
+        <v>259341</v>
       </c>
       <c r="AY36" s="5">
-        <v>745630</v>
+        <v>745639</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.95214197786256816</v>
+        <v>0.95215347053024613</v>
       </c>
       <c r="BA36" s="5">
         <v>793830</v>
@@ -6685,14 +6685,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>252868</v>
+        <v>252875</v>
       </c>
       <c r="BD36" s="5">
-        <v>759214</v>
+        <v>759221</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.95639368630563215</v>
+        <v>0.95640250431452578</v>
       </c>
       <c r="BF36" s="5">
         <v>1468416</v>
@@ -6702,14 +6702,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="24"/>
-        <v>554453</v>
+        <v>554470</v>
       </c>
       <c r="BI36" s="5">
-        <v>1403624</v>
+        <v>1403641</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="25"/>
-        <v>0.95587626394700143</v>
+        <v>0.95588784104776847</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
-        <v>483613</v>
+        <v>483618</v>
       </c>
       <c r="F37" s="5">
-        <v>548008</v>
+        <v>548013</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="1"/>
-        <v>0.92503760020391046</v>
+        <v>0.9250460402047882</v>
       </c>
       <c r="H37" s="3">
         <v>593173</v>
@@ -6744,14 +6744,14 @@
       </c>
       <c r="J37" s="6">
         <f t="shared" si="2"/>
-        <v>489494</v>
+        <v>489499</v>
       </c>
       <c r="K37" s="5">
-        <v>547540</v>
+        <v>547545</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="3"/>
-        <v>0.92306966095894449</v>
+        <v>0.92307809020302678</v>
       </c>
       <c r="M37" s="2">
         <v>768378</v>
@@ -6761,14 +6761,14 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="4"/>
-        <v>455268</v>
+        <v>455274</v>
       </c>
       <c r="P37" s="5">
-        <v>713675</v>
+        <v>713681</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="5"/>
-        <v>0.92880717563490889</v>
+        <v>0.9288149842915856</v>
       </c>
       <c r="R37" s="5">
         <v>601605</v>
@@ -6778,14 +6778,14 @@
       </c>
       <c r="T37" s="6">
         <f t="shared" si="6"/>
-        <v>294902</v>
+        <v>294909</v>
       </c>
       <c r="U37" s="5">
-        <v>556546</v>
+        <v>556553</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="7"/>
-        <v>0.92510201876646636</v>
+        <v>0.92511365430805925</v>
       </c>
       <c r="W37" s="5">
         <v>609453</v>
@@ -6795,14 +6795,14 @@
       </c>
       <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>298786</v>
+        <v>298794</v>
       </c>
       <c r="Z37" s="5">
-        <v>564823</v>
+        <v>564831</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="9"/>
-        <v>0.92677039902994984</v>
+        <v>0.92678352555488286</v>
       </c>
       <c r="AB37" s="6">
         <v>790568</v>
@@ -6812,14 +6812,14 @@
       </c>
       <c r="AD37" s="6">
         <f t="shared" si="10"/>
-        <v>342009</v>
+        <v>342021</v>
       </c>
       <c r="AE37" s="5">
-        <v>735784</v>
+        <v>735796</v>
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="11"/>
-        <v>0.93070298823124642</v>
+        <v>0.93071816719118405</v>
       </c>
       <c r="AG37" s="5">
         <v>617773</v>
@@ -6829,14 +6829,14 @@
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="12"/>
-        <v>268086</v>
+        <v>268093</v>
       </c>
       <c r="AJ37" s="5">
-        <v>572922</v>
+        <v>572929</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="13"/>
-        <v>0.92739889894831917</v>
+        <v>0.92741022997120304</v>
       </c>
       <c r="AL37" s="5">
         <v>624724</v>
@@ -6846,14 +6846,14 @@
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="14"/>
-        <v>101156</v>
+        <v>101166</v>
       </c>
       <c r="AO37" s="5">
-        <v>581010</v>
+        <v>581020</v>
       </c>
       <c r="AP37" s="7">
         <f t="shared" si="15"/>
-        <v>0.93002669979062758</v>
+        <v>0.93004270685934909</v>
       </c>
       <c r="AQ37" s="6">
         <v>810789</v>
@@ -6863,14 +6863,14 @@
       </c>
       <c r="AS37" s="6">
         <f t="shared" si="16"/>
-        <v>350623</v>
+        <v>350636</v>
       </c>
       <c r="AT37" s="5">
-        <v>756816</v>
+        <v>756829</v>
       </c>
       <c r="AU37" s="7">
         <f t="shared" si="17"/>
-        <v>0.93343150930760033</v>
+        <v>0.93344754307224198</v>
       </c>
       <c r="AV37" s="5">
         <v>633338</v>
@@ -6880,14 +6880,14 @@
       </c>
       <c r="AX37" s="6">
         <f t="shared" si="18"/>
-        <v>242757</v>
+        <v>242766</v>
       </c>
       <c r="AY37" s="5">
-        <v>591822</v>
+        <v>591831</v>
       </c>
       <c r="AZ37" s="7">
         <f t="shared" si="19"/>
-        <v>0.93444890406070691</v>
+        <v>0.93446311448231434</v>
       </c>
       <c r="BA37" s="5">
         <v>640933</v>
@@ -6897,14 +6897,14 @@
       </c>
       <c r="BC37" s="6">
         <f t="shared" si="20"/>
-        <v>236695</v>
+        <v>236702</v>
       </c>
       <c r="BD37" s="5">
-        <v>600807</v>
+        <v>600814</v>
       </c>
       <c r="BE37" s="7">
         <f t="shared" si="21"/>
-        <v>0.93739439223756615</v>
+        <v>0.93740531381595271</v>
       </c>
       <c r="BF37" s="5">
         <v>830528</v>
@@ -6914,14 +6914,14 @@
       </c>
       <c r="BH37" s="6">
         <f t="shared" si="24"/>
-        <v>361770</v>
+        <v>361782</v>
       </c>
       <c r="BI37" s="5">
-        <v>776587</v>
+        <v>776599</v>
       </c>
       <c r="BJ37" s="7">
         <f t="shared" si="25"/>
-        <v>0.93505215959004395</v>
+        <v>0.93506660822994525</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6973,14 +6973,14 @@
       </c>
       <c r="O38" s="6">
         <f t="shared" si="4"/>
-        <v>18713</v>
+        <v>18714</v>
       </c>
       <c r="P38" s="5">
-        <v>31185</v>
+        <v>31186</v>
       </c>
       <c r="Q38" s="7">
         <f t="shared" si="5"/>
-        <v>0.87605697109306968</v>
+        <v>0.87608506334803493</v>
       </c>
       <c r="R38" s="5">
         <v>24050</v>
@@ -7024,14 +7024,14 @@
       </c>
       <c r="AD38" s="6">
         <f t="shared" si="10"/>
-        <v>15394</v>
+        <v>15395</v>
       </c>
       <c r="AE38" s="5">
-        <v>31562</v>
+        <v>31563</v>
       </c>
       <c r="AF38" s="7">
         <f t="shared" si="11"/>
-        <v>0.87628408018213111</v>
+        <v>0.87631184407796103</v>
       </c>
       <c r="AG38" s="5">
         <v>24216</v>
@@ -7075,14 +7075,14 @@
       </c>
       <c r="AS38" s="6">
         <f t="shared" si="16"/>
-        <v>15505</v>
+        <v>15506</v>
       </c>
       <c r="AT38" s="5">
-        <v>32162</v>
+        <v>32163</v>
       </c>
       <c r="AU38" s="7">
         <f t="shared" si="17"/>
-        <v>0.88274688477795471</v>
+        <v>0.88277433166822195</v>
       </c>
       <c r="AV38" s="5">
         <v>24471</v>
@@ -7126,14 +7126,14 @@
       </c>
       <c r="BH38" s="6">
         <f t="shared" si="24"/>
-        <v>15818</v>
+        <v>15819</v>
       </c>
       <c r="BI38" s="5">
-        <v>32737</v>
+        <v>32738</v>
       </c>
       <c r="BJ38" s="7">
         <f t="shared" si="25"/>
-        <v>0.87839759585714672</v>
+        <v>0.8784244278086345</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7363,14 +7363,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>214677</v>
+        <v>214679</v>
       </c>
       <c r="F40" s="5">
-        <v>240186</v>
+        <v>240188</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.94171015436007421</v>
+        <v>0.94171799586752558</v>
       </c>
       <c r="H40" s="3">
         <v>254802</v>
@@ -7380,14 +7380,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>221359</v>
+        <v>221361</v>
       </c>
       <c r="K40" s="5">
-        <v>240315</v>
+        <v>240317</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.94314408835095487</v>
+        <v>0.9431519375829075</v>
       </c>
       <c r="M40" s="2">
         <v>315837</v>
@@ -7397,14 +7397,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>210331</v>
+        <v>210334</v>
       </c>
       <c r="P40" s="5">
-        <v>299302</v>
+        <v>299305</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.94764704578627579</v>
+        <v>0.94765654435674096</v>
       </c>
       <c r="R40" s="5">
         <v>257348</v>
@@ -7414,14 +7414,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>121899</v>
+        <v>121902</v>
       </c>
       <c r="U40" s="5">
-        <v>242357</v>
+        <v>242360</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.94174813870712037</v>
+        <v>0.94175979607379889</v>
       </c>
       <c r="W40" s="5">
         <v>259512</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>111088</v>
+        <v>111091</v>
       </c>
       <c r="Z40" s="5">
-        <v>244311</v>
+        <v>244314</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.94142467400351426</v>
+        <v>0.94143623416258204</v>
       </c>
       <c r="AB40" s="6">
         <v>322067</v>
@@ -7448,14 +7448,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>125320</v>
+        <v>125322</v>
       </c>
       <c r="AE40" s="5">
-        <v>305016</v>
+        <v>305018</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.94705759981618731</v>
+        <v>0.94706380970419202</v>
       </c>
       <c r="AG40" s="5">
         <v>262041</v>
@@ -7465,14 +7465,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>92325</v>
+        <v>92327</v>
       </c>
       <c r="AJ40" s="5">
-        <v>247108</v>
+        <v>247110</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.94301273464839475</v>
+        <v>0.94302036704179881</v>
       </c>
       <c r="AL40" s="5">
         <v>264607</v>
@@ -7482,14 +7482,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>39742</v>
+        <v>39744</v>
       </c>
       <c r="AO40" s="5">
-        <v>250043</v>
+        <v>250045</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.9449598839032981</v>
+        <v>0.9449674422823281</v>
       </c>
       <c r="AQ40" s="6">
         <v>328683</v>
@@ -7499,14 +7499,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>125217</v>
+        <v>125220</v>
       </c>
       <c r="AT40" s="5">
-        <v>312598</v>
+        <v>312601</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.95106226972493257</v>
+        <v>0.95107139706038946</v>
       </c>
       <c r="AV40" s="5">
         <v>267796</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>91422</v>
+        <v>91424</v>
       </c>
       <c r="AY40" s="5">
-        <v>253322</v>
+        <v>253324</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.94595139583862342</v>
+        <v>0.94595886421007036</v>
       </c>
       <c r="BA40" s="5">
         <v>270158</v>
@@ -7533,14 +7533,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="BD40" s="5">
-        <v>256020</v>
+        <v>256022</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.94766766114644019</v>
+        <v>0.94767506422167769</v>
       </c>
       <c r="BF40" s="5">
         <v>335514</v>
@@ -7550,14 +7550,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="24"/>
-        <v>137571</v>
+        <v>137574</v>
       </c>
       <c r="BI40" s="5">
-        <v>318077</v>
+        <v>318080</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="25"/>
-        <v>0.94802899431916399</v>
+        <v>0.94803793582384044</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7575,14 +7575,14 @@
       </c>
       <c r="E41" s="6">
         <f t="shared" si="0"/>
-        <v>580304</v>
+        <v>580325</v>
       </c>
       <c r="F41" s="5">
-        <v>764151</v>
+        <v>764172</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="1"/>
-        <v>0.95147324697057989</v>
+        <v>0.95149939486305979</v>
       </c>
       <c r="H41" s="3">
         <v>805681</v>
@@ -7592,14 +7592,14 @@
       </c>
       <c r="J41" s="6">
         <f t="shared" si="2"/>
-        <v>690178</v>
+        <v>690197</v>
       </c>
       <c r="K41" s="5">
-        <v>764242</v>
+        <v>764261</v>
       </c>
       <c r="L41" s="7">
         <f t="shared" si="3"/>
-        <v>0.94856649219728406</v>
+        <v>0.94859007473181078</v>
       </c>
       <c r="M41" s="2">
         <v>924274</v>
@@ -7609,14 +7609,14 @@
       </c>
       <c r="O41" s="6">
         <f t="shared" si="4"/>
-        <v>505875</v>
+        <v>505894</v>
       </c>
       <c r="P41" s="5">
-        <v>874751</v>
+        <v>874770</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" si="5"/>
-        <v>0.94641956822327578</v>
+        <v>0.94644012489802809</v>
       </c>
       <c r="R41" s="5">
         <v>822173</v>
@@ -7626,14 +7626,14 @@
       </c>
       <c r="T41" s="6">
         <f t="shared" si="6"/>
-        <v>371870</v>
+        <v>371889</v>
       </c>
       <c r="U41" s="5">
-        <v>778590</v>
+        <v>778609</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="7"/>
-        <v>0.94699047524061242</v>
+        <v>0.94701358473216712</v>
       </c>
       <c r="W41" s="5">
         <v>833879</v>
@@ -7643,14 +7643,14 @@
       </c>
       <c r="Y41" s="6">
         <f t="shared" si="8"/>
-        <v>376185</v>
+        <v>376205</v>
       </c>
       <c r="Z41" s="5">
-        <v>786031</v>
+        <v>786051</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="9"/>
-        <v>0.94261997244204498</v>
+        <v>0.94264395673712853</v>
       </c>
       <c r="AB41" s="6">
         <v>956956</v>
@@ -7660,14 +7660,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>367815</v>
+        <v>367844</v>
       </c>
       <c r="AE41" s="5">
-        <v>899936</v>
+        <v>899965</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.94041523330226262</v>
+        <v>0.94044553772587247</v>
       </c>
       <c r="AG41" s="5">
         <v>851169</v>
@@ -7677,14 +7677,14 @@
       </c>
       <c r="AI41" s="6">
         <f t="shared" si="12"/>
-        <v>370351</v>
+        <v>370376</v>
       </c>
       <c r="AJ41" s="5">
-        <v>798484</v>
+        <v>798509</v>
       </c>
       <c r="AK41" s="7">
         <f t="shared" si="13"/>
-        <v>0.9381027739497092</v>
+        <v>0.93813214532014211</v>
       </c>
       <c r="AL41" s="5">
         <v>859964</v>
@@ -7694,14 +7694,14 @@
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="14"/>
-        <v>117954</v>
+        <v>117979</v>
       </c>
       <c r="AO41" s="5">
-        <v>806977</v>
+        <v>807002</v>
       </c>
       <c r="AP41" s="7">
         <f t="shared" si="15"/>
-        <v>0.9383846300542813</v>
+        <v>0.93841370103864818</v>
       </c>
       <c r="AQ41" s="6">
         <v>982238</v>
@@ -7711,14 +7711,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>370228</v>
+        <v>370251</v>
       </c>
       <c r="AT41" s="5">
-        <v>921103</v>
+        <v>921126</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.93775948395399078</v>
+        <v>0.93778289986744556</v>
       </c>
       <c r="AV41" s="5">
         <v>867973</v>
@@ -7728,14 +7728,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>303473</v>
+        <v>303493</v>
       </c>
       <c r="AY41" s="5">
-        <v>816670</v>
+        <v>816690</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.94089332271856385</v>
+        <v>0.94091636490996844</v>
       </c>
       <c r="BA41" s="5">
         <v>869274</v>
@@ -7745,14 +7745,14 @@
       </c>
       <c r="BC41" s="6">
         <f t="shared" si="20"/>
-        <v>302041</v>
+        <v>302061</v>
       </c>
       <c r="BD41" s="5">
-        <v>822901</v>
+        <v>822921</v>
       </c>
       <c r="BE41" s="7">
         <f t="shared" si="21"/>
-        <v>0.94665318415137234</v>
+        <v>0.94667619185665275</v>
       </c>
       <c r="BF41" s="5">
         <v>986817</v>
@@ -7762,14 +7762,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="24"/>
-        <v>395350</v>
+        <v>395374</v>
       </c>
       <c r="BI41" s="5">
-        <v>937167</v>
+        <v>937191</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="25"/>
-        <v>0.94968672003015753</v>
+        <v>0.94971104064887413</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8118,14 +8118,14 @@
       </c>
       <c r="AN43" s="6">
         <f t="shared" si="14"/>
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AO43" s="5">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="AP43" s="7">
         <f t="shared" si="15"/>
-        <v>0.90655884995507641</v>
+        <v>0.90685834082060501</v>
       </c>
       <c r="AQ43" s="6">
         <v>4111</v>
@@ -8135,14 +8135,14 @@
       </c>
       <c r="AS43" s="6">
         <f t="shared" si="16"/>
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="AT43" s="5">
-        <v>3816</v>
+        <v>3817</v>
       </c>
       <c r="AU43" s="7">
         <f t="shared" si="17"/>
-        <v>0.92824130381902215</v>
+        <v>0.92848455363658478</v>
       </c>
       <c r="AV43" s="5">
         <v>3256</v>
@@ -8152,14 +8152,14 @@
       </c>
       <c r="AX43" s="6">
         <f t="shared" si="18"/>
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AY43" s="5">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="AZ43" s="7">
         <f t="shared" si="19"/>
-        <v>0.9441031941031941</v>
+        <v>0.94441031941031939</v>
       </c>
       <c r="BA43" s="5">
         <v>3286</v>
@@ -8169,14 +8169,14 @@
       </c>
       <c r="BC43" s="6">
         <f t="shared" si="20"/>
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="BD43" s="5">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="BE43" s="7">
         <f t="shared" si="21"/>
-        <v>0.94309190505173468</v>
+        <v>0.94339622641509435</v>
       </c>
       <c r="BF43" s="5">
         <v>4091</v>
@@ -8186,14 +8186,14 @@
       </c>
       <c r="BH43" s="6">
         <f t="shared" si="24"/>
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="BI43" s="5">
-        <v>3895</v>
+        <v>3896</v>
       </c>
       <c r="BJ43" s="7">
         <f t="shared" si="25"/>
-        <v>0.95208995355658765</v>
+        <v>0.95233439256905406</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8279,14 +8279,14 @@
       </c>
       <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>161075</v>
+        <v>161076</v>
       </c>
       <c r="Z44" s="5">
-        <v>275332</v>
+        <v>275333</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>0.84110647787502479</v>
+        <v>0.84110953275596079</v>
       </c>
       <c r="AB44" s="6">
         <v>393681</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="AD44" s="6">
         <f t="shared" si="10"/>
-        <v>175093</v>
+        <v>175094</v>
       </c>
       <c r="AE44" s="5">
-        <v>336173</v>
+        <v>336174</v>
       </c>
       <c r="AF44" s="7">
         <f t="shared" si="11"/>
-        <v>0.8539223381367147</v>
+        <v>0.85392487826438157</v>
       </c>
       <c r="AG44" s="5">
         <v>333199</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>145822</v>
+        <v>145823</v>
       </c>
       <c r="AJ44" s="5">
-        <v>279560</v>
+        <v>279561</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.8390181243040945</v>
+        <v>0.83902112551358199</v>
       </c>
       <c r="AL44" s="5">
         <v>336893</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>65079</v>
+        <v>65080</v>
       </c>
       <c r="AO44" s="5">
-        <v>284665</v>
+        <v>284666</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.84497154883004399</v>
+        <v>0.84497451713155214</v>
       </c>
       <c r="AQ44" s="6">
         <v>406157</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>177441</v>
+        <v>177442</v>
       </c>
       <c r="AT44" s="5">
-        <v>347544</v>
+        <v>347545</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.8556888099921951</v>
+        <v>0.85569127209428864</v>
       </c>
       <c r="AV44" s="5">
         <v>341214</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>140158</v>
+        <v>140159</v>
       </c>
       <c r="AY44" s="5">
-        <v>288750</v>
+        <v>288751</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.8462431201533348</v>
+        <v>0.84624605086543925</v>
       </c>
       <c r="BA44" s="5">
         <v>343859</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="BC44" s="6">
         <f t="shared" si="20"/>
-        <v>138780</v>
+        <v>138781</v>
       </c>
       <c r="BD44" s="5">
-        <v>292341</v>
+        <v>292342</v>
       </c>
       <c r="BE44" s="7">
         <f t="shared" si="21"/>
-        <v>0.85017696206875493</v>
+        <v>0.85017987023751018</v>
       </c>
       <c r="BF44" s="5">
         <v>410714</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="BH44" s="6">
         <f t="shared" si="24"/>
-        <v>190894</v>
+        <v>190895</v>
       </c>
       <c r="BI44" s="5">
-        <v>354693</v>
+        <v>354694</v>
       </c>
       <c r="BJ44" s="7">
         <f t="shared" si="25"/>
-        <v>0.86360094859196423</v>
+        <v>0.86360338337626674</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8474,14 +8474,14 @@
       </c>
       <c r="T45" s="6">
         <f t="shared" si="6"/>
-        <v>110253</v>
+        <v>110254</v>
       </c>
       <c r="U45" s="5">
-        <v>218693</v>
+        <v>218694</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="7"/>
-        <v>0.90034541105562393</v>
+        <v>0.90034952799311652</v>
       </c>
       <c r="W45" s="5">
         <v>244806</v>
@@ -8491,14 +8491,14 @@
       </c>
       <c r="Y45" s="6">
         <f t="shared" si="8"/>
-        <v>113528</v>
+        <v>113530</v>
       </c>
       <c r="Z45" s="5">
-        <v>220499</v>
+        <v>220501</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="9"/>
-        <v>0.9007091329460879</v>
+        <v>0.90071730268048988</v>
       </c>
       <c r="AB45" s="6">
         <v>299772</v>
@@ -8508,14 +8508,14 @@
       </c>
       <c r="AD45" s="6">
         <f t="shared" si="10"/>
-        <v>124970</v>
+        <v>124972</v>
       </c>
       <c r="AE45" s="5">
-        <v>271300</v>
+        <v>271302</v>
       </c>
       <c r="AF45" s="7">
         <f t="shared" si="11"/>
-        <v>0.90502114940688261</v>
+        <v>0.90502782114406954</v>
       </c>
       <c r="AG45" s="5">
         <v>246243</v>
@@ -8525,14 +8525,14 @@
       </c>
       <c r="AI45" s="6">
         <f t="shared" si="12"/>
-        <v>101042</v>
+        <v>101045</v>
       </c>
       <c r="AJ45" s="5">
-        <v>222567</v>
+        <v>222570</v>
       </c>
       <c r="AK45" s="7">
         <f t="shared" si="13"/>
-        <v>0.90385107393915765</v>
+        <v>0.90386325702659565</v>
       </c>
       <c r="AL45" s="5">
         <v>247584</v>
@@ -8542,14 +8542,14 @@
       </c>
       <c r="AN45" s="6">
         <f t="shared" si="14"/>
-        <v>40250</v>
+        <v>40253</v>
       </c>
       <c r="AO45" s="5">
-        <v>225197</v>
+        <v>225200</v>
       </c>
       <c r="AP45" s="7">
         <f t="shared" si="15"/>
-        <v>0.90957816337081554</v>
+        <v>0.90959028047046664</v>
       </c>
       <c r="AQ45" s="6">
         <v>303759</v>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="AS45" s="6">
         <f t="shared" si="16"/>
-        <v>134138</v>
+        <v>134141</v>
       </c>
       <c r="AT45" s="5">
-        <v>277031</v>
+        <v>277034</v>
       </c>
       <c r="AU45" s="7">
         <f t="shared" si="17"/>
-        <v>0.91200919149720672</v>
+        <v>0.91201906774778685</v>
       </c>
       <c r="AV45" s="5">
         <v>248547</v>
@@ -8576,14 +8576,14 @@
       </c>
       <c r="AX45" s="6">
         <f t="shared" si="18"/>
-        <v>101075</v>
+        <v>101077</v>
       </c>
       <c r="AY45" s="5">
-        <v>227082</v>
+        <v>227084</v>
       </c>
       <c r="AZ45" s="7">
         <f t="shared" si="19"/>
-        <v>0.91363806443046991</v>
+        <v>0.91364611119828443</v>
       </c>
       <c r="BA45" s="5">
         <v>248925</v>
@@ -8593,14 +8593,14 @@
       </c>
       <c r="BC45" s="6">
         <f t="shared" si="20"/>
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="BD45" s="5">
-        <v>229248</v>
+        <v>229250</v>
       </c>
       <c r="BE45" s="7">
         <f t="shared" si="21"/>
-        <v>0.92095209400421818</v>
+        <v>0.92096012855277698</v>
       </c>
       <c r="BF45" s="5">
         <v>305535</v>
@@ -8610,14 +8610,14 @@
       </c>
       <c r="BH45" s="6">
         <f t="shared" si="24"/>
-        <v>145880</v>
+        <v>145882</v>
       </c>
       <c r="BI45" s="5">
-        <v>281593</v>
+        <v>281595</v>
       </c>
       <c r="BJ45" s="7">
         <f t="shared" si="25"/>
-        <v>0.92163909208437655</v>
+        <v>0.92164563797928223</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -8635,14 +8635,14 @@
       </c>
       <c r="E46" s="6">
         <f t="shared" si="0"/>
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="F46" s="5">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="G46" s="7">
         <f t="shared" si="1"/>
-        <v>0.85652173913043483</v>
+        <v>0.85700483091787438</v>
       </c>
       <c r="H46" s="3">
         <v>2134</v>
@@ -8652,14 +8652,14 @@
       </c>
       <c r="J46" s="6">
         <f t="shared" si="2"/>
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="K46" s="5">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="L46" s="7">
         <f t="shared" si="3"/>
-        <v>0.83411433926897849</v>
+        <v>0.83458294283036549</v>
       </c>
       <c r="M46" s="2">
         <v>4565</v>
@@ -8669,14 +8669,14 @@
       </c>
       <c r="O46" s="6">
         <f t="shared" si="4"/>
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="P46" s="5">
-        <v>4042</v>
+        <v>4043</v>
       </c>
       <c r="Q46" s="7">
         <f t="shared" si="5"/>
-        <v>0.88543263964950714</v>
+        <v>0.88565169769989049</v>
       </c>
       <c r="R46" s="5">
         <v>2092</v>
@@ -8686,14 +8686,14 @@
       </c>
       <c r="T46" s="6">
         <f t="shared" si="6"/>
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="U46" s="5">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="V46" s="7">
         <f t="shared" si="7"/>
-        <v>0.81166347992351817</v>
+        <v>0.8121414913957935</v>
       </c>
       <c r="W46" s="5">
         <v>2205</v>
@@ -8703,14 +8703,14 @@
       </c>
       <c r="Y46" s="6">
         <f t="shared" si="8"/>
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="Z46" s="5">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="AA46" s="7">
         <f t="shared" si="9"/>
-        <v>0.82585034013605441</v>
+        <v>0.82630385487528346</v>
       </c>
       <c r="AB46" s="6">
         <v>4967</v>
@@ -8720,14 +8720,14 @@
       </c>
       <c r="AD46" s="6">
         <f t="shared" si="10"/>
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="AE46" s="5">
-        <v>4395</v>
+        <v>4396</v>
       </c>
       <c r="AF46" s="7">
         <f t="shared" si="11"/>
-        <v>0.88483994362794438</v>
+        <v>0.8850412723978256</v>
       </c>
       <c r="AG46" s="5">
         <v>2151</v>
@@ -8737,14 +8737,14 @@
       </c>
       <c r="AI46" s="6">
         <f t="shared" si="12"/>
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="AJ46" s="5">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="AK46" s="7">
         <f t="shared" si="13"/>
-        <v>0.79172477917247797</v>
+        <v>0.79218967921896788</v>
       </c>
       <c r="AL46" s="5">
         <v>2221</v>
@@ -8754,14 +8754,14 @@
       </c>
       <c r="AN46" s="6">
         <f t="shared" si="14"/>
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AO46" s="5">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="AP46" s="7">
         <f t="shared" si="15"/>
-        <v>0.80324178298063931</v>
+        <v>0.80369203061683925</v>
       </c>
       <c r="AQ46" s="6">
         <v>5242</v>
@@ -8771,14 +8771,14 @@
       </c>
       <c r="AS46" s="6">
         <f t="shared" si="16"/>
-        <v>2951</v>
+        <v>2952</v>
       </c>
       <c r="AT46" s="5">
-        <v>4772</v>
+        <v>4773</v>
       </c>
       <c r="AU46" s="7">
         <f t="shared" si="17"/>
-        <v>0.91033956505150704</v>
+        <v>0.91053033193437616</v>
       </c>
       <c r="AV46" s="5">
         <v>2226</v>
@@ -8788,14 +8788,14 @@
       </c>
       <c r="AX46" s="6">
         <f t="shared" si="18"/>
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="AY46" s="5">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="AZ46" s="7">
         <f t="shared" si="19"/>
-        <v>0.83333333333333337</v>
+        <v>0.83378256963162622</v>
       </c>
       <c r="BA46" s="5">
         <v>2322</v>
@@ -8805,14 +8805,14 @@
       </c>
       <c r="BC46" s="6">
         <f t="shared" si="20"/>
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="BD46" s="5">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="BE46" s="7">
         <f t="shared" si="21"/>
-        <v>0.82730404823428083</v>
+        <v>0.8277347114556417</v>
       </c>
       <c r="BF46" s="5">
         <v>5417</v>
@@ -8822,14 +8822,14 @@
       </c>
       <c r="BH46" s="6">
         <f t="shared" si="24"/>
-        <v>3211</v>
+        <v>3212</v>
       </c>
       <c r="BI46" s="5">
-        <v>5167</v>
+        <v>5168</v>
       </c>
       <c r="BJ46" s="7">
         <f t="shared" si="25"/>
-        <v>0.95384899390806721</v>
+        <v>0.95403359793243492</v>
       </c>
     </row>
     <row r="47" spans="1:62" x14ac:dyDescent="0.3">
@@ -9059,15 +9059,15 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" si="0"/>
-        <v>5348017</v>
+        <v>5348076</v>
       </c>
       <c r="F48" s="9">
         <f>SUM(F10:F47)</f>
-        <v>6383747</v>
+        <v>6383806</v>
       </c>
       <c r="G48" s="8">
         <f t="shared" si="1"/>
-        <v>0.92081685346257591</v>
+        <v>0.92082536385535219</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9079,15 +9079,15 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="2"/>
-        <v>5526896</v>
+        <v>5526950</v>
       </c>
       <c r="K48" s="9">
         <f>SUM(K10:K47)</f>
-        <v>6398633</v>
+        <v>6398687</v>
       </c>
       <c r="L48" s="8">
         <f t="shared" si="3"/>
-        <v>0.92056886621247991</v>
+        <v>0.92057663517168964</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="O48" s="10">
         <f t="shared" si="4"/>
-        <v>5889949</v>
+        <v>5890017</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>10190887</v>
+        <v>10190955</v>
       </c>
       <c r="Q48" s="8">
         <f t="shared" si="5"/>
-        <v>0.93871126621680612</v>
+        <v>0.93871752988807466</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="T48" s="10">
         <f t="shared" si="6"/>
-        <v>3238796</v>
+        <v>3238865</v>
       </c>
       <c r="U48" s="9">
         <f>SUM(U10:U47)</f>
-        <v>6483853</v>
+        <v>6483922</v>
       </c>
       <c r="V48" s="8">
         <f t="shared" si="7"/>
-        <v>0.92385082406113173</v>
+        <v>0.92386065551580232</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="8"/>
-        <v>3177147</v>
+        <v>3177222</v>
       </c>
       <c r="Z48" s="9">
         <f>SUM(Z10:Z47)</f>
-        <v>6602768</v>
+        <v>6602843</v>
       </c>
       <c r="AA48" s="8">
         <f t="shared" si="9"/>
-        <v>0.92659243936872182</v>
+        <v>0.92660296441411982</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="AD48" s="10">
         <f t="shared" si="10"/>
-        <v>4486559</v>
+        <v>4486660</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>10492129</v>
+        <v>10492230</v>
       </c>
       <c r="AF48" s="8">
         <f t="shared" si="11"/>
-        <v>0.93837420350521206</v>
+        <v>0.93838323654269706</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="AI48" s="10">
         <f t="shared" si="12"/>
-        <v>2995913</v>
+        <v>2995987</v>
       </c>
       <c r="AJ48" s="9">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6600625</v>
+        <v>6600699</v>
       </c>
       <c r="AK48" s="8">
         <f t="shared" si="13"/>
-        <v>0.92610715448249548</v>
+        <v>0.92611753712496214</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AN48" s="10">
         <f t="shared" si="14"/>
-        <v>1213285</v>
+        <v>1213361</v>
       </c>
       <c r="AO48" s="9">
         <f>SUM(AO10:AO47)</f>
-        <v>6708454</v>
+        <v>6708530</v>
       </c>
       <c r="AP48" s="8">
         <f t="shared" si="15"/>
-        <v>0.93056277065885018</v>
+        <v>0.93057331299402457</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AS48" s="10">
         <f t="shared" si="16"/>
-        <v>4624621</v>
+        <v>4624724</v>
       </c>
       <c r="AT48" s="9">
         <f>SUM(AT10:AT47)</f>
-        <v>10740448</v>
+        <v>10740551</v>
       </c>
       <c r="AU48" s="8">
         <f t="shared" si="17"/>
-        <v>0.9397451611923836</v>
+        <v>0.93975417327005517</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AX48" s="10">
         <f t="shared" si="18"/>
-        <v>2609839</v>
+        <v>2609911</v>
       </c>
       <c r="AY48" s="9">
         <f>SUM(AY10:AY47)</f>
-        <v>6760911</v>
+        <v>6760983</v>
       </c>
       <c r="AZ48" s="8">
         <f t="shared" si="19"/>
-        <v>0.93347085906130334</v>
+        <v>0.93348080001480094</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="BC48" s="10">
         <f t="shared" si="20"/>
-        <v>2558861</v>
+        <v>2558932</v>
       </c>
       <c r="BD48" s="9">
         <f>SUM(BD10:BD47)</f>
-        <v>6870399</v>
+        <v>6870470</v>
       </c>
       <c r="BE48" s="8">
         <f t="shared" ref="BE48" si="26">BD48/BA48</f>
-        <v>0.93963940183868677</v>
+        <v>0.939649112249615</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="BH48" s="10">
         <f t="shared" si="24"/>
-        <v>4819218</v>
+        <v>4819336</v>
       </c>
       <c r="BI48" s="9">
         <f>SUM(BI10:BI47)</f>
-        <v>10950883</v>
+        <v>10951001</v>
       </c>
       <c r="BJ48" s="8">
         <f t="shared" si="25"/>
-        <v>0.94150873593772344</v>
+        <v>0.94151888105851778</v>
       </c>
     </row>
   </sheetData>

--- a/gstdatabase/GSTR-1-2021-2022.xlsx
+++ b/gstdatabase/GSTR-1-2021-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20391D09-2A22-4381-9045-C36B4D442838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDC6B51-D42A-4C05-9E2E-B02584FB5B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,10 +179,10 @@
     <t>Gujarat</t>
   </si>
   <si>
-    <t>Data Considered upto 30th Jun 2026</t>
+    <t>Data Considered upto 31st Jul 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 30th Jun 2026</t>
+    <t>Filing %age as on 31st Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -1027,14 +1027,14 @@
       </c>
       <c r="E10" s="6">
         <f>F10-D10</f>
-        <v>46327</v>
+        <v>46329</v>
       </c>
       <c r="F10" s="5">
-        <v>51814</v>
+        <v>51816</v>
       </c>
       <c r="G10" s="7">
         <f>F10/C10</f>
-        <v>0.95059350175206858</v>
+        <v>0.95063019428697226</v>
       </c>
       <c r="H10" s="3">
         <v>53973</v>
@@ -1044,14 +1044,14 @@
       </c>
       <c r="J10" s="6">
         <f>K10-I10</f>
-        <v>45939</v>
+        <v>45941</v>
       </c>
       <c r="K10" s="5">
-        <v>52099</v>
+        <v>52101</v>
       </c>
       <c r="L10" s="7">
         <f>K10/H10</f>
-        <v>0.96527893576417834</v>
+        <v>0.96531599132899781</v>
       </c>
       <c r="M10" s="2">
         <v>85686</v>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="O10" s="6">
         <f>P10-N10</f>
-        <v>58833</v>
+        <v>58834</v>
       </c>
       <c r="P10" s="5">
-        <v>82091</v>
+        <v>82092</v>
       </c>
       <c r="Q10" s="7">
         <f>P10/M10</f>
-        <v>0.95804448801437803</v>
+        <v>0.95805615853231563</v>
       </c>
       <c r="R10" s="5">
         <v>56418</v>
@@ -1146,14 +1146,14 @@
       </c>
       <c r="AN10" s="6">
         <f>AO10-AM10</f>
-        <v>15569</v>
+        <v>15570</v>
       </c>
       <c r="AO10" s="5">
-        <v>59254</v>
+        <v>59255</v>
       </c>
       <c r="AP10" s="7">
         <f>AO10/AL10</f>
-        <v>0.94947682151040746</v>
+        <v>0.94949284535388656</v>
       </c>
       <c r="AQ10" s="6">
         <v>99346</v>
@@ -1163,14 +1163,14 @@
       </c>
       <c r="AS10" s="6">
         <f>AT10-AR10</f>
-        <v>54388</v>
+        <v>54389</v>
       </c>
       <c r="AT10" s="5">
-        <v>93654</v>
+        <v>93655</v>
       </c>
       <c r="AU10" s="7">
         <f>AT10/AQ10</f>
-        <v>0.94270529261369351</v>
+        <v>0.94271535844422527</v>
       </c>
       <c r="AV10" s="5">
         <v>63719</v>
@@ -1180,14 +1180,14 @@
       </c>
       <c r="AX10" s="6">
         <f>AY10-AW10</f>
-        <v>31823</v>
+        <v>31824</v>
       </c>
       <c r="AY10" s="5">
-        <v>60271</v>
+        <v>60272</v>
       </c>
       <c r="AZ10" s="7">
         <f>AY10/AV10</f>
-        <v>0.94588741191795223</v>
+        <v>0.94590310582400849</v>
       </c>
       <c r="BA10" s="5">
         <v>65133</v>
@@ -1197,14 +1197,14 @@
       </c>
       <c r="BC10" s="6">
         <f>BD10-BB10</f>
-        <v>32462</v>
+        <v>32463</v>
       </c>
       <c r="BD10" s="5">
-        <v>61502</v>
+        <v>61503</v>
       </c>
       <c r="BE10" s="7">
         <f>BD10/BA10</f>
-        <v>0.94425252943976168</v>
+        <v>0.94426788264013639</v>
       </c>
       <c r="BF10" s="5">
         <v>104274</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="BH10" s="6">
         <f>BI10-BG10</f>
-        <v>59411</v>
+        <v>59412</v>
       </c>
       <c r="BI10" s="5">
-        <v>97134</v>
+        <v>97135</v>
       </c>
       <c r="BJ10" s="7">
         <f>BI10/BF10</f>
-        <v>0.93152655503768922</v>
+        <v>0.93153614515603123</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1451,14 +1451,14 @@
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>115033</v>
+        <v>115034</v>
       </c>
       <c r="F12" s="5">
-        <v>148731</v>
+        <v>148732</v>
       </c>
       <c r="G12" s="7">
         <f t="shared" si="1"/>
-        <v>0.92689812477798339</v>
+        <v>0.92690435682190686</v>
       </c>
       <c r="H12" s="3">
         <v>161190</v>
@@ -1468,14 +1468,14 @@
       </c>
       <c r="J12" s="6">
         <f t="shared" si="2"/>
-        <v>124717</v>
+        <v>124718</v>
       </c>
       <c r="K12" s="5">
-        <v>150205</v>
+        <v>150206</v>
       </c>
       <c r="L12" s="7">
         <f t="shared" si="3"/>
-        <v>0.93185061108009182</v>
+        <v>0.93185681493889194</v>
       </c>
       <c r="M12" s="2">
         <v>320319</v>
@@ -1875,14 +1875,14 @@
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>63913</v>
+        <v>63916</v>
       </c>
       <c r="F14" s="5">
-        <v>72491</v>
+        <v>72494</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0.91857267762332573</v>
+        <v>0.91861069224628411</v>
       </c>
       <c r="H14" s="3">
         <v>78856</v>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="2"/>
-        <v>62770</v>
+        <v>62773</v>
       </c>
       <c r="K14" s="5">
-        <v>72500</v>
+        <v>72503</v>
       </c>
       <c r="L14" s="7">
         <f t="shared" si="3"/>
-        <v>0.91939738257076187</v>
+        <v>0.91943542660038546</v>
       </c>
       <c r="M14" s="2">
         <v>139510</v>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="O14" s="6">
         <f t="shared" si="4"/>
-        <v>84030</v>
+        <v>84035</v>
       </c>
       <c r="P14" s="5">
-        <v>131023</v>
+        <v>131028</v>
       </c>
       <c r="Q14" s="7">
         <f t="shared" si="5"/>
-        <v>0.93916565120779871</v>
+        <v>0.93920149093254968</v>
       </c>
       <c r="R14" s="5">
         <v>78838</v>
@@ -1926,14 +1926,14 @@
       </c>
       <c r="T14" s="6">
         <f t="shared" si="6"/>
-        <v>40330</v>
+        <v>40333</v>
       </c>
       <c r="U14" s="5">
-        <v>72426</v>
+        <v>72429</v>
       </c>
       <c r="V14" s="7">
         <f t="shared" si="7"/>
-        <v>0.91866866232020095</v>
+        <v>0.9187067150358964</v>
       </c>
       <c r="W14" s="5">
         <v>80553</v>
@@ -1943,14 +1943,14 @@
       </c>
       <c r="Y14" s="6">
         <f t="shared" si="8"/>
-        <v>38581</v>
+        <v>38584</v>
       </c>
       <c r="Z14" s="5">
-        <v>74213</v>
+        <v>74216</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="9"/>
-        <v>0.9212940548458779</v>
+        <v>0.9213312974066763</v>
       </c>
       <c r="AB14" s="6">
         <v>144082</v>
@@ -1960,14 +1960,14 @@
       </c>
       <c r="AD14" s="6">
         <f t="shared" si="10"/>
-        <v>66585</v>
+        <v>66590</v>
       </c>
       <c r="AE14" s="5">
-        <v>135270</v>
+        <v>135275</v>
       </c>
       <c r="AF14" s="7">
         <f t="shared" si="11"/>
-        <v>0.93884038255993119</v>
+        <v>0.93887508502102968</v>
       </c>
       <c r="AG14" s="5">
         <v>79635</v>
@@ -1977,14 +1977,14 @@
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="12"/>
-        <v>36585</v>
+        <v>36588</v>
       </c>
       <c r="AJ14" s="5">
-        <v>73459</v>
+        <v>73462</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" si="13"/>
-        <v>0.92244616060777296</v>
+        <v>0.92248383248571608</v>
       </c>
       <c r="AL14" s="5">
         <v>81274</v>
@@ -1994,14 +1994,14 @@
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="14"/>
-        <v>16027</v>
+        <v>16029</v>
       </c>
       <c r="AO14" s="5">
-        <v>75080</v>
+        <v>75082</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="15"/>
-        <v>0.92378866550188254</v>
+        <v>0.9238132736176391</v>
       </c>
       <c r="AQ14" s="6">
         <v>148266</v>
@@ -2011,14 +2011,14 @@
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="16"/>
-        <v>68571</v>
+        <v>68574</v>
       </c>
       <c r="AT14" s="5">
-        <v>139144</v>
+        <v>139147</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="17"/>
-        <v>0.93847544278526429</v>
+        <v>0.93849567668919376</v>
       </c>
       <c r="AV14" s="5">
         <v>81291</v>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="AX14" s="6">
         <f t="shared" si="18"/>
-        <v>31970</v>
+        <v>31972</v>
       </c>
       <c r="AY14" s="5">
-        <v>75336</v>
+        <v>75338</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="19"/>
-        <v>0.92674465808023032</v>
+        <v>0.92676926104980872</v>
       </c>
       <c r="BA14" s="5">
         <v>82359</v>
@@ -2045,14 +2045,14 @@
       </c>
       <c r="BC14" s="6">
         <f t="shared" si="20"/>
-        <v>31699</v>
+        <v>31701</v>
       </c>
       <c r="BD14" s="5">
-        <v>76622</v>
+        <v>76624</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="21"/>
-        <v>0.93034155344285385</v>
+        <v>0.93036583737053635</v>
       </c>
       <c r="BF14" s="5">
         <v>151377</v>
@@ -2062,14 +2062,14 @@
       </c>
       <c r="BH14" s="6">
         <f t="shared" si="22"/>
-        <v>71660</v>
+        <v>71665</v>
       </c>
       <c r="BI14" s="5">
-        <v>141679</v>
+        <v>141684</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="23"/>
-        <v>0.93593478533727048</v>
+        <v>0.9359678154541311</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2333,14 +2333,14 @@
       </c>
       <c r="O16" s="6">
         <f t="shared" si="4"/>
-        <v>296138</v>
+        <v>296139</v>
       </c>
       <c r="P16" s="5">
-        <v>672239</v>
+        <v>672240</v>
       </c>
       <c r="Q16" s="7">
         <f t="shared" si="5"/>
-        <v>0.93525130812113322</v>
+        <v>0.93525269936934718</v>
       </c>
       <c r="R16" s="5">
         <v>403668</v>
@@ -2367,14 +2367,14 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" si="8"/>
-        <v>131967</v>
+        <v>131968</v>
       </c>
       <c r="Z16" s="5">
-        <v>376717</v>
+        <v>376718</v>
       </c>
       <c r="AA16" s="7">
         <f t="shared" si="9"/>
-        <v>0.92592902104691377</v>
+        <v>0.92593147893710992</v>
       </c>
       <c r="AB16" s="6">
         <v>722282</v>
@@ -2452,14 +2452,14 @@
       </c>
       <c r="AX16" s="6">
         <f t="shared" si="18"/>
-        <v>96442</v>
+        <v>96443</v>
       </c>
       <c r="AY16" s="5">
-        <v>378363</v>
+        <v>378364</v>
       </c>
       <c r="AZ16" s="7">
         <f t="shared" si="19"/>
-        <v>0.93953976921415105</v>
+        <v>0.93954225238446432</v>
       </c>
       <c r="BA16" s="5">
         <v>402569</v>
@@ -2469,14 +2469,14 @@
       </c>
       <c r="BC16" s="6">
         <f t="shared" si="20"/>
-        <v>94067</v>
+        <v>94068</v>
       </c>
       <c r="BD16" s="5">
-        <v>384276</v>
+        <v>384277</v>
       </c>
       <c r="BE16" s="7">
         <f t="shared" si="21"/>
-        <v>0.95455934262201014</v>
+        <v>0.95456182666822331</v>
       </c>
       <c r="BF16" s="5">
         <v>736680</v>
@@ -2486,14 +2486,14 @@
       </c>
       <c r="BH16" s="6">
         <f t="shared" si="22"/>
-        <v>196447</v>
+        <v>196448</v>
       </c>
       <c r="BI16" s="5">
-        <v>706646</v>
+        <v>706647</v>
       </c>
       <c r="BJ16" s="7">
         <f t="shared" si="23"/>
-        <v>0.95923060216104683</v>
+        <v>0.95923195960254115</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2511,14 +2511,14 @@
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>225678</v>
+        <v>225682</v>
       </c>
       <c r="F17" s="5">
-        <v>255294</v>
+        <v>255298</v>
       </c>
       <c r="G17" s="7">
         <f t="shared" si="1"/>
-        <v>0.96730485785626863</v>
+        <v>0.96732001379190147</v>
       </c>
       <c r="H17" s="3">
         <v>264168</v>
@@ -2528,14 +2528,14 @@
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>221973</v>
+        <v>221978</v>
       </c>
       <c r="K17" s="5">
-        <v>256560</v>
+        <v>256565</v>
       </c>
       <c r="L17" s="7">
         <f t="shared" si="3"/>
-        <v>0.97120014536204236</v>
+        <v>0.97121907271130492</v>
       </c>
       <c r="M17" s="2">
         <v>591219</v>
@@ -2545,14 +2545,14 @@
       </c>
       <c r="O17" s="6">
         <f t="shared" si="4"/>
-        <v>323448</v>
+        <v>323452</v>
       </c>
       <c r="P17" s="5">
-        <v>577395</v>
+        <v>577399</v>
       </c>
       <c r="Q17" s="7">
         <f t="shared" si="5"/>
-        <v>0.97661780152532307</v>
+        <v>0.97662456720775215</v>
       </c>
       <c r="R17" s="5">
         <v>261213</v>
@@ -2562,14 +2562,14 @@
       </c>
       <c r="T17" s="6">
         <f t="shared" si="6"/>
-        <v>119509</v>
+        <v>119513</v>
       </c>
       <c r="U17" s="5">
-        <v>253303</v>
+        <v>253307</v>
       </c>
       <c r="V17" s="7">
         <f t="shared" si="7"/>
-        <v>0.96971819932392334</v>
+        <v>0.96973351249746376</v>
       </c>
       <c r="W17" s="5">
         <v>269820</v>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="Y17" s="6">
         <f t="shared" si="8"/>
-        <v>114743</v>
+        <v>114749</v>
       </c>
       <c r="Z17" s="5">
-        <v>262472</v>
+        <v>262478</v>
       </c>
       <c r="AA17" s="7">
         <f t="shared" si="9"/>
-        <v>0.97276702987176633</v>
+        <v>0.9727892669186865</v>
       </c>
       <c r="AB17" s="6">
         <v>613565</v>
@@ -2596,14 +2596,14 @@
       </c>
       <c r="AD17" s="6">
         <f t="shared" si="10"/>
-        <v>238276</v>
+        <v>238284</v>
       </c>
       <c r="AE17" s="5">
-        <v>597227</v>
+        <v>597235</v>
       </c>
       <c r="AF17" s="7">
         <f t="shared" si="11"/>
-        <v>0.97337201437500509</v>
+        <v>0.97338505292837763</v>
       </c>
       <c r="AG17" s="5">
         <v>263808</v>
@@ -2613,14 +2613,14 @@
       </c>
       <c r="AI17" s="6">
         <f t="shared" si="12"/>
-        <v>102911</v>
+        <v>102915</v>
       </c>
       <c r="AJ17" s="5">
-        <v>255223</v>
+        <v>255227</v>
       </c>
       <c r="AK17" s="7">
         <f t="shared" si="13"/>
-        <v>0.96745739325570113</v>
+        <v>0.96747255579815628</v>
       </c>
       <c r="AL17" s="5">
         <v>270212</v>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="AN17" s="6">
         <f t="shared" si="14"/>
-        <v>46321</v>
+        <v>46325</v>
       </c>
       <c r="AO17" s="5">
-        <v>262873</v>
+        <v>262877</v>
       </c>
       <c r="AP17" s="7">
         <f t="shared" si="15"/>
-        <v>0.97283984427042469</v>
+        <v>0.97285464746199279</v>
       </c>
       <c r="AQ17" s="6">
         <v>633137</v>
@@ -2647,14 +2647,14 @@
       </c>
       <c r="AS17" s="6">
         <f t="shared" si="16"/>
-        <v>253905</v>
+        <v>253914</v>
       </c>
       <c r="AT17" s="5">
-        <v>612908</v>
+        <v>612917</v>
       </c>
       <c r="AU17" s="7">
         <f t="shared" si="17"/>
-        <v>0.96804956905061623</v>
+        <v>0.96806378398356119</v>
       </c>
       <c r="AV17" s="5">
         <v>270996</v>
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AX17" s="6">
         <f t="shared" si="18"/>
-        <v>84230</v>
+        <v>84234</v>
       </c>
       <c r="AY17" s="5">
-        <v>261437</v>
+        <v>261441</v>
       </c>
       <c r="AZ17" s="7">
         <f t="shared" si="19"/>
-        <v>0.96472641662607561</v>
+        <v>0.96474117699154227</v>
       </c>
       <c r="BA17" s="5">
         <v>277009</v>
@@ -2681,14 +2681,14 @@
       </c>
       <c r="BC17" s="6">
         <f t="shared" si="20"/>
-        <v>81160</v>
+        <v>81165</v>
       </c>
       <c r="BD17" s="5">
-        <v>270955</v>
+        <v>270960</v>
       </c>
       <c r="BE17" s="7">
         <f t="shared" si="21"/>
-        <v>0.97814511441866514</v>
+        <v>0.97816316437372075</v>
       </c>
       <c r="BF17" s="5">
         <v>651560</v>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="BH17" s="6">
         <f t="shared" si="22"/>
-        <v>264498</v>
+        <v>264509</v>
       </c>
       <c r="BI17" s="5">
-        <v>629110</v>
+        <v>629121</v>
       </c>
       <c r="BJ17" s="7">
         <f t="shared" si="23"/>
-        <v>0.96554423230400888</v>
+        <v>0.96556111486279084</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2723,14 +2723,14 @@
       </c>
       <c r="E18" s="6">
         <f t="shared" si="0"/>
-        <v>650573</v>
+        <v>650575</v>
       </c>
       <c r="F18" s="5">
-        <v>716486</v>
+        <v>716488</v>
       </c>
       <c r="G18" s="7">
         <f t="shared" si="1"/>
-        <v>0.93232478067493041</v>
+        <v>0.93232738316759789</v>
       </c>
       <c r="H18" s="3">
         <v>766983</v>
@@ -2740,14 +2740,14 @@
       </c>
       <c r="J18" s="6">
         <f t="shared" si="2"/>
-        <v>624802</v>
+        <v>624803</v>
       </c>
       <c r="K18" s="5">
-        <v>716171</v>
+        <v>716172</v>
       </c>
       <c r="L18" s="7">
         <f t="shared" si="3"/>
-        <v>0.93375081325140197</v>
+        <v>0.93375211706126471</v>
       </c>
       <c r="M18" s="2">
         <v>1193073</v>
@@ -2757,14 +2757,14 @@
       </c>
       <c r="O18" s="6">
         <f t="shared" si="4"/>
-        <v>736277</v>
+        <v>736280</v>
       </c>
       <c r="P18" s="5">
-        <v>1137376</v>
+        <v>1137379</v>
       </c>
       <c r="Q18" s="7">
         <f t="shared" si="5"/>
-        <v>0.95331635197510967</v>
+        <v>0.95331886649014774</v>
       </c>
       <c r="R18" s="5">
         <v>775495</v>
@@ -2774,14 +2774,14 @@
       </c>
       <c r="T18" s="6">
         <f t="shared" si="6"/>
-        <v>411978</v>
+        <v>411981</v>
       </c>
       <c r="U18" s="5">
-        <v>732692</v>
+        <v>732695</v>
       </c>
       <c r="V18" s="7">
         <f t="shared" si="7"/>
-        <v>0.94480557579352542</v>
+        <v>0.94480944429042091</v>
       </c>
       <c r="W18" s="5">
         <v>789854</v>
@@ -2791,14 +2791,14 @@
       </c>
       <c r="Y18" s="6">
         <f t="shared" si="8"/>
-        <v>390052</v>
+        <v>390055</v>
       </c>
       <c r="Z18" s="5">
-        <v>748178</v>
+        <v>748181</v>
       </c>
       <c r="AA18" s="7">
         <f t="shared" si="9"/>
-        <v>0.94723581826514769</v>
+        <v>0.94723961643544252</v>
       </c>
       <c r="AB18" s="6">
         <v>1245422</v>
@@ -2808,14 +2808,14 @@
       </c>
       <c r="AD18" s="6">
         <f t="shared" si="10"/>
-        <v>569097</v>
+        <v>569102</v>
       </c>
       <c r="AE18" s="5">
-        <v>1175171</v>
+        <v>1175176</v>
       </c>
       <c r="AF18" s="7">
         <f t="shared" si="11"/>
-        <v>0.94359261358800472</v>
+        <v>0.94359662829145463</v>
       </c>
       <c r="AG18" s="5">
         <v>794310</v>
@@ -2825,14 +2825,14 @@
       </c>
       <c r="AI18" s="6">
         <f t="shared" si="12"/>
-        <v>388020</v>
+        <v>388025</v>
       </c>
       <c r="AJ18" s="5">
-        <v>750379</v>
+        <v>750384</v>
       </c>
       <c r="AK18" s="7">
         <f t="shared" si="13"/>
-        <v>0.94469287809545388</v>
+        <v>0.94469917286701666</v>
       </c>
       <c r="AL18" s="5">
         <v>807429</v>
@@ -2842,14 +2842,14 @@
       </c>
       <c r="AN18" s="6">
         <f t="shared" si="14"/>
-        <v>142065</v>
+        <v>142069</v>
       </c>
       <c r="AO18" s="5">
-        <v>765805</v>
+        <v>765809</v>
       </c>
       <c r="AP18" s="7">
         <f t="shared" si="15"/>
-        <v>0.94844871809162168</v>
+        <v>0.94845367208757669</v>
       </c>
       <c r="AQ18" s="6">
         <v>1285494</v>
@@ -2859,14 +2859,14 @@
       </c>
       <c r="AS18" s="6">
         <f t="shared" si="16"/>
-        <v>603852</v>
+        <v>603857</v>
       </c>
       <c r="AT18" s="5">
-        <v>1212042</v>
+        <v>1212047</v>
       </c>
       <c r="AU18" s="7">
         <f t="shared" si="17"/>
-        <v>0.94286087683023023</v>
+        <v>0.94286476638552963</v>
       </c>
       <c r="AV18" s="5">
         <v>820095</v>
@@ -2876,14 +2876,14 @@
       </c>
       <c r="AX18" s="6">
         <f t="shared" si="18"/>
-        <v>349471</v>
+        <v>349475</v>
       </c>
       <c r="AY18" s="5">
-        <v>773539</v>
+        <v>773543</v>
       </c>
       <c r="AZ18" s="7">
         <f t="shared" si="19"/>
-        <v>0.94323096714405041</v>
+        <v>0.94323584462775656</v>
       </c>
       <c r="BA18" s="5">
         <v>829968</v>
@@ -2893,14 +2893,14 @@
       </c>
       <c r="BC18" s="6">
         <f t="shared" si="20"/>
-        <v>340739</v>
+        <v>340743</v>
       </c>
       <c r="BD18" s="5">
-        <v>785692</v>
+        <v>785696</v>
       </c>
       <c r="BE18" s="7">
         <f t="shared" si="21"/>
-        <v>0.94665336494901009</v>
+        <v>0.94665818441192917</v>
       </c>
       <c r="BF18" s="5">
         <v>1319511</v>
@@ -2910,14 +2910,14 @@
       </c>
       <c r="BH18" s="6">
         <f t="shared" si="22"/>
-        <v>631897</v>
+        <v>631901</v>
       </c>
       <c r="BI18" s="5">
-        <v>1235571</v>
+        <v>1235575</v>
       </c>
       <c r="BJ18" s="7">
         <f t="shared" si="23"/>
-        <v>0.93638552463753622</v>
+        <v>0.93638855606357208</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2935,14 +2935,14 @@
       </c>
       <c r="E19" s="6">
         <f t="shared" si="0"/>
-        <v>188020</v>
+        <v>188021</v>
       </c>
       <c r="F19" s="5">
-        <v>203914</v>
+        <v>203915</v>
       </c>
       <c r="G19" s="7">
         <f t="shared" si="1"/>
-        <v>0.83076258687982274</v>
+        <v>0.83076666096295027</v>
       </c>
       <c r="H19" s="3">
         <v>247965</v>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="J19" s="6">
         <f t="shared" si="2"/>
-        <v>185925</v>
+        <v>185926</v>
       </c>
       <c r="K19" s="5">
-        <v>204608</v>
+        <v>204609</v>
       </c>
       <c r="L19" s="7">
         <f t="shared" si="3"/>
-        <v>0.82514871050349847</v>
+        <v>0.82515274333071198</v>
       </c>
       <c r="M19" s="2">
         <v>387570</v>
@@ -2969,14 +2969,14 @@
       </c>
       <c r="O19" s="6">
         <f t="shared" si="4"/>
-        <v>259996</v>
+        <v>259999</v>
       </c>
       <c r="P19" s="5">
-        <v>337561</v>
+        <v>337564</v>
       </c>
       <c r="Q19" s="7">
         <f t="shared" si="5"/>
-        <v>0.87096782516706661</v>
+        <v>0.87097556570425982</v>
       </c>
       <c r="R19" s="5">
         <v>254467</v>
@@ -2986,14 +2986,14 @@
       </c>
       <c r="T19" s="6">
         <f t="shared" si="6"/>
-        <v>158287</v>
+        <v>158289</v>
       </c>
       <c r="U19" s="5">
-        <v>216799</v>
+        <v>216801</v>
       </c>
       <c r="V19" s="7">
         <f t="shared" si="7"/>
-        <v>0.8519729473762806</v>
+        <v>0.85198080694156808</v>
       </c>
       <c r="W19" s="5">
         <v>263449</v>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="Y19" s="6">
         <f t="shared" si="8"/>
-        <v>162774</v>
+        <v>162776</v>
       </c>
       <c r="Z19" s="5">
-        <v>229839</v>
+        <v>229841</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="9"/>
-        <v>0.8724231255385293</v>
+        <v>0.87243071714069897</v>
       </c>
       <c r="AB19" s="6">
         <v>418128</v>
@@ -3020,14 +3020,14 @@
       </c>
       <c r="AD19" s="6">
         <f t="shared" si="10"/>
-        <v>231557</v>
+        <v>231558</v>
       </c>
       <c r="AE19" s="5">
-        <v>372445</v>
+        <v>372446</v>
       </c>
       <c r="AF19" s="7">
         <f t="shared" si="11"/>
-        <v>0.89074398270386101</v>
+        <v>0.8907463743159989</v>
       </c>
       <c r="AG19" s="5">
         <v>259213</v>
@@ -3037,14 +3037,14 @@
       </c>
       <c r="AI19" s="6">
         <f t="shared" si="12"/>
-        <v>162938</v>
+        <v>162939</v>
       </c>
       <c r="AJ19" s="5">
-        <v>221044</v>
+        <v>221045</v>
       </c>
       <c r="AK19" s="7">
         <f t="shared" si="13"/>
-        <v>0.85275044075721507</v>
+        <v>0.85275429858841956</v>
       </c>
       <c r="AL19" s="5">
         <v>262802</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="AN19" s="6">
         <f t="shared" si="14"/>
-        <v>63217</v>
+        <v>63219</v>
       </c>
       <c r="AO19" s="5">
-        <v>224991</v>
+        <v>224993</v>
       </c>
       <c r="AP19" s="7">
         <f t="shared" si="15"/>
-        <v>0.85612362158583266</v>
+        <v>0.85613123187799178</v>
       </c>
       <c r="AQ19" s="6">
         <v>437396</v>
@@ -3071,14 +3071,14 @@
       </c>
       <c r="AS19" s="6">
         <f t="shared" si="16"/>
-        <v>254088</v>
+        <v>254091</v>
       </c>
       <c r="AT19" s="5">
-        <v>381171</v>
+        <v>381174</v>
       </c>
       <c r="AU19" s="7">
         <f t="shared" si="17"/>
-        <v>0.87145515734025913</v>
+        <v>0.87146201611354468</v>
       </c>
       <c r="AV19" s="5">
         <v>265429</v>
@@ -3088,14 +3088,14 @@
       </c>
       <c r="AX19" s="6">
         <f t="shared" si="18"/>
-        <v>145065</v>
+        <v>145067</v>
       </c>
       <c r="AY19" s="5">
-        <v>226869</v>
+        <v>226871</v>
       </c>
       <c r="AZ19" s="7">
         <f t="shared" si="19"/>
-        <v>0.85472574586800987</v>
+        <v>0.85473328083969724</v>
       </c>
       <c r="BA19" s="5">
         <v>272122</v>
@@ -3105,14 +3105,14 @@
       </c>
       <c r="BC19" s="6">
         <f t="shared" si="20"/>
-        <v>142887</v>
+        <v>142889</v>
       </c>
       <c r="BD19" s="5">
-        <v>232937</v>
+        <v>232939</v>
       </c>
       <c r="BE19" s="7">
         <f t="shared" si="21"/>
-        <v>0.85600208729907912</v>
+        <v>0.85600943694372378</v>
       </c>
       <c r="BF19" s="5">
         <v>456786</v>
@@ -3122,14 +3122,14 @@
       </c>
       <c r="BH19" s="6">
         <f t="shared" si="22"/>
-        <v>273306</v>
+        <v>273308</v>
       </c>
       <c r="BI19" s="5">
-        <v>393754</v>
+        <v>393756</v>
       </c>
       <c r="BJ19" s="7">
         <f t="shared" si="23"/>
-        <v>0.86200978138559414</v>
+        <v>0.8620141598034966</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3300,14 +3300,14 @@
       </c>
       <c r="AX20" s="6">
         <f t="shared" si="18"/>
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="AY20" s="5">
-        <v>4831</v>
+        <v>4832</v>
       </c>
       <c r="AZ20" s="7">
         <f t="shared" si="19"/>
-        <v>0.82765119068014392</v>
+        <v>0.82782251156415965</v>
       </c>
       <c r="BA20" s="5">
         <v>5912</v>
@@ -3317,14 +3317,14 @@
       </c>
       <c r="BC20" s="6">
         <f t="shared" si="20"/>
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="BD20" s="5">
-        <v>4958</v>
+        <v>4959</v>
       </c>
       <c r="BE20" s="7">
         <f t="shared" si="21"/>
-        <v>0.83863328822733418</v>
+        <v>0.8388024357239513</v>
       </c>
       <c r="BF20" s="5">
         <v>8941</v>
@@ -3334,14 +3334,14 @@
       </c>
       <c r="BH20" s="6">
         <f t="shared" si="22"/>
-        <v>5011</v>
+        <v>5012</v>
       </c>
       <c r="BI20" s="5">
-        <v>7877</v>
+        <v>7878</v>
       </c>
       <c r="BJ20" s="7">
         <f t="shared" si="23"/>
-        <v>0.88099765126943297</v>
+        <v>0.88110949558214968</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="E21" s="6">
         <f t="shared" si="0"/>
-        <v>6577</v>
+        <v>6579</v>
       </c>
       <c r="F21" s="5">
-        <v>7374</v>
+        <v>7376</v>
       </c>
       <c r="G21" s="7">
         <f t="shared" si="1"/>
-        <v>0.72944900583638339</v>
+        <v>0.72964684934217039</v>
       </c>
       <c r="H21" s="3">
         <v>10163</v>
@@ -3376,14 +3376,14 @@
       </c>
       <c r="J21" s="6">
         <f t="shared" si="2"/>
-        <v>6778</v>
+        <v>6780</v>
       </c>
       <c r="K21" s="5">
-        <v>7405</v>
+        <v>7407</v>
       </c>
       <c r="L21" s="7">
         <f t="shared" si="3"/>
-        <v>0.72862343796123197</v>
+        <v>0.72882023024697429</v>
       </c>
       <c r="M21" s="2">
         <v>12994</v>
@@ -3393,14 +3393,14 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="4"/>
-        <v>8008</v>
+        <v>8010</v>
       </c>
       <c r="P21" s="5">
-        <v>9965</v>
+        <v>9967</v>
       </c>
       <c r="Q21" s="7">
         <f t="shared" si="5"/>
-        <v>0.76689241188240731</v>
+        <v>0.76704632907495762</v>
       </c>
       <c r="R21" s="5">
         <v>10237</v>
@@ -3410,14 +3410,14 @@
       </c>
       <c r="T21" s="6">
         <f t="shared" si="6"/>
-        <v>5831</v>
+        <v>5832</v>
       </c>
       <c r="U21" s="5">
-        <v>7503</v>
+        <v>7504</v>
       </c>
       <c r="V21" s="7">
         <f t="shared" si="7"/>
-        <v>0.7329295692097294</v>
+        <v>0.73302725407834324</v>
       </c>
       <c r="W21" s="5">
         <v>10162</v>
@@ -3427,14 +3427,14 @@
       </c>
       <c r="Y21" s="6">
         <f t="shared" si="8"/>
-        <v>5829</v>
+        <v>5830</v>
       </c>
       <c r="Z21" s="5">
-        <v>7609</v>
+        <v>7610</v>
       </c>
       <c r="AA21" s="7">
         <f t="shared" si="9"/>
-        <v>0.74876992717968904</v>
+        <v>0.74886833300531397</v>
       </c>
       <c r="AB21" s="6">
         <v>13196</v>
@@ -3444,14 +3444,14 @@
       </c>
       <c r="AD21" s="6">
         <f t="shared" si="10"/>
-        <v>7181</v>
+        <v>7182</v>
       </c>
       <c r="AE21" s="5">
-        <v>10281</v>
+        <v>10282</v>
       </c>
       <c r="AF21" s="7">
         <f t="shared" si="11"/>
-        <v>0.7790997271900576</v>
+        <v>0.77917550772961508</v>
       </c>
       <c r="AG21" s="5">
         <v>10295</v>
@@ -3461,14 +3461,14 @@
       </c>
       <c r="AI21" s="6">
         <f t="shared" si="12"/>
-        <v>5356</v>
+        <v>5357</v>
       </c>
       <c r="AJ21" s="5">
-        <v>7691</v>
+        <v>7692</v>
       </c>
       <c r="AK21" s="7">
         <f t="shared" si="13"/>
-        <v>0.74706168042739196</v>
+        <v>0.74715881495871783</v>
       </c>
       <c r="AL21" s="5">
         <v>10459</v>
@@ -3478,14 +3478,14 @@
       </c>
       <c r="AN21" s="6">
         <f t="shared" si="14"/>
-        <v>2952</v>
+        <v>2953</v>
       </c>
       <c r="AO21" s="5">
-        <v>7785</v>
+        <v>7786</v>
       </c>
       <c r="AP21" s="7">
         <f t="shared" si="15"/>
-        <v>0.74433502246868721</v>
+        <v>0.74443063390381492</v>
       </c>
       <c r="AQ21" s="6">
         <v>13595</v>
@@ -3495,14 +3495,14 @@
       </c>
       <c r="AS21" s="6">
         <f t="shared" si="16"/>
-        <v>7430</v>
+        <v>7431</v>
       </c>
       <c r="AT21" s="5">
-        <v>10593</v>
+        <v>10594</v>
       </c>
       <c r="AU21" s="7">
         <f t="shared" si="17"/>
-        <v>0.77918352335417429</v>
+        <v>0.77925707980875325</v>
       </c>
       <c r="AV21" s="5">
         <v>10391</v>
@@ -3512,14 +3512,14 @@
       </c>
       <c r="AX21" s="6">
         <f t="shared" si="18"/>
-        <v>5188</v>
+        <v>5189</v>
       </c>
       <c r="AY21" s="5">
-        <v>7909</v>
+        <v>7910</v>
       </c>
       <c r="AZ21" s="7">
         <f t="shared" si="19"/>
-        <v>0.76113944759888363</v>
+        <v>0.76123568472716774</v>
       </c>
       <c r="BA21" s="5">
         <v>10525</v>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="BC21" s="6">
         <f t="shared" si="20"/>
-        <v>5274</v>
+        <v>5275</v>
       </c>
       <c r="BD21" s="5">
-        <v>8049</v>
+        <v>8050</v>
       </c>
       <c r="BE21" s="7">
         <f t="shared" si="21"/>
-        <v>0.76475059382422805</v>
+        <v>0.76484560570071258</v>
       </c>
       <c r="BF21" s="5">
         <v>13618</v>
@@ -3546,14 +3546,14 @@
       </c>
       <c r="BH21" s="6">
         <f t="shared" si="22"/>
-        <v>8335</v>
+        <v>8336</v>
       </c>
       <c r="BI21" s="5">
-        <v>10968</v>
+        <v>10969</v>
       </c>
       <c r="BJ21" s="7">
         <f t="shared" si="23"/>
-        <v>0.80540461154354526</v>
+        <v>0.80547804376560439</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3605,14 +3605,14 @@
       </c>
       <c r="O22" s="6">
         <f t="shared" si="4"/>
-        <v>4755</v>
+        <v>4756</v>
       </c>
       <c r="P22" s="5">
-        <v>5950</v>
+        <v>5951</v>
       </c>
       <c r="Q22" s="7">
         <f t="shared" si="5"/>
-        <v>0.84951456310679607</v>
+        <v>0.84965733866362081</v>
       </c>
       <c r="R22" s="5">
         <v>5966</v>
@@ -3656,14 +3656,14 @@
       </c>
       <c r="AD22" s="6">
         <f t="shared" si="10"/>
-        <v>4012</v>
+        <v>4013</v>
       </c>
       <c r="AE22" s="5">
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="AF22" s="7">
         <f t="shared" si="11"/>
-        <v>0.86794853668881666</v>
+        <v>0.86808991941184788</v>
       </c>
       <c r="AG22" s="5">
         <v>5998</v>
@@ -3707,14 +3707,14 @@
       </c>
       <c r="AS22" s="6">
         <f t="shared" si="16"/>
-        <v>4195</v>
+        <v>4196</v>
       </c>
       <c r="AT22" s="5">
-        <v>6317</v>
+        <v>6318</v>
       </c>
       <c r="AU22" s="7">
         <f t="shared" si="17"/>
-        <v>0.89781125639567938</v>
+        <v>0.89795338260375213</v>
       </c>
       <c r="AV22" s="5">
         <v>5943</v>
@@ -3758,14 +3758,14 @@
       </c>
       <c r="BH22" s="6">
         <f t="shared" si="22"/>
-        <v>4617</v>
+        <v>4619</v>
       </c>
       <c r="BI22" s="5">
-        <v>6510</v>
+        <v>6512</v>
       </c>
       <c r="BJ22" s="7">
         <f t="shared" si="23"/>
-        <v>0.90241197671194895</v>
+        <v>0.90268921541447189</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3783,14 +3783,14 @@
       </c>
       <c r="E23" s="6">
         <f t="shared" si="0"/>
-        <v>6038</v>
+        <v>6039</v>
       </c>
       <c r="F23" s="5">
-        <v>6619</v>
+        <v>6620</v>
       </c>
       <c r="G23" s="7">
         <f t="shared" si="1"/>
-        <v>0.6982067510548523</v>
+        <v>0.69831223628691985</v>
       </c>
       <c r="H23" s="3">
         <v>9486</v>
@@ -3800,14 +3800,14 @@
       </c>
       <c r="J23" s="6">
         <f t="shared" si="2"/>
-        <v>6013</v>
+        <v>6014</v>
       </c>
       <c r="K23" s="5">
-        <v>6583</v>
+        <v>6584</v>
       </c>
       <c r="L23" s="7">
         <f t="shared" si="3"/>
-        <v>0.69397006114273663</v>
+        <v>0.69407547965422733</v>
       </c>
       <c r="M23" s="2">
         <v>11077</v>
@@ -3817,14 +3817,14 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" si="4"/>
-        <v>6621</v>
+        <v>6622</v>
       </c>
       <c r="P23" s="5">
-        <v>7933</v>
+        <v>7934</v>
       </c>
       <c r="Q23" s="7">
         <f t="shared" si="5"/>
-        <v>0.7161686377177936</v>
+        <v>0.71625891486864679</v>
       </c>
       <c r="R23" s="5">
         <v>9575</v>
@@ -3834,14 +3834,14 @@
       </c>
       <c r="T23" s="6">
         <f t="shared" si="6"/>
-        <v>5225</v>
+        <v>5226</v>
       </c>
       <c r="U23" s="5">
-        <v>6633</v>
+        <v>6634</v>
       </c>
       <c r="V23" s="7">
         <f t="shared" si="7"/>
-        <v>0.69274151436031328</v>
+        <v>0.69284595300261098</v>
       </c>
       <c r="W23" s="5">
         <v>9750</v>
@@ -3851,14 +3851,14 @@
       </c>
       <c r="Y23" s="6">
         <f t="shared" si="8"/>
-        <v>5175</v>
+        <v>5176</v>
       </c>
       <c r="Z23" s="5">
-        <v>6690</v>
+        <v>6691</v>
       </c>
       <c r="AA23" s="7">
         <f t="shared" si="9"/>
-        <v>0.68615384615384611</v>
+        <v>0.68625641025641027</v>
       </c>
       <c r="AB23" s="6">
         <v>11436</v>
@@ -3868,14 +3868,14 @@
       </c>
       <c r="AD23" s="6">
         <f t="shared" si="10"/>
-        <v>5997</v>
+        <v>5998</v>
       </c>
       <c r="AE23" s="5">
-        <v>8193</v>
+        <v>8194</v>
       </c>
       <c r="AF23" s="7">
         <f t="shared" si="11"/>
-        <v>0.71642182581322145</v>
+        <v>0.71650926897516609</v>
       </c>
       <c r="AG23" s="5">
         <v>9837</v>
@@ -3885,14 +3885,14 @@
       </c>
       <c r="AI23" s="6">
         <f t="shared" si="12"/>
-        <v>5047</v>
+        <v>5048</v>
       </c>
       <c r="AJ23" s="5">
-        <v>6813</v>
+        <v>6814</v>
       </c>
       <c r="AK23" s="7">
         <f t="shared" si="13"/>
-        <v>0.69258920402561752</v>
+        <v>0.69269086103486832</v>
       </c>
       <c r="AL23" s="5">
         <v>9887</v>
@@ -3902,14 +3902,14 @@
       </c>
       <c r="AN23" s="6">
         <f t="shared" si="14"/>
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="AO23" s="5">
-        <v>6921</v>
+        <v>6922</v>
       </c>
       <c r="AP23" s="7">
         <f t="shared" si="15"/>
-        <v>0.70001011429149385</v>
+        <v>0.70011125720643264</v>
       </c>
       <c r="AQ23" s="6">
         <v>10570</v>
@@ -3919,14 +3919,14 @@
       </c>
       <c r="AS23" s="6">
         <f t="shared" si="16"/>
-        <v>6300</v>
+        <v>6301</v>
       </c>
       <c r="AT23" s="5">
-        <v>8476</v>
+        <v>8477</v>
       </c>
       <c r="AU23" s="7">
         <f t="shared" si="17"/>
-        <v>0.80189214758751182</v>
+        <v>0.80198675496688743</v>
       </c>
       <c r="AV23" s="5">
         <v>8848</v>
@@ -3936,14 +3936,14 @@
       </c>
       <c r="AX23" s="6">
         <f t="shared" si="18"/>
-        <v>4995</v>
+        <v>4996</v>
       </c>
       <c r="AY23" s="5">
-        <v>6958</v>
+        <v>6959</v>
       </c>
       <c r="AZ23" s="7">
         <f t="shared" si="19"/>
-        <v>0.78639240506329111</v>
+        <v>0.78650542495479203</v>
       </c>
       <c r="BA23" s="5">
         <v>8869</v>
@@ -3953,14 +3953,14 @@
       </c>
       <c r="BC23" s="6">
         <f t="shared" si="20"/>
-        <v>5100</v>
+        <v>5101</v>
       </c>
       <c r="BD23" s="5">
-        <v>7064</v>
+        <v>7065</v>
       </c>
       <c r="BE23" s="7">
         <f t="shared" si="21"/>
-        <v>0.79648212876310742</v>
+        <v>0.79659488104634124</v>
       </c>
       <c r="BF23" s="5">
         <v>10711</v>
@@ -3970,14 +3970,14 @@
       </c>
       <c r="BH23" s="6">
         <f t="shared" si="22"/>
-        <v>6493</v>
+        <v>6494</v>
       </c>
       <c r="BI23" s="5">
-        <v>8695</v>
+        <v>8696</v>
       </c>
       <c r="BJ23" s="7">
         <f t="shared" si="23"/>
-        <v>0.81178227989916907</v>
+        <v>0.8118756418635048</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -3995,14 +3995,14 @@
       </c>
       <c r="E24" s="6">
         <f t="shared" si="0"/>
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="F24" s="5">
-        <v>4542</v>
+        <v>4543</v>
       </c>
       <c r="G24" s="7">
         <f t="shared" si="1"/>
-        <v>0.76996101034073572</v>
+        <v>0.77013053059840653</v>
       </c>
       <c r="H24" s="3">
         <v>5806</v>
@@ -4012,14 +4012,14 @@
       </c>
       <c r="J24" s="6">
         <f t="shared" si="2"/>
-        <v>3936</v>
+        <v>3937</v>
       </c>
       <c r="K24" s="5">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="L24" s="7">
         <f t="shared" si="3"/>
-        <v>0.77781605235962792</v>
+        <v>0.77798828797795383</v>
       </c>
       <c r="M24" s="2">
         <v>6586</v>
@@ -4029,14 +4029,14 @@
       </c>
       <c r="O24" s="6">
         <f t="shared" si="4"/>
-        <v>4278</v>
+        <v>4279</v>
       </c>
       <c r="P24" s="5">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="Q24" s="7">
         <f t="shared" si="5"/>
-        <v>0.79532341330094136</v>
+        <v>0.79547525053143031</v>
       </c>
       <c r="R24" s="5">
         <v>5878</v>
@@ -4046,14 +4046,14 @@
       </c>
       <c r="T24" s="6">
         <f t="shared" si="6"/>
-        <v>3485</v>
+        <v>3486</v>
       </c>
       <c r="U24" s="5">
-        <v>4520</v>
+        <v>4521</v>
       </c>
       <c r="V24" s="7">
         <f t="shared" si="7"/>
-        <v>0.76896903708744468</v>
+        <v>0.7691391629806057</v>
       </c>
       <c r="W24" s="5">
         <v>5897</v>
@@ -4063,14 +4063,14 @@
       </c>
       <c r="Y24" s="6">
         <f t="shared" si="8"/>
-        <v>3447</v>
+        <v>3449</v>
       </c>
       <c r="Z24" s="5">
-        <v>4518</v>
+        <v>4520</v>
       </c>
       <c r="AA24" s="7">
         <f t="shared" si="9"/>
-        <v>0.76615228082075637</v>
+        <v>0.76649143632355432</v>
       </c>
       <c r="AB24" s="6">
         <v>6699</v>
@@ -4080,14 +4080,14 @@
       </c>
       <c r="AD24" s="6">
         <f t="shared" si="10"/>
-        <v>3805</v>
+        <v>3807</v>
       </c>
       <c r="AE24" s="5">
-        <v>5294</v>
+        <v>5296</v>
       </c>
       <c r="AF24" s="7">
         <f t="shared" si="11"/>
-        <v>0.79026720406030748</v>
+        <v>0.79056575608299751</v>
       </c>
       <c r="AG24" s="5">
         <v>5948</v>
@@ -4097,14 +4097,14 @@
       </c>
       <c r="AI24" s="6">
         <f t="shared" si="12"/>
-        <v>3359</v>
+        <v>3361</v>
       </c>
       <c r="AJ24" s="5">
-        <v>4601</v>
+        <v>4603</v>
       </c>
       <c r="AK24" s="7">
         <f t="shared" si="13"/>
-        <v>0.77353732347007398</v>
+        <v>0.77387357094821785</v>
       </c>
       <c r="AL24" s="5">
         <v>5965</v>
@@ -4114,14 +4114,14 @@
       </c>
       <c r="AN24" s="6">
         <f t="shared" si="14"/>
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="AO24" s="5">
-        <v>4712</v>
+        <v>4714</v>
       </c>
       <c r="AP24" s="7">
         <f t="shared" si="15"/>
-        <v>0.78994132439228837</v>
+        <v>0.79027661357921208</v>
       </c>
       <c r="AQ24" s="6">
         <v>6810</v>
@@ -4131,14 +4131,14 @@
       </c>
       <c r="AS24" s="6">
         <f t="shared" si="16"/>
-        <v>4237</v>
+        <v>4239</v>
       </c>
       <c r="AT24" s="5">
-        <v>5557</v>
+        <v>5559</v>
       </c>
       <c r="AU24" s="7">
         <f t="shared" si="17"/>
-        <v>0.81600587371512479</v>
+        <v>0.81629955947136568</v>
       </c>
       <c r="AV24" s="5">
         <v>6017</v>
@@ -4148,14 +4148,14 @@
       </c>
       <c r="AX24" s="6">
         <f t="shared" si="18"/>
-        <v>3579</v>
+        <v>3581</v>
       </c>
       <c r="AY24" s="5">
-        <v>4809</v>
+        <v>4811</v>
       </c>
       <c r="AZ24" s="7">
         <f t="shared" si="19"/>
-        <v>0.79923549941831473</v>
+        <v>0.79956789097556924</v>
       </c>
       <c r="BA24" s="5">
         <v>6141</v>
@@ -4165,14 +4165,14 @@
       </c>
       <c r="BC24" s="6">
         <f t="shared" si="20"/>
-        <v>3560</v>
+        <v>3562</v>
       </c>
       <c r="BD24" s="5">
-        <v>4877</v>
+        <v>4879</v>
       </c>
       <c r="BE24" s="7">
         <f t="shared" si="21"/>
-        <v>0.79417033056505459</v>
+        <v>0.79449601042175544</v>
       </c>
       <c r="BF24" s="5">
         <v>7097</v>
@@ -4182,14 +4182,14 @@
       </c>
       <c r="BH24" s="6">
         <f t="shared" si="22"/>
-        <v>4472</v>
+        <v>4474</v>
       </c>
       <c r="BI24" s="5">
-        <v>5747</v>
+        <v>5749</v>
       </c>
       <c r="BJ24" s="7">
         <f t="shared" si="23"/>
-        <v>0.80977877976609836</v>
+        <v>0.81006058898125965</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4419,14 +4419,14 @@
       </c>
       <c r="E26" s="6">
         <f t="shared" si="0"/>
-        <v>10112</v>
+        <v>10114</v>
       </c>
       <c r="F26" s="5">
-        <v>11375</v>
+        <v>11377</v>
       </c>
       <c r="G26" s="7">
         <f t="shared" si="1"/>
-        <v>0.68681318681318682</v>
+        <v>0.68693394517570339</v>
       </c>
       <c r="H26" s="3">
         <v>16580</v>
@@ -4436,14 +4436,14 @@
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>10070</v>
+        <v>10073</v>
       </c>
       <c r="K26" s="5">
-        <v>11296</v>
+        <v>11299</v>
       </c>
       <c r="L26" s="7">
         <f t="shared" si="3"/>
-        <v>0.68130277442702047</v>
+        <v>0.68148371531966223</v>
       </c>
       <c r="M26" s="2">
         <v>25396</v>
@@ -4453,14 +4453,14 @@
       </c>
       <c r="O26" s="6">
         <f t="shared" si="4"/>
-        <v>14654</v>
+        <v>14659</v>
       </c>
       <c r="P26" s="5">
-        <v>18720</v>
+        <v>18725</v>
       </c>
       <c r="Q26" s="7">
         <f t="shared" si="5"/>
-        <v>0.7371239565285872</v>
+        <v>0.73732083792723269</v>
       </c>
       <c r="R26" s="5">
         <v>16475</v>
@@ -4470,14 +4470,14 @@
       </c>
       <c r="T26" s="6">
         <f t="shared" si="6"/>
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="U26" s="5">
-        <v>11299</v>
+        <v>11302</v>
       </c>
       <c r="V26" s="7">
         <f t="shared" si="7"/>
-        <v>0.68582701062215479</v>
+        <v>0.68600910470409715</v>
       </c>
       <c r="W26" s="5">
         <v>16675</v>
@@ -4487,14 +4487,14 @@
       </c>
       <c r="Y26" s="6">
         <f t="shared" si="8"/>
-        <v>7988</v>
+        <v>7990</v>
       </c>
       <c r="Z26" s="5">
-        <v>11452</v>
+        <v>11454</v>
       </c>
       <c r="AA26" s="7">
         <f t="shared" si="9"/>
-        <v>0.68677661169415294</v>
+        <v>0.68689655172413788</v>
       </c>
       <c r="AB26" s="6">
         <v>25656</v>
@@ -4504,14 +4504,14 @@
       </c>
       <c r="AD26" s="6">
         <f t="shared" si="10"/>
-        <v>12766</v>
+        <v>12771</v>
       </c>
       <c r="AE26" s="5">
-        <v>19356</v>
+        <v>19361</v>
       </c>
       <c r="AF26" s="7">
         <f t="shared" si="11"/>
-        <v>0.75444340505144991</v>
+        <v>0.75463829123791704</v>
       </c>
       <c r="AG26" s="5">
         <v>15844</v>
@@ -4521,14 +4521,14 @@
       </c>
       <c r="AI26" s="6">
         <f t="shared" si="12"/>
-        <v>7385</v>
+        <v>7387</v>
       </c>
       <c r="AJ26" s="5">
-        <v>11195</v>
+        <v>11197</v>
       </c>
       <c r="AK26" s="7">
         <f t="shared" si="13"/>
-        <v>0.70657662206513505</v>
+        <v>0.70670285281494571</v>
       </c>
       <c r="AL26" s="5">
         <v>16081</v>
@@ -4538,14 +4538,14 @@
       </c>
       <c r="AN26" s="6">
         <f t="shared" si="14"/>
-        <v>3584</v>
+        <v>3586</v>
       </c>
       <c r="AO26" s="5">
-        <v>11424</v>
+        <v>11426</v>
       </c>
       <c r="AP26" s="7">
         <f t="shared" si="15"/>
-        <v>0.71040358186679931</v>
+        <v>0.71052795224177601</v>
       </c>
       <c r="AQ26" s="6">
         <v>26317</v>
@@ -4555,14 +4555,14 @@
       </c>
       <c r="AS26" s="6">
         <f t="shared" si="16"/>
-        <v>13379</v>
+        <v>13381</v>
       </c>
       <c r="AT26" s="5">
-        <v>20105</v>
+        <v>20107</v>
       </c>
       <c r="AU26" s="7">
         <f t="shared" si="17"/>
-        <v>0.76395485807652852</v>
+        <v>0.76403085458068931</v>
       </c>
       <c r="AV26" s="5">
         <v>15987</v>
@@ -4572,14 +4572,14 @@
       </c>
       <c r="AX26" s="6">
         <f t="shared" si="18"/>
-        <v>7194</v>
+        <v>7195</v>
       </c>
       <c r="AY26" s="5">
-        <v>11382</v>
+        <v>11383</v>
       </c>
       <c r="AZ26" s="7">
         <f t="shared" si="19"/>
-        <v>0.7119534621880278</v>
+        <v>0.71201601301057105</v>
       </c>
       <c r="BA26" s="5">
         <v>16133</v>
@@ -4589,14 +4589,14 @@
       </c>
       <c r="BC26" s="6">
         <f t="shared" si="20"/>
-        <v>7246</v>
+        <v>7247</v>
       </c>
       <c r="BD26" s="5">
-        <v>11568</v>
+        <v>11569</v>
       </c>
       <c r="BE26" s="7">
         <f t="shared" si="21"/>
-        <v>0.71703960825636892</v>
+        <v>0.71710159300812004</v>
       </c>
       <c r="BF26" s="5">
         <v>26642</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH26" s="6">
         <f t="shared" si="22"/>
-        <v>13813</v>
+        <v>13815</v>
       </c>
       <c r="BI26" s="5">
-        <v>20667</v>
+        <v>20669</v>
       </c>
       <c r="BJ26" s="7">
         <f t="shared" si="23"/>
-        <v>0.77573005029652431</v>
+        <v>0.77580511973575561</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="E27" s="6">
         <f t="shared" si="0"/>
-        <v>85615</v>
+        <v>85618</v>
       </c>
       <c r="F27" s="5">
-        <v>97162</v>
+        <v>97165</v>
       </c>
       <c r="G27" s="7">
         <f t="shared" si="1"/>
-        <v>0.86108280085432964</v>
+        <v>0.86110938787808966</v>
       </c>
       <c r="H27" s="3">
         <v>111842</v>
@@ -4648,14 +4648,14 @@
       </c>
       <c r="J27" s="6">
         <f t="shared" si="2"/>
-        <v>89152</v>
+        <v>89155</v>
       </c>
       <c r="K27" s="5">
-        <v>97011</v>
+        <v>97014</v>
       </c>
       <c r="L27" s="7">
         <f t="shared" si="3"/>
-        <v>0.86739328695838769</v>
+        <v>0.86742011051304524</v>
       </c>
       <c r="M27" s="2">
         <v>156288</v>
@@ -4665,14 +4665,14 @@
       </c>
       <c r="O27" s="6">
         <f t="shared" si="4"/>
-        <v>107176</v>
+        <v>107183</v>
       </c>
       <c r="P27" s="5">
-        <v>138423</v>
+        <v>138430</v>
       </c>
       <c r="Q27" s="7">
         <f t="shared" si="5"/>
-        <v>0.88569179975429979</v>
+        <v>0.8857365888615889</v>
       </c>
       <c r="R27" s="5">
         <v>113087</v>
@@ -4682,14 +4682,14 @@
       </c>
       <c r="T27" s="6">
         <f t="shared" si="6"/>
-        <v>70961</v>
+        <v>70966</v>
       </c>
       <c r="U27" s="5">
-        <v>99659</v>
+        <v>99664</v>
       </c>
       <c r="V27" s="7">
         <f t="shared" si="7"/>
-        <v>0.88125956122277538</v>
+        <v>0.88130377496971357</v>
       </c>
       <c r="W27" s="5">
         <v>116164</v>
@@ -4699,14 +4699,14 @@
       </c>
       <c r="Y27" s="6">
         <f t="shared" si="8"/>
-        <v>68635</v>
+        <v>68640</v>
       </c>
       <c r="Z27" s="5">
-        <v>102900</v>
+        <v>102905</v>
       </c>
       <c r="AA27" s="7">
         <f t="shared" si="9"/>
-        <v>0.88581660411142871</v>
+        <v>0.88585964670638062</v>
       </c>
       <c r="AB27" s="6">
         <v>165468</v>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="AD27" s="6">
         <f t="shared" si="10"/>
-        <v>87053</v>
+        <v>87058</v>
       </c>
       <c r="AE27" s="5">
-        <v>147894</v>
+        <v>147899</v>
       </c>
       <c r="AF27" s="7">
         <f t="shared" si="11"/>
-        <v>0.89379215316556671</v>
+        <v>0.89382237048855373</v>
       </c>
       <c r="AG27" s="5">
         <v>116084</v>
@@ -4733,14 +4733,14 @@
       </c>
       <c r="AI27" s="6">
         <f t="shared" si="12"/>
-        <v>63654</v>
+        <v>63657</v>
       </c>
       <c r="AJ27" s="5">
-        <v>102269</v>
+        <v>102272</v>
       </c>
       <c r="AK27" s="7">
         <f t="shared" si="13"/>
-        <v>0.88099135109058957</v>
+        <v>0.88101719444540161</v>
       </c>
       <c r="AL27" s="5">
         <v>117992</v>
@@ -4750,14 +4750,14 @@
       </c>
       <c r="AN27" s="6">
         <f t="shared" si="14"/>
-        <v>33231</v>
+        <v>33234</v>
       </c>
       <c r="AO27" s="5">
-        <v>104347</v>
+        <v>104350</v>
       </c>
       <c r="AP27" s="7">
         <f t="shared" si="15"/>
-        <v>0.88435656654688455</v>
+        <v>0.88438199199945755</v>
       </c>
       <c r="AQ27" s="6">
         <v>170879</v>
@@ -4767,14 +4767,14 @@
       </c>
       <c r="AS27" s="6">
         <f t="shared" si="16"/>
-        <v>94816</v>
+        <v>94820</v>
       </c>
       <c r="AT27" s="5">
-        <v>153095</v>
+        <v>153099</v>
       </c>
       <c r="AU27" s="7">
         <f t="shared" si="17"/>
-        <v>0.89592635724694081</v>
+        <v>0.89594976562362838</v>
       </c>
       <c r="AV27" s="5">
         <v>116485</v>
@@ -4784,14 +4784,14 @@
       </c>
       <c r="AX27" s="6">
         <f t="shared" si="18"/>
-        <v>62243</v>
+        <v>62246</v>
       </c>
       <c r="AY27" s="5">
-        <v>105080</v>
+        <v>105083</v>
       </c>
       <c r="AZ27" s="7">
         <f t="shared" si="19"/>
-        <v>0.90209039790530965</v>
+        <v>0.90211615229428677</v>
       </c>
       <c r="BA27" s="5">
         <v>117017</v>
@@ -4801,14 +4801,14 @@
       </c>
       <c r="BC27" s="6">
         <f t="shared" si="20"/>
-        <v>62160</v>
+        <v>62163</v>
       </c>
       <c r="BD27" s="5">
-        <v>106742</v>
+        <v>106745</v>
       </c>
       <c r="BE27" s="7">
         <f t="shared" si="21"/>
-        <v>0.9121922455711563</v>
+        <v>0.91221788287171945</v>
       </c>
       <c r="BF27" s="5">
         <v>172738</v>
@@ -4818,14 +4818,14 @@
       </c>
       <c r="BH27" s="6">
         <f t="shared" si="22"/>
-        <v>103538</v>
+        <v>103542</v>
       </c>
       <c r="BI27" s="5">
-        <v>156642</v>
+        <v>156646</v>
       </c>
       <c r="BJ27" s="7">
         <f t="shared" si="23"/>
-        <v>0.90681841864557888</v>
+        <v>0.90684157510217789</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4843,14 +4843,14 @@
       </c>
       <c r="E28" s="6">
         <f t="shared" si="0"/>
-        <v>250550</v>
+        <v>250551</v>
       </c>
       <c r="F28" s="5">
-        <v>316191</v>
+        <v>316192</v>
       </c>
       <c r="G28" s="7">
         <f t="shared" si="1"/>
-        <v>0.83927504956960053</v>
+        <v>0.8392777038989444</v>
       </c>
       <c r="H28" s="3">
         <v>377506</v>
@@ -4860,14 +4860,14 @@
       </c>
       <c r="J28" s="6">
         <f t="shared" si="2"/>
-        <v>278960</v>
+        <v>278961</v>
       </c>
       <c r="K28" s="5">
-        <v>316486</v>
+        <v>316487</v>
       </c>
       <c r="L28" s="7">
         <f t="shared" si="3"/>
-        <v>0.83836018500368203</v>
+        <v>0.83836283396820188</v>
       </c>
       <c r="M28" s="2">
         <v>622937</v>
@@ -4877,14 +4877,14 @@
       </c>
       <c r="O28" s="6">
         <f t="shared" si="4"/>
-        <v>331112</v>
+        <v>331114</v>
       </c>
       <c r="P28" s="5">
-        <v>549580</v>
+        <v>549582</v>
       </c>
       <c r="Q28" s="7">
         <f t="shared" si="5"/>
-        <v>0.88224009811586079</v>
+        <v>0.88224330871340118</v>
       </c>
       <c r="R28" s="5">
         <v>379798</v>
@@ -4894,14 +4894,14 @@
       </c>
       <c r="T28" s="6">
         <f t="shared" si="6"/>
-        <v>170717</v>
+        <v>170718</v>
       </c>
       <c r="U28" s="5">
-        <v>318467</v>
+        <v>318468</v>
       </c>
       <c r="V28" s="7">
         <f t="shared" si="7"/>
-        <v>0.83851679050442607</v>
+        <v>0.83851942348300934</v>
       </c>
       <c r="W28" s="5">
         <v>378910</v>
@@ -4911,14 +4911,14 @@
       </c>
       <c r="Y28" s="6">
         <f t="shared" si="8"/>
-        <v>163230</v>
+        <v>163231</v>
       </c>
       <c r="Z28" s="5">
-        <v>322475</v>
+        <v>322476</v>
       </c>
       <c r="AA28" s="7">
         <f t="shared" si="9"/>
-        <v>0.85105961837903465</v>
+        <v>0.85106225752817288</v>
       </c>
       <c r="AB28" s="6">
         <v>628364</v>
@@ -4928,14 +4928,14 @@
       </c>
       <c r="AD28" s="6">
         <f t="shared" si="10"/>
-        <v>254359</v>
+        <v>254361</v>
       </c>
       <c r="AE28" s="5">
-        <v>559991</v>
+        <v>559993</v>
       </c>
       <c r="AF28" s="7">
         <f t="shared" si="11"/>
-        <v>0.89118886505274009</v>
+        <v>0.8911920479212686</v>
       </c>
       <c r="AG28" s="5">
         <v>375124</v>
@@ -4945,14 +4945,14 @@
       </c>
       <c r="AI28" s="6">
         <f t="shared" si="12"/>
-        <v>152976</v>
+        <v>152978</v>
       </c>
       <c r="AJ28" s="5">
-        <v>323063</v>
+        <v>323065</v>
       </c>
       <c r="AK28" s="7">
         <f t="shared" si="13"/>
-        <v>0.86121655772491235</v>
+        <v>0.86122188929527299</v>
       </c>
       <c r="AL28" s="5">
         <v>368781</v>
@@ -4962,14 +4962,14 @@
       </c>
       <c r="AN28" s="6">
         <f t="shared" si="14"/>
-        <v>60408</v>
+        <v>60410</v>
       </c>
       <c r="AO28" s="5">
-        <v>328467</v>
+        <v>328469</v>
       </c>
       <c r="AP28" s="7">
         <f t="shared" si="15"/>
-        <v>0.89068308833698051</v>
+        <v>0.89068851160987139</v>
       </c>
       <c r="AQ28" s="6">
         <v>617418</v>
@@ -4979,14 +4979,14 @@
       </c>
       <c r="AS28" s="6">
         <f t="shared" si="16"/>
-        <v>275502</v>
+        <v>275504</v>
       </c>
       <c r="AT28" s="5">
-        <v>571901</v>
+        <v>571903</v>
       </c>
       <c r="AU28" s="7">
         <f t="shared" si="17"/>
-        <v>0.92627846936759217</v>
+        <v>0.9262817086641465</v>
       </c>
       <c r="AV28" s="5">
         <v>357852</v>
@@ -4996,14 +4996,14 @@
       </c>
       <c r="AX28" s="6">
         <f t="shared" si="18"/>
-        <v>144540</v>
+        <v>144542</v>
       </c>
       <c r="AY28" s="5">
-        <v>331103</v>
+        <v>331105</v>
       </c>
       <c r="AZ28" s="7">
         <f t="shared" si="19"/>
-        <v>0.92525122117523451</v>
+        <v>0.92525681007790928</v>
       </c>
       <c r="BA28" s="5">
         <v>359943</v>
@@ -5013,14 +5013,14 @@
       </c>
       <c r="BC28" s="6">
         <f t="shared" si="20"/>
-        <v>140363</v>
+        <v>140365</v>
       </c>
       <c r="BD28" s="5">
-        <v>335595</v>
+        <v>335597</v>
       </c>
       <c r="BE28" s="7">
         <f t="shared" si="21"/>
-        <v>0.93235595635975699</v>
+        <v>0.93236151279508139</v>
       </c>
       <c r="BF28" s="5">
         <v>622234</v>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="BH28" s="6">
         <f t="shared" si="22"/>
-        <v>281147</v>
+        <v>281150</v>
       </c>
       <c r="BI28" s="5">
-        <v>582337</v>
+        <v>582340</v>
       </c>
       <c r="BJ28" s="7">
         <f t="shared" si="23"/>
-        <v>0.93588103510897824</v>
+        <v>0.93588585644628874</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5055,14 +5055,14 @@
       </c>
       <c r="E29" s="6">
         <f t="shared" si="0"/>
-        <v>89407</v>
+        <v>89408</v>
       </c>
       <c r="F29" s="5">
-        <v>101493</v>
+        <v>101494</v>
       </c>
       <c r="G29" s="7">
         <f t="shared" si="1"/>
-        <v>0.93617865180976279</v>
+        <v>0.9361878758808988</v>
       </c>
       <c r="H29" s="3">
         <v>108534</v>
@@ -5072,14 +5072,14 @@
       </c>
       <c r="J29" s="6">
         <f t="shared" si="2"/>
-        <v>89384</v>
+        <v>89385</v>
       </c>
       <c r="K29" s="5">
-        <v>101415</v>
+        <v>101416</v>
       </c>
       <c r="L29" s="7">
         <f t="shared" si="3"/>
-        <v>0.93440765105865442</v>
+        <v>0.93441686476127295</v>
       </c>
       <c r="M29" s="2">
         <v>155259</v>
@@ -5089,14 +5089,14 @@
       </c>
       <c r="O29" s="6">
         <f t="shared" si="4"/>
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="P29" s="5">
-        <v>145430</v>
+        <v>145432</v>
       </c>
       <c r="Q29" s="7">
         <f t="shared" si="5"/>
-        <v>0.93669288092799774</v>
+        <v>0.93670576262889749</v>
       </c>
       <c r="R29" s="5">
         <v>111838</v>
@@ -5106,14 +5106,14 @@
       </c>
       <c r="T29" s="6">
         <f t="shared" si="6"/>
-        <v>61571</v>
+        <v>61573</v>
       </c>
       <c r="U29" s="5">
-        <v>103720</v>
+        <v>103722</v>
       </c>
       <c r="V29" s="7">
         <f t="shared" si="7"/>
-        <v>0.92741286503692844</v>
+        <v>0.92743074804628123</v>
       </c>
       <c r="W29" s="5">
         <v>113722</v>
@@ -5123,14 +5123,14 @@
       </c>
       <c r="Y29" s="6">
         <f t="shared" si="8"/>
-        <v>58673</v>
+        <v>58675</v>
       </c>
       <c r="Z29" s="5">
-        <v>105046</v>
+        <v>105048</v>
       </c>
       <c r="AA29" s="7">
         <f t="shared" si="9"/>
-        <v>0.92370869312885806</v>
+        <v>0.92372627987548583</v>
       </c>
       <c r="AB29" s="6">
         <v>160157</v>
@@ -5140,14 +5140,14 @@
       </c>
       <c r="AD29" s="6">
         <f t="shared" si="10"/>
-        <v>76483</v>
+        <v>76485</v>
       </c>
       <c r="AE29" s="5">
-        <v>149210</v>
+        <v>149212</v>
       </c>
       <c r="AF29" s="7">
         <f t="shared" si="11"/>
-        <v>0.93164832008591569</v>
+        <v>0.93166080783231453</v>
       </c>
       <c r="AG29" s="5">
         <v>115309</v>
@@ -5157,14 +5157,14 @@
       </c>
       <c r="AI29" s="6">
         <f t="shared" si="12"/>
-        <v>61728</v>
+        <v>61729</v>
       </c>
       <c r="AJ29" s="5">
-        <v>106347</v>
+        <v>106348</v>
       </c>
       <c r="AK29" s="7">
         <f t="shared" si="13"/>
-        <v>0.92227839977798787</v>
+        <v>0.92228707212793448</v>
       </c>
       <c r="AL29" s="5">
         <v>116530</v>
@@ -5174,14 +5174,14 @@
       </c>
       <c r="AN29" s="6">
         <f t="shared" si="14"/>
-        <v>22820</v>
+        <v>22821</v>
       </c>
       <c r="AO29" s="5">
-        <v>107884</v>
+        <v>107885</v>
       </c>
       <c r="AP29" s="7">
         <f t="shared" si="15"/>
-        <v>0.92580451385909213</v>
+        <v>0.92581309534025569</v>
       </c>
       <c r="AQ29" s="6">
         <v>164389</v>
@@ -5191,14 +5191,14 @@
       </c>
       <c r="AS29" s="6">
         <f t="shared" si="16"/>
-        <v>81642</v>
+        <v>81643</v>
       </c>
       <c r="AT29" s="5">
-        <v>153098</v>
+        <v>153099</v>
       </c>
       <c r="AU29" s="7">
         <f t="shared" si="17"/>
-        <v>0.9313153556503172</v>
+        <v>0.93132143878240026</v>
       </c>
       <c r="AV29" s="5">
         <v>118862</v>
@@ -5208,14 +5208,14 @@
       </c>
       <c r="AX29" s="6">
         <f t="shared" si="18"/>
-        <v>54652</v>
+        <v>54653</v>
       </c>
       <c r="AY29" s="5">
-        <v>109745</v>
+        <v>109746</v>
       </c>
       <c r="AZ29" s="7">
         <f t="shared" si="19"/>
-        <v>0.92329760562669316</v>
+        <v>0.9233060187444263</v>
       </c>
       <c r="BA29" s="5">
         <v>119046</v>
@@ -5225,14 +5225,14 @@
       </c>
       <c r="BC29" s="6">
         <f t="shared" si="20"/>
-        <v>53036</v>
+        <v>53037</v>
       </c>
       <c r="BD29" s="5">
-        <v>111243</v>
+        <v>111244</v>
       </c>
       <c r="BE29" s="7">
         <f t="shared" si="21"/>
-        <v>0.93445390857315658</v>
+        <v>0.9344623086873981</v>
       </c>
       <c r="BF29" s="5">
         <v>167253</v>
@@ -5242,14 +5242,14 @@
       </c>
       <c r="BH29" s="6">
         <f t="shared" si="22"/>
-        <v>89126</v>
+        <v>89127</v>
       </c>
       <c r="BI29" s="5">
-        <v>156295</v>
+        <v>156296</v>
       </c>
       <c r="BJ29" s="7">
         <f t="shared" si="23"/>
-        <v>0.93448249059807598</v>
+        <v>0.93448846956407361</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5301,14 +5301,14 @@
       </c>
       <c r="O30" s="6">
         <f t="shared" si="4"/>
-        <v>169129</v>
+        <v>169130</v>
       </c>
       <c r="P30" s="5">
-        <v>226894</v>
+        <v>226895</v>
       </c>
       <c r="Q30" s="7">
         <f t="shared" si="5"/>
-        <v>0.90775028805530666</v>
+        <v>0.9077542888234541</v>
       </c>
       <c r="R30" s="5">
         <v>151431</v>
@@ -5318,14 +5318,14 @@
       </c>
       <c r="T30" s="6">
         <f t="shared" si="6"/>
-        <v>94131</v>
+        <v>94132</v>
       </c>
       <c r="U30" s="5">
-        <v>135554</v>
+        <v>135555</v>
       </c>
       <c r="V30" s="7">
         <f t="shared" si="7"/>
-        <v>0.89515356829182924</v>
+        <v>0.89516017195950626</v>
       </c>
       <c r="W30" s="5">
         <v>154416</v>
@@ -5335,14 +5335,14 @@
       </c>
       <c r="Y30" s="6">
         <f t="shared" si="8"/>
-        <v>93957</v>
+        <v>93958</v>
       </c>
       <c r="Z30" s="5">
-        <v>138537</v>
+        <v>138538</v>
       </c>
       <c r="AA30" s="7">
         <f t="shared" si="9"/>
-        <v>0.89716739198010564</v>
+        <v>0.89717386799295407</v>
       </c>
       <c r="AB30" s="6">
         <v>259264</v>
@@ -5352,14 +5352,14 @@
       </c>
       <c r="AD30" s="6">
         <f t="shared" si="10"/>
-        <v>140055</v>
+        <v>140057</v>
       </c>
       <c r="AE30" s="5">
-        <v>234126</v>
+        <v>234128</v>
       </c>
       <c r="AF30" s="7">
         <f t="shared" si="11"/>
-        <v>0.90304091582325352</v>
+        <v>0.90304862996790913</v>
       </c>
       <c r="AG30" s="5">
         <v>153178</v>
@@ -5369,14 +5369,14 @@
       </c>
       <c r="AI30" s="6">
         <f t="shared" si="12"/>
-        <v>82963</v>
+        <v>82964</v>
       </c>
       <c r="AJ30" s="5">
-        <v>137367</v>
+        <v>137368</v>
       </c>
       <c r="AK30" s="7">
         <f t="shared" si="13"/>
-        <v>0.89678021648017336</v>
+        <v>0.89678674483280885</v>
       </c>
       <c r="AL30" s="5">
         <v>156106</v>
@@ -5386,14 +5386,14 @@
       </c>
       <c r="AN30" s="6">
         <f t="shared" si="14"/>
-        <v>37358</v>
+        <v>37359</v>
       </c>
       <c r="AO30" s="5">
-        <v>141050</v>
+        <v>141051</v>
       </c>
       <c r="AP30" s="7">
         <f t="shared" si="15"/>
-        <v>0.9035527141813896</v>
+        <v>0.90355912008507044</v>
       </c>
       <c r="AQ30" s="6">
         <v>266513</v>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="AS30" s="6">
         <f t="shared" si="16"/>
-        <v>145548</v>
+        <v>145550</v>
       </c>
       <c r="AT30" s="5">
-        <v>242504</v>
+        <v>242506</v>
       </c>
       <c r="AU30" s="7">
         <f t="shared" si="17"/>
-        <v>0.90991433813735167</v>
+        <v>0.90992184246171859</v>
       </c>
       <c r="AV30" s="5">
         <v>155103</v>
@@ -5420,14 +5420,14 @@
       </c>
       <c r="AX30" s="6">
         <f t="shared" si="18"/>
-        <v>81275</v>
+        <v>81276</v>
       </c>
       <c r="AY30" s="5">
-        <v>142135</v>
+        <v>142136</v>
       </c>
       <c r="AZ30" s="7">
         <f t="shared" si="19"/>
-        <v>0.91639104337117916</v>
+        <v>0.91639749069972853</v>
       </c>
       <c r="BA30" s="5">
         <v>156855</v>
@@ -5437,14 +5437,14 @@
       </c>
       <c r="BC30" s="6">
         <f t="shared" si="20"/>
-        <v>80544</v>
+        <v>80545</v>
       </c>
       <c r="BD30" s="5">
-        <v>144576</v>
+        <v>144577</v>
       </c>
       <c r="BE30" s="7">
         <f t="shared" si="21"/>
-        <v>0.92171750980204648</v>
+        <v>0.92172388511682768</v>
       </c>
       <c r="BF30" s="5">
         <v>270589</v>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="BH30" s="6">
         <f t="shared" si="22"/>
-        <v>155903</v>
+        <v>155906</v>
       </c>
       <c r="BI30" s="5">
-        <v>247612</v>
+        <v>247615</v>
       </c>
       <c r="BJ30" s="7">
         <f t="shared" si="23"/>
-        <v>0.91508523997649571</v>
+        <v>0.91509632690168485</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5479,14 +5479,14 @@
       </c>
       <c r="E31" s="6">
         <f t="shared" si="0"/>
-        <v>59919</v>
+        <v>59921</v>
       </c>
       <c r="F31" s="5">
-        <v>66618</v>
+        <v>66620</v>
       </c>
       <c r="G31" s="7">
         <f t="shared" si="1"/>
-        <v>0.92734941603908849</v>
+        <v>0.92737725684535821</v>
       </c>
       <c r="H31" s="3">
         <v>72505</v>
@@ -5496,14 +5496,14 @@
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>57741</v>
+        <v>57743</v>
       </c>
       <c r="K31" s="5">
-        <v>66724</v>
+        <v>66726</v>
       </c>
       <c r="L31" s="7">
         <f t="shared" si="3"/>
-        <v>0.92026756775394802</v>
+        <v>0.92029515205847867</v>
       </c>
       <c r="M31" s="2">
         <v>118891</v>
@@ -5513,14 +5513,14 @@
       </c>
       <c r="O31" s="6">
         <f t="shared" si="4"/>
-        <v>80423</v>
+        <v>80425</v>
       </c>
       <c r="P31" s="5">
-        <v>111878</v>
+        <v>111880</v>
       </c>
       <c r="Q31" s="7">
         <f t="shared" si="5"/>
-        <v>0.94101319696192309</v>
+        <v>0.9410300190931189</v>
       </c>
       <c r="R31" s="5">
         <v>72813</v>
@@ -5530,14 +5530,14 @@
       </c>
       <c r="T31" s="6">
         <f t="shared" si="6"/>
-        <v>42983</v>
+        <v>42984</v>
       </c>
       <c r="U31" s="5">
-        <v>67152</v>
+        <v>67153</v>
       </c>
       <c r="V31" s="7">
         <f t="shared" si="7"/>
-        <v>0.92225289440072511</v>
+        <v>0.92226662821199512</v>
       </c>
       <c r="W31" s="5">
         <v>74776</v>
@@ -5547,14 +5547,14 @@
       </c>
       <c r="Y31" s="6">
         <f t="shared" si="8"/>
-        <v>42003</v>
+        <v>42004</v>
       </c>
       <c r="Z31" s="5">
-        <v>68807</v>
+        <v>68808</v>
       </c>
       <c r="AA31" s="7">
         <f t="shared" si="9"/>
-        <v>0.92017492243500587</v>
+        <v>0.92018829570985339</v>
       </c>
       <c r="AB31" s="6">
         <v>124489</v>
@@ -5564,14 +5564,14 @@
       </c>
       <c r="AD31" s="6">
         <f t="shared" si="10"/>
-        <v>65121</v>
+        <v>65124</v>
       </c>
       <c r="AE31" s="5">
-        <v>116347</v>
+        <v>116350</v>
       </c>
       <c r="AF31" s="7">
         <f t="shared" si="11"/>
-        <v>0.93459663102764101</v>
+        <v>0.93462072954236919</v>
       </c>
       <c r="AG31" s="5">
         <v>73552</v>
@@ -5581,14 +5581,14 @@
       </c>
       <c r="AI31" s="6">
         <f t="shared" si="12"/>
-        <v>38801</v>
+        <v>38803</v>
       </c>
       <c r="AJ31" s="5">
-        <v>67167</v>
+        <v>67169</v>
       </c>
       <c r="AK31" s="7">
         <f t="shared" si="13"/>
-        <v>0.91319066782684355</v>
+        <v>0.9132178594735697</v>
       </c>
       <c r="AL31" s="5">
         <v>74464</v>
@@ -5598,14 +5598,14 @@
       </c>
       <c r="AN31" s="6">
         <f t="shared" si="14"/>
-        <v>20747</v>
+        <v>20749</v>
       </c>
       <c r="AO31" s="5">
-        <v>68250</v>
+        <v>68252</v>
       </c>
       <c r="AP31" s="7">
         <f t="shared" si="15"/>
-        <v>0.91655027932960897</v>
+        <v>0.91657713794585305</v>
       </c>
       <c r="AQ31" s="6">
         <v>126646</v>
@@ -5615,14 +5615,14 @@
       </c>
       <c r="AS31" s="6">
         <f t="shared" si="16"/>
-        <v>67772</v>
+        <v>67773</v>
       </c>
       <c r="AT31" s="5">
-        <v>119014</v>
+        <v>119015</v>
       </c>
       <c r="AU31" s="7">
         <f t="shared" si="17"/>
-        <v>0.93973753612431499</v>
+        <v>0.93974543214945594</v>
       </c>
       <c r="AV31" s="5">
         <v>72827</v>
@@ -5632,14 +5632,14 @@
       </c>
       <c r="AX31" s="6">
         <f t="shared" si="18"/>
-        <v>33467</v>
+        <v>33468</v>
       </c>
       <c r="AY31" s="5">
-        <v>68019</v>
+        <v>68020</v>
       </c>
       <c r="AZ31" s="7">
         <f t="shared" si="19"/>
-        <v>0.93398052919933539</v>
+        <v>0.93399426037046696</v>
       </c>
       <c r="BA31" s="5">
         <v>73978</v>
@@ -5649,14 +5649,14 @@
       </c>
       <c r="BC31" s="6">
         <f t="shared" si="20"/>
-        <v>32847</v>
+        <v>32849</v>
       </c>
       <c r="BD31" s="5">
-        <v>69846</v>
+        <v>69848</v>
       </c>
       <c r="BE31" s="7">
         <f t="shared" si="21"/>
-        <v>0.94414555678715295</v>
+        <v>0.9441725918516316</v>
       </c>
       <c r="BF31" s="5">
         <v>129555</v>
@@ -5666,14 +5666,14 @@
       </c>
       <c r="BH31" s="6">
         <f t="shared" si="22"/>
-        <v>72573</v>
+        <v>72577</v>
       </c>
       <c r="BI31" s="5">
-        <v>121951</v>
+        <v>121955</v>
       </c>
       <c r="BJ31" s="7">
         <f t="shared" si="23"/>
-        <v>0.94130678090386322</v>
+        <v>0.94133765582185169</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5691,14 +5691,14 @@
       </c>
       <c r="E32" s="6">
         <f t="shared" si="0"/>
-        <v>159903</v>
+        <v>159904</v>
       </c>
       <c r="F32" s="5">
-        <v>176170</v>
+        <v>176171</v>
       </c>
       <c r="G32" s="7">
         <f t="shared" si="1"/>
-        <v>0.9488799478619635</v>
+        <v>0.94888533402276187</v>
       </c>
       <c r="H32" s="3">
         <v>186389</v>
@@ -5708,14 +5708,14 @@
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>154551</v>
+        <v>154552</v>
       </c>
       <c r="K32" s="5">
-        <v>176550</v>
+        <v>176551</v>
       </c>
       <c r="L32" s="7">
         <f t="shared" si="3"/>
-        <v>0.94721255009684047</v>
+        <v>0.94721791522031884</v>
       </c>
       <c r="M32" s="2">
         <v>382231</v>
@@ -5776,14 +5776,14 @@
       </c>
       <c r="AD32" s="6">
         <f t="shared" si="10"/>
-        <v>213235</v>
+        <v>213236</v>
       </c>
       <c r="AE32" s="5">
-        <v>373032</v>
+        <v>373033</v>
       </c>
       <c r="AF32" s="7">
         <f t="shared" si="11"/>
-        <v>0.95076819558147363</v>
+        <v>0.95077074433920905</v>
       </c>
       <c r="AG32" s="5">
         <v>183147</v>
@@ -5878,14 +5878,14 @@
       </c>
       <c r="BH32" s="6">
         <f t="shared" si="22"/>
-        <v>227770</v>
+        <v>227771</v>
       </c>
       <c r="BI32" s="5">
-        <v>388851</v>
+        <v>388852</v>
       </c>
       <c r="BJ32" s="7">
         <f t="shared" si="23"/>
-        <v>0.9469066416009585</v>
+        <v>0.94690907674100333</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5903,14 +5903,14 @@
       </c>
       <c r="E33" s="6">
         <f t="shared" si="0"/>
-        <v>398262</v>
+        <v>398265</v>
       </c>
       <c r="F33" s="5">
-        <v>534844</v>
+        <v>534847</v>
       </c>
       <c r="G33" s="7">
         <f t="shared" si="1"/>
-        <v>0.96451705979946623</v>
+        <v>0.96452246988386348</v>
       </c>
       <c r="H33" s="3">
         <v>558618</v>
@@ -5920,14 +5920,14 @@
       </c>
       <c r="J33" s="6">
         <f t="shared" si="2"/>
-        <v>412276</v>
+        <v>412279</v>
       </c>
       <c r="K33" s="5">
-        <v>539932</v>
+        <v>539935</v>
       </c>
       <c r="L33" s="7">
         <f t="shared" si="3"/>
-        <v>0.9665495920288999</v>
+        <v>0.96655496242512773</v>
       </c>
       <c r="M33" s="2">
         <v>943614</v>
@@ -5937,14 +5937,14 @@
       </c>
       <c r="O33" s="6">
         <f t="shared" si="4"/>
-        <v>332787</v>
+        <v>332791</v>
       </c>
       <c r="P33" s="5">
-        <v>926021</v>
+        <v>926025</v>
       </c>
       <c r="Q33" s="7">
         <f t="shared" si="5"/>
-        <v>0.98135572384470771</v>
+        <v>0.981359962866172</v>
       </c>
       <c r="R33" s="5">
         <v>563773</v>
@@ -5954,14 +5954,14 @@
       </c>
       <c r="T33" s="6">
         <f t="shared" si="6"/>
-        <v>150537</v>
+        <v>150541</v>
       </c>
       <c r="U33" s="5">
-        <v>549202</v>
+        <v>549206</v>
       </c>
       <c r="V33" s="7">
         <f t="shared" si="7"/>
-        <v>0.97415449125800635</v>
+        <v>0.97416158631222138</v>
       </c>
       <c r="W33" s="5">
         <v>571583</v>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="Y33" s="6">
         <f t="shared" si="8"/>
-        <v>139901</v>
+        <v>139904</v>
       </c>
       <c r="Z33" s="5">
-        <v>554804</v>
+        <v>554807</v>
       </c>
       <c r="AA33" s="7">
         <f t="shared" si="9"/>
-        <v>0.97064468327434505</v>
+        <v>0.97064993185591597</v>
       </c>
       <c r="AB33" s="6">
         <v>961057</v>
@@ -5988,14 +5988,14 @@
       </c>
       <c r="AD33" s="6">
         <f t="shared" si="10"/>
-        <v>220237</v>
+        <v>220240</v>
       </c>
       <c r="AE33" s="5">
-        <v>941302</v>
+        <v>941305</v>
       </c>
       <c r="AF33" s="7">
         <f t="shared" si="11"/>
-        <v>0.97944450745377221</v>
+        <v>0.97944762901680127</v>
       </c>
       <c r="AG33" s="5">
         <v>565645</v>
@@ -6005,14 +6005,14 @@
       </c>
       <c r="AI33" s="6">
         <f t="shared" si="12"/>
-        <v>154556</v>
+        <v>154558</v>
       </c>
       <c r="AJ33" s="5">
-        <v>550821</v>
+        <v>550823</v>
       </c>
       <c r="AK33" s="7">
         <f t="shared" si="13"/>
-        <v>0.97379274986961784</v>
+        <v>0.9737962856561978</v>
       </c>
       <c r="AL33" s="5">
         <v>569536</v>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="AN33" s="6">
         <f t="shared" si="14"/>
-        <v>52851</v>
+        <v>52853</v>
       </c>
       <c r="AO33" s="5">
-        <v>556514</v>
+        <v>556516</v>
       </c>
       <c r="AP33" s="7">
         <f t="shared" si="15"/>
-        <v>0.9771357736824362</v>
+        <v>0.97713928531295646</v>
       </c>
       <c r="AQ33" s="6">
         <v>971221</v>
@@ -6039,14 +6039,14 @@
       </c>
       <c r="AS33" s="6">
         <f t="shared" si="16"/>
-        <v>215724</v>
+        <v>215727</v>
       </c>
       <c r="AT33" s="5">
-        <v>953013</v>
+        <v>953016</v>
       </c>
       <c r="AU33" s="7">
         <f t="shared" si="17"/>
-        <v>0.98125246468105609</v>
+        <v>0.98125555357637451</v>
       </c>
       <c r="AV33" s="5">
         <v>571074</v>
@@ -6056,14 +6056,14 @@
       </c>
       <c r="AX33" s="6">
         <f t="shared" si="18"/>
-        <v>101112</v>
+        <v>101113</v>
       </c>
       <c r="AY33" s="5">
-        <v>560631</v>
+        <v>560632</v>
       </c>
       <c r="AZ33" s="7">
         <f t="shared" si="19"/>
-        <v>0.98171340316666489</v>
+        <v>0.9817151542532141</v>
       </c>
       <c r="BA33" s="5">
         <v>575700</v>
@@ -6073,14 +6073,14 @@
       </c>
       <c r="BC33" s="6">
         <f t="shared" si="20"/>
-        <v>95012</v>
+        <v>95013</v>
       </c>
       <c r="BD33" s="5">
-        <v>570884</v>
+        <v>570885</v>
       </c>
       <c r="BE33" s="7">
         <f t="shared" si="21"/>
-        <v>0.99163453187424011</v>
+        <v>0.99163626889004686</v>
       </c>
       <c r="BF33" s="5">
         <v>986775</v>
@@ -6090,14 +6090,14 @@
       </c>
       <c r="BH33" s="6">
         <f t="shared" si="22"/>
-        <v>221379</v>
+        <v>221382</v>
       </c>
       <c r="BI33" s="5">
-        <v>972679</v>
+        <v>972682</v>
       </c>
       <c r="BJ33" s="7">
         <f t="shared" si="23"/>
-        <v>0.98571508195890656</v>
+        <v>0.98571812216564059</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6515,14 +6515,14 @@
       </c>
       <c r="E36" s="6">
         <f t="shared" si="0"/>
-        <v>564959</v>
+        <v>564965</v>
       </c>
       <c r="F36" s="5">
-        <v>708800</v>
+        <v>708806</v>
       </c>
       <c r="G36" s="7">
         <f t="shared" si="1"/>
-        <v>0.94806761669604855</v>
+        <v>0.94807564209912443</v>
       </c>
       <c r="H36" s="3">
         <v>754952</v>
@@ -6532,14 +6532,14 @@
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>589835</v>
+        <v>589842</v>
       </c>
       <c r="K36" s="5">
-        <v>714399</v>
+        <v>714406</v>
       </c>
       <c r="L36" s="7">
         <f t="shared" si="3"/>
-        <v>0.94628400216172681</v>
+        <v>0.94629327427439092</v>
       </c>
       <c r="M36" s="2">
         <v>1378095</v>
@@ -6549,14 +6549,14 @@
       </c>
       <c r="O36" s="6">
         <f t="shared" si="4"/>
-        <v>749540</v>
+        <v>749545</v>
       </c>
       <c r="P36" s="5">
-        <v>1322852</v>
+        <v>1322857</v>
       </c>
       <c r="Q36" s="7">
         <f t="shared" si="5"/>
-        <v>0.95991350378602347</v>
+        <v>0.9599171319829185</v>
       </c>
       <c r="R36" s="5">
         <v>758000</v>
@@ -6566,14 +6566,14 @@
       </c>
       <c r="T36" s="6">
         <f t="shared" si="6"/>
-        <v>349411</v>
+        <v>349417</v>
       </c>
       <c r="U36" s="5">
-        <v>717597</v>
+        <v>717603</v>
       </c>
       <c r="V36" s="7">
         <f t="shared" si="7"/>
-        <v>0.94669788918205799</v>
+        <v>0.94670580474934041</v>
       </c>
       <c r="W36" s="5">
         <v>766789</v>
@@ -6583,14 +6583,14 @@
       </c>
       <c r="Y36" s="6">
         <f t="shared" si="8"/>
-        <v>352536</v>
+        <v>352542</v>
       </c>
       <c r="Z36" s="5">
-        <v>731796</v>
+        <v>731802</v>
       </c>
       <c r="AA36" s="7">
         <f t="shared" si="9"/>
-        <v>0.95436423840195939</v>
+        <v>0.95437206324034385</v>
       </c>
       <c r="AB36" s="6">
         <v>1410553</v>
@@ -6600,14 +6600,14 @@
       </c>
       <c r="AD36" s="6">
         <f t="shared" si="10"/>
-        <v>580365</v>
+        <v>580371</v>
       </c>
       <c r="AE36" s="5">
-        <v>1353314</v>
+        <v>1353320</v>
       </c>
       <c r="AF36" s="7">
         <f t="shared" si="11"/>
-        <v>0.95942087961246403</v>
+        <v>0.95942513326333712</v>
       </c>
       <c r="AG36" s="5">
         <v>767229</v>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="AI36" s="6">
         <f t="shared" si="12"/>
-        <v>321696</v>
+        <v>321704</v>
       </c>
       <c r="AJ36" s="5">
-        <v>729733</v>
+        <v>729741</v>
       </c>
       <c r="AK36" s="7">
         <f t="shared" si="13"/>
-        <v>0.9511280204476108</v>
+        <v>0.95113844758214305</v>
       </c>
       <c r="AL36" s="5">
         <v>779513</v>
@@ -6634,14 +6634,14 @@
       </c>
       <c r="AN36" s="6">
         <f t="shared" si="14"/>
-        <v>159019</v>
+        <v>159026</v>
       </c>
       <c r="AO36" s="5">
-        <v>741651</v>
+        <v>741658</v>
       </c>
       <c r="AP36" s="7">
         <f t="shared" si="15"/>
-        <v>0.95142864839970598</v>
+        <v>0.95143762836540247</v>
       </c>
       <c r="AQ36" s="6">
         <v>1443943</v>
@@ -6651,14 +6651,14 @@
       </c>
       <c r="AS36" s="6">
         <f t="shared" si="16"/>
-        <v>553783</v>
+        <v>553787</v>
       </c>
       <c r="AT36" s="5">
-        <v>1380650</v>
+        <v>1380654</v>
       </c>
       <c r="AU36" s="7">
         <f t="shared" si="17"/>
-        <v>0.95616655228080338</v>
+        <v>0.95616932247325548</v>
       </c>
       <c r="AV36" s="5">
         <v>783108</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="AX36" s="6">
         <f t="shared" si="18"/>
-        <v>259341</v>
+        <v>259345</v>
       </c>
       <c r="AY36" s="5">
-        <v>745639</v>
+        <v>745643</v>
       </c>
       <c r="AZ36" s="7">
         <f t="shared" si="19"/>
-        <v>0.95215347053024613</v>
+        <v>0.95215857838254747</v>
       </c>
       <c r="BA36" s="5">
         <v>793830</v>
@@ -6685,14 +6685,14 @@
       </c>
       <c r="BC36" s="6">
         <f t="shared" si="20"/>
-        <v>252875</v>
+        <v>252879</v>
       </c>
       <c r="BD36" s="5">
-        <v>759221</v>
+        <v>759225</v>
       </c>
       <c r="BE36" s="7">
         <f t="shared" si="21"/>
-        <v>0.95640250431452578</v>
+        <v>0.9564075431767507</v>
       </c>
       <c r="BF36" s="5">
         <v>1468416</v>
@@ -6702,14 +6702,14 @@
       </c>
       <c r="BH36" s="6">
         <f t="shared" si="24"/>
-        <v>554470</v>
+        <v>554475</v>
       </c>
       <c r="BI36" s="5">
-        <v>1403641</v>
+        <v>1403646</v>
       </c>
       <c r="BJ36" s="7">
         <f t="shared" si="25"/>
-        <v>0.95588784104776847</v>
+        <v>0.95589124607740583</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6727,14 +6727,14 @@
       </c>
       <c r="E37" s="6">
         <f t="shared" si="0"/>
-        <v>483618</v>
+        <v>483622</v>
       </c>
       <c r="F37" s="5">
-        <v>548013</v>
+        <v>548017</v>
       </c>
       <c r="G37" s="7">
         <f t="shared" si="1"/>
-        <v>0.9250460402047882</v>
+        <v>0.92505279220549042</v>
       </c>
       <c r="H37" s="3">
         <v>593173</v>
@@ -6744,14 +6744,14 @@
       </c>
       <c r="J37" s="6">
         <f t="shared" si="2"/>
-        <v>489499</v>
+        <v>489506</v>
       </c>
       <c r="K37" s="5">
-        <v>547545</v>
+        <v>547552</v>
       </c>
       <c r="L37" s="7">
         <f t="shared" si="3"/>
-        <v>0.92307809020302678</v>
+        <v>0.92308989114474194</v>
       </c>
       <c r="M37" s="2">
         <v>768378</v>
@@ -6761,14 +6761,14 @@
       </c>
       <c r="O37" s="6">
         <f t="shared" si="4"/>
-        <v>455274</v>
+        <v>455283</v>
       </c>
       <c r="P37" s="5">
-        <v>713681</v>
+        <v>713690</v>
       </c>
       <c r="Q37" s="7">
         <f t="shared" si="5"/>
-        <v>0.9288149842915856</v>
+        <v>0.92882669727660083</v>
       </c>
       <c r="R37" s="5">
         <v>601605</v>
@@ -6778,14 +6778,14 @@
       </c>
       <c r="T37" s="6">
         <f t="shared" si="6"/>
-        <v>294909</v>
+        <v>294918</v>
       </c>
       <c r="U37" s="5">
-        <v>556553</v>
+        <v>556562</v>
       </c>
       <c r="V37" s="7">
         <f t="shared" si="7"/>
-        <v>0.92511365430805925</v>
+        <v>0.92512861429010729</v>
       </c>
       <c r="W37" s="5">
         <v>609453</v>
@@ -6795,14 +6795,14 @@
       </c>
       <c r="Y37" s="6">
         <f t="shared" si="8"/>
-        <v>298794</v>
+        <v>298803</v>
       </c>
       <c r="Z37" s="5">
-        <v>564831</v>
+        <v>564840</v>
       </c>
       <c r="AA37" s="7">
         <f t="shared" si="9"/>
-        <v>0.92678352555488286</v>
+        <v>0.92679829289543247</v>
       </c>
       <c r="AB37" s="6">
         <v>790568</v>
@@ -6812,14 +6812,14 @@
       </c>
       <c r="AD37" s="6">
         <f t="shared" si="10"/>
-        <v>342021</v>
+        <v>342031</v>
       </c>
       <c r="AE37" s="5">
-        <v>735796</v>
+        <v>735806</v>
       </c>
       <c r="AF37" s="7">
         <f t="shared" si="11"/>
-        <v>0.93071816719118405</v>
+        <v>0.93073081632446542</v>
       </c>
       <c r="AG37" s="5">
         <v>617773</v>
@@ -6829,14 +6829,14 @@
       </c>
       <c r="AI37" s="6">
         <f t="shared" si="12"/>
-        <v>268093</v>
+        <v>268101</v>
       </c>
       <c r="AJ37" s="5">
-        <v>572929</v>
+        <v>572937</v>
       </c>
       <c r="AK37" s="7">
         <f t="shared" si="13"/>
-        <v>0.92741022997120304</v>
+        <v>0.92742317971164168</v>
       </c>
       <c r="AL37" s="5">
         <v>624724</v>
@@ -6846,14 +6846,14 @@
       </c>
       <c r="AN37" s="6">
         <f t="shared" si="14"/>
-        <v>101166</v>
+        <v>101173</v>
       </c>
       <c r="AO37" s="5">
-        <v>581020</v>
+        <v>581027</v>
       </c>
       <c r="AP37" s="7">
         <f t="shared" si="15"/>
-        <v>0.93004270685934909</v>
+        <v>0.93005391180745423</v>
       </c>
       <c r="AQ37" s="6">
         <v>810789</v>
@@ -6863,14 +6863,14 @@
       </c>
       <c r="AS37" s="6">
         <f t="shared" si="16"/>
-        <v>350636</v>
+        <v>350643</v>
       </c>
       <c r="AT37" s="5">
-        <v>756829</v>
+        <v>756836</v>
       </c>
       <c r="AU37" s="7">
         <f t="shared" si="17"/>
-        <v>0.93344754307224198</v>
+        <v>0.93345617663781821</v>
       </c>
       <c r="AV37" s="5">
         <v>633338</v>
@@ -6880,14 +6880,14 @@
       </c>
       <c r="AX37" s="6">
         <f t="shared" si="18"/>
-        <v>242766</v>
+        <v>242773</v>
       </c>
       <c r="AY37" s="5">
-        <v>591831</v>
+        <v>591838</v>
       </c>
       <c r="AZ37" s="7">
         <f t="shared" si="19"/>
-        <v>0.93446311448231434</v>
+        <v>0.93447416703245345</v>
       </c>
       <c r="BA37" s="5">
         <v>640933</v>
@@ -6897,14 +6897,14 @@
       </c>
       <c r="BC37" s="6">
         <f t="shared" si="20"/>
-        <v>236702</v>
+        <v>236707</v>
       </c>
       <c r="BD37" s="5">
-        <v>600814</v>
+        <v>600819</v>
       </c>
       <c r="BE37" s="7">
         <f t="shared" si="21"/>
-        <v>0.93740531381595271</v>
+        <v>0.93741311494337165</v>
       </c>
       <c r="BF37" s="5">
         <v>830528</v>
@@ -6914,14 +6914,14 @@
       </c>
       <c r="BH37" s="6">
         <f t="shared" si="24"/>
-        <v>361782</v>
+        <v>361794</v>
       </c>
       <c r="BI37" s="5">
-        <v>776599</v>
+        <v>776611</v>
       </c>
       <c r="BJ37" s="7">
         <f t="shared" si="25"/>
-        <v>0.93506660822994525</v>
+        <v>0.93508105686984666</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7363,14 +7363,14 @@
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>214679</v>
+        <v>214682</v>
       </c>
       <c r="F40" s="5">
-        <v>240188</v>
+        <v>240191</v>
       </c>
       <c r="G40" s="7">
         <f t="shared" si="1"/>
-        <v>0.94171799586752558</v>
+        <v>0.94172975812870263</v>
       </c>
       <c r="H40" s="3">
         <v>254802</v>
@@ -7380,14 +7380,14 @@
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>221361</v>
+        <v>221364</v>
       </c>
       <c r="K40" s="5">
-        <v>240317</v>
+        <v>240320</v>
       </c>
       <c r="L40" s="7">
         <f t="shared" si="3"/>
-        <v>0.9431519375829075</v>
+        <v>0.94316371143083644</v>
       </c>
       <c r="M40" s="2">
         <v>315837</v>
@@ -7397,14 +7397,14 @@
       </c>
       <c r="O40" s="6">
         <f t="shared" si="4"/>
-        <v>210334</v>
+        <v>210339</v>
       </c>
       <c r="P40" s="5">
-        <v>299305</v>
+        <v>299310</v>
       </c>
       <c r="Q40" s="7">
         <f t="shared" si="5"/>
-        <v>0.94765654435674096</v>
+        <v>0.94767237530751625</v>
       </c>
       <c r="R40" s="5">
         <v>257348</v>
@@ -7414,14 +7414,14 @@
       </c>
       <c r="T40" s="6">
         <f t="shared" si="6"/>
-        <v>121902</v>
+        <v>121905</v>
       </c>
       <c r="U40" s="5">
-        <v>242360</v>
+        <v>242363</v>
       </c>
       <c r="V40" s="7">
         <f t="shared" si="7"/>
-        <v>0.94175979607379889</v>
+        <v>0.94177145344047752</v>
       </c>
       <c r="W40" s="5">
         <v>259512</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="Y40" s="6">
         <f t="shared" si="8"/>
-        <v>111091</v>
+        <v>111095</v>
       </c>
       <c r="Z40" s="5">
-        <v>244314</v>
+        <v>244318</v>
       </c>
       <c r="AA40" s="7">
         <f t="shared" si="9"/>
-        <v>0.94143623416258204</v>
+        <v>0.94145164770800582</v>
       </c>
       <c r="AB40" s="6">
         <v>322067</v>
@@ -7448,14 +7448,14 @@
       </c>
       <c r="AD40" s="6">
         <f t="shared" si="10"/>
-        <v>125322</v>
+        <v>125324</v>
       </c>
       <c r="AE40" s="5">
-        <v>305018</v>
+        <v>305020</v>
       </c>
       <c r="AF40" s="7">
         <f t="shared" si="11"/>
-        <v>0.94706380970419202</v>
+        <v>0.94707001959219661</v>
       </c>
       <c r="AG40" s="5">
         <v>262041</v>
@@ -7465,14 +7465,14 @@
       </c>
       <c r="AI40" s="6">
         <f t="shared" si="12"/>
-        <v>92327</v>
+        <v>92329</v>
       </c>
       <c r="AJ40" s="5">
-        <v>247110</v>
+        <v>247112</v>
       </c>
       <c r="AK40" s="7">
         <f t="shared" si="13"/>
-        <v>0.94302036704179881</v>
+        <v>0.94302799943520288</v>
       </c>
       <c r="AL40" s="5">
         <v>264607</v>
@@ -7482,14 +7482,14 @@
       </c>
       <c r="AN40" s="6">
         <f t="shared" si="14"/>
-        <v>39744</v>
+        <v>39746</v>
       </c>
       <c r="AO40" s="5">
-        <v>250045</v>
+        <v>250047</v>
       </c>
       <c r="AP40" s="7">
         <f t="shared" si="15"/>
-        <v>0.9449674422823281</v>
+        <v>0.9449750006613582</v>
       </c>
       <c r="AQ40" s="6">
         <v>328683</v>
@@ -7499,14 +7499,14 @@
       </c>
       <c r="AS40" s="6">
         <f t="shared" si="16"/>
-        <v>125220</v>
+        <v>125224</v>
       </c>
       <c r="AT40" s="5">
-        <v>312601</v>
+        <v>312605</v>
       </c>
       <c r="AU40" s="7">
         <f t="shared" si="17"/>
-        <v>0.95107139706038946</v>
+        <v>0.95108356684099882</v>
       </c>
       <c r="AV40" s="5">
         <v>267796</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="AX40" s="6">
         <f t="shared" si="18"/>
-        <v>91424</v>
+        <v>91426</v>
       </c>
       <c r="AY40" s="5">
-        <v>253324</v>
+        <v>253326</v>
       </c>
       <c r="AZ40" s="7">
         <f t="shared" si="19"/>
-        <v>0.94595886421007036</v>
+        <v>0.9459663325815173</v>
       </c>
       <c r="BA40" s="5">
         <v>270158</v>
@@ -7533,14 +7533,14 @@
       </c>
       <c r="BC40" s="6">
         <f t="shared" si="20"/>
-        <v>92571</v>
+        <v>92574</v>
       </c>
       <c r="BD40" s="5">
-        <v>256022</v>
+        <v>256025</v>
       </c>
       <c r="BE40" s="7">
         <f t="shared" si="21"/>
-        <v>0.94767506422167769</v>
+        <v>0.94768616883453383</v>
       </c>
       <c r="BF40" s="5">
         <v>335514</v>
@@ -7550,14 +7550,14 @@
       </c>
       <c r="BH40" s="6">
         <f t="shared" si="24"/>
-        <v>137574</v>
+        <v>137579</v>
       </c>
       <c r="BI40" s="5">
-        <v>318080</v>
+        <v>318085</v>
       </c>
       <c r="BJ40" s="7">
         <f t="shared" si="25"/>
-        <v>0.94803793582384044</v>
+        <v>0.94805283833163445</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7575,14 +7575,14 @@
       </c>
       <c r="E41" s="6">
         <f t="shared" si="0"/>
-        <v>580325</v>
+        <v>580343</v>
       </c>
       <c r="F41" s="5">
-        <v>764172</v>
+        <v>764190</v>
       </c>
       <c r="G41" s="7">
         <f t="shared" si="1"/>
-        <v>0.95149939486305979</v>
+        <v>0.95152180734232816</v>
       </c>
       <c r="H41" s="3">
         <v>805681</v>
@@ -7592,14 +7592,14 @@
       </c>
       <c r="J41" s="6">
         <f t="shared" si="2"/>
-        <v>690197</v>
+        <v>690213</v>
       </c>
       <c r="K41" s="5">
-        <v>764261</v>
+        <v>764277</v>
       </c>
       <c r="L41" s="7">
         <f t="shared" si="3"/>
-        <v>0.94859007473181078</v>
+        <v>0.9486099337082543</v>
       </c>
       <c r="M41" s="2">
         <v>924274</v>
@@ -7609,14 +7609,14 @@
       </c>
       <c r="O41" s="6">
         <f t="shared" si="4"/>
-        <v>505894</v>
+        <v>505915</v>
       </c>
       <c r="P41" s="5">
-        <v>874770</v>
+        <v>874791</v>
       </c>
       <c r="Q41" s="7">
         <f t="shared" si="5"/>
-        <v>0.94644012489802809</v>
+        <v>0.94646284543328063</v>
       </c>
       <c r="R41" s="5">
         <v>822173</v>
@@ -7626,14 +7626,14 @@
       </c>
       <c r="T41" s="6">
         <f t="shared" si="6"/>
-        <v>371889</v>
+        <v>371908</v>
       </c>
       <c r="U41" s="5">
-        <v>778609</v>
+        <v>778628</v>
       </c>
       <c r="V41" s="7">
         <f t="shared" si="7"/>
-        <v>0.94701358473216712</v>
+        <v>0.94703669422372172</v>
       </c>
       <c r="W41" s="5">
         <v>833879</v>
@@ -7643,14 +7643,14 @@
       </c>
       <c r="Y41" s="6">
         <f t="shared" si="8"/>
-        <v>376205</v>
+        <v>376226</v>
       </c>
       <c r="Z41" s="5">
-        <v>786051</v>
+        <v>786072</v>
       </c>
       <c r="AA41" s="7">
         <f t="shared" si="9"/>
-        <v>0.94264395673712853</v>
+        <v>0.94266914024696624</v>
       </c>
       <c r="AB41" s="6">
         <v>956956</v>
@@ -7660,14 +7660,14 @@
       </c>
       <c r="AD41" s="6">
         <f t="shared" si="10"/>
-        <v>367844</v>
+        <v>367869</v>
       </c>
       <c r="AE41" s="5">
-        <v>899965</v>
+        <v>899990</v>
       </c>
       <c r="AF41" s="7">
         <f t="shared" si="11"/>
-        <v>0.94044553772587247</v>
+        <v>0.94047166222898437</v>
       </c>
       <c r="AG41" s="5">
         <v>851169</v>
@@ -7677,14 +7677,14 @@
       </c>
       <c r="AI41" s="6">
         <f t="shared" si="12"/>
-        <v>370376</v>
+        <v>370398</v>
       </c>
       <c r="AJ41" s="5">
-        <v>798509</v>
+        <v>798531</v>
       </c>
       <c r="AK41" s="7">
         <f t="shared" si="13"/>
-        <v>0.93813214532014211</v>
+        <v>0.93815799212612305</v>
       </c>
       <c r="AL41" s="5">
         <v>859964</v>
@@ -7694,14 +7694,14 @@
       </c>
       <c r="AN41" s="6">
         <f t="shared" si="14"/>
-        <v>117979</v>
+        <v>118001</v>
       </c>
       <c r="AO41" s="5">
-        <v>807002</v>
+        <v>807024</v>
       </c>
       <c r="AP41" s="7">
         <f t="shared" si="15"/>
-        <v>0.93841370103864818</v>
+        <v>0.93843928350489092</v>
       </c>
       <c r="AQ41" s="6">
         <v>982238</v>
@@ -7711,14 +7711,14 @@
       </c>
       <c r="AS41" s="6">
         <f t="shared" si="16"/>
-        <v>370251</v>
+        <v>370278</v>
       </c>
       <c r="AT41" s="5">
-        <v>921126</v>
+        <v>921153</v>
       </c>
       <c r="AU41" s="7">
         <f t="shared" si="17"/>
-        <v>0.93778289986744556</v>
+        <v>0.93781038811367512</v>
       </c>
       <c r="AV41" s="5">
         <v>867973</v>
@@ -7728,14 +7728,14 @@
       </c>
       <c r="AX41" s="6">
         <f t="shared" si="18"/>
-        <v>303493</v>
+        <v>303518</v>
       </c>
       <c r="AY41" s="5">
-        <v>816690</v>
+        <v>816715</v>
       </c>
       <c r="AZ41" s="7">
         <f t="shared" si="19"/>
-        <v>0.94091636490996844</v>
+        <v>0.94094516764922409</v>
       </c>
       <c r="BA41" s="5">
         <v>869274</v>
@@ -7745,14 +7745,14 @@
       </c>
       <c r="BC41" s="6">
         <f t="shared" si="20"/>
-        <v>302061</v>
+        <v>302086</v>
       </c>
       <c r="BD41" s="5">
-        <v>822921</v>
+        <v>822946</v>
       </c>
       <c r="BE41" s="7">
         <f t="shared" si="21"/>
-        <v>0.94667619185665275</v>
+        <v>0.9467049514882534</v>
       </c>
       <c r="BF41" s="5">
         <v>986817</v>
@@ -7762,14 +7762,14 @@
       </c>
       <c r="BH41" s="6">
         <f t="shared" si="24"/>
-        <v>395374</v>
+        <v>395400</v>
       </c>
       <c r="BI41" s="5">
-        <v>937191</v>
+        <v>937217</v>
       </c>
       <c r="BJ41" s="7">
         <f t="shared" si="25"/>
-        <v>0.94971104064887413</v>
+        <v>0.94973738798581697</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8211,14 +8211,14 @@
       </c>
       <c r="E44" s="6">
         <f t="shared" si="0"/>
-        <v>213008</v>
+        <v>213009</v>
       </c>
       <c r="F44" s="5">
-        <v>265079</v>
+        <v>265080</v>
       </c>
       <c r="G44" s="7">
         <f t="shared" si="1"/>
-        <v>0.84536638102861594</v>
+        <v>0.84536957013971492</v>
       </c>
       <c r="H44" s="3">
         <v>315037</v>
@@ -8228,14 +8228,14 @@
       </c>
       <c r="J44" s="6">
         <f t="shared" si="2"/>
-        <v>230420</v>
+        <v>230421</v>
       </c>
       <c r="K44" s="5">
-        <v>265480</v>
+        <v>265481</v>
       </c>
       <c r="L44" s="7">
         <f t="shared" si="3"/>
-        <v>0.84269466761047118</v>
+        <v>0.84269784184079966</v>
       </c>
       <c r="M44" s="2">
         <v>378050</v>
@@ -8245,14 +8245,14 @@
       </c>
       <c r="O44" s="6">
         <f t="shared" si="4"/>
-        <v>207283</v>
+        <v>207285</v>
       </c>
       <c r="P44" s="5">
-        <v>325455</v>
+        <v>325457</v>
       </c>
       <c r="Q44" s="7">
         <f t="shared" si="5"/>
-        <v>0.86087819071551386</v>
+        <v>0.86088348102102896</v>
       </c>
       <c r="R44" s="5">
         <v>322476</v>
@@ -8262,14 +8262,14 @@
       </c>
       <c r="T44" s="6">
         <f t="shared" si="6"/>
-        <v>156955</v>
+        <v>156957</v>
       </c>
       <c r="U44" s="5">
-        <v>272184</v>
+        <v>272186</v>
       </c>
       <c r="V44" s="7">
         <f t="shared" si="7"/>
-        <v>0.84404420794105606</v>
+        <v>0.84405040995298874</v>
       </c>
       <c r="W44" s="5">
         <v>327345</v>
@@ -8279,14 +8279,14 @@
       </c>
       <c r="Y44" s="6">
         <f t="shared" si="8"/>
-        <v>161076</v>
+        <v>161080</v>
       </c>
       <c r="Z44" s="5">
-        <v>275333</v>
+        <v>275337</v>
       </c>
       <c r="AA44" s="7">
         <f t="shared" si="9"/>
-        <v>0.84110953275596079</v>
+        <v>0.84112175227970487</v>
       </c>
       <c r="AB44" s="6">
         <v>393681</v>
@@ -8296,14 +8296,14 @@
       </c>
       <c r="AD44" s="6">
         <f t="shared" si="10"/>
-        <v>175094</v>
+        <v>175096</v>
       </c>
       <c r="AE44" s="5">
-        <v>336174</v>
+        <v>336176</v>
       </c>
       <c r="AF44" s="7">
         <f t="shared" si="11"/>
-        <v>0.85392487826438157</v>
+        <v>0.8539299585197152</v>
       </c>
       <c r="AG44" s="5">
         <v>333199</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="AI44" s="6">
         <f t="shared" si="12"/>
-        <v>145823</v>
+        <v>145825</v>
       </c>
       <c r="AJ44" s="5">
-        <v>279561</v>
+        <v>279563</v>
       </c>
       <c r="AK44" s="7">
         <f t="shared" si="13"/>
-        <v>0.83902112551358199</v>
+        <v>0.83902712793255685</v>
       </c>
       <c r="AL44" s="5">
         <v>336893</v>
@@ -8330,14 +8330,14 @@
       </c>
       <c r="AN44" s="6">
         <f t="shared" si="14"/>
-        <v>65080</v>
+        <v>65083</v>
       </c>
       <c r="AO44" s="5">
-        <v>284666</v>
+        <v>284669</v>
       </c>
       <c r="AP44" s="7">
         <f t="shared" si="15"/>
-        <v>0.84497451713155214</v>
+        <v>0.84498342203607668</v>
       </c>
       <c r="AQ44" s="6">
         <v>406157</v>
@@ -8347,14 +8347,14 @@
       </c>
       <c r="AS44" s="6">
         <f t="shared" si="16"/>
-        <v>177442</v>
+        <v>177445</v>
       </c>
       <c r="AT44" s="5">
-        <v>347545</v>
+        <v>347548</v>
       </c>
       <c r="AU44" s="7">
         <f t="shared" si="17"/>
-        <v>0.85569127209428864</v>
+        <v>0.85569865840056925</v>
       </c>
       <c r="AV44" s="5">
         <v>341214</v>
@@ -8364,14 +8364,14 @@
       </c>
       <c r="AX44" s="6">
         <f t="shared" si="18"/>
-        <v>140159</v>
+        <v>140162</v>
       </c>
       <c r="AY44" s="5">
-        <v>288751</v>
+        <v>288754</v>
       </c>
       <c r="AZ44" s="7">
         <f t="shared" si="19"/>
-        <v>0.84624605086543925</v>
+        <v>0.84625484300175258</v>
       </c>
       <c r="BA44" s="5">
         <v>343859</v>
@@ -8381,14 +8381,14 @@
       </c>
       <c r="BC44" s="6">
         <f t="shared" si="20"/>
-        <v>138781</v>
+        <v>138784</v>
       </c>
       <c r="BD44" s="5">
-        <v>292342</v>
+        <v>292345</v>
       </c>
       <c r="BE44" s="7">
         <f t="shared" si="21"/>
-        <v>0.85017987023751018</v>
+        <v>0.85018859474377584</v>
       </c>
       <c r="BF44" s="5">
         <v>410714</v>
@@ -8398,14 +8398,14 @@
       </c>
       <c r="BH44" s="6">
         <f t="shared" si="24"/>
-        <v>190895</v>
+        <v>190899</v>
       </c>
       <c r="BI44" s="5">
-        <v>354694</v>
+        <v>354698</v>
       </c>
       <c r="BJ44" s="7">
         <f t="shared" si="25"/>
-        <v>0.86360338337626674</v>
+        <v>0.86361312251347655</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8423,14 +8423,14 @@
       </c>
       <c r="E45" s="6">
         <f t="shared" si="0"/>
-        <v>180643</v>
+        <v>180644</v>
       </c>
       <c r="F45" s="5">
-        <v>214271</v>
+        <v>214272</v>
       </c>
       <c r="G45" s="7">
         <f t="shared" si="1"/>
-        <v>0.90115024708232572</v>
+        <v>0.90115445273893391</v>
       </c>
       <c r="H45" s="3">
         <v>238690</v>
@@ -8440,14 +8440,14 @@
       </c>
       <c r="J45" s="6">
         <f t="shared" si="2"/>
-        <v>187334</v>
+        <v>187335</v>
       </c>
       <c r="K45" s="5">
-        <v>214937</v>
+        <v>214938</v>
       </c>
       <c r="L45" s="7">
         <f t="shared" si="3"/>
-        <v>0.90048598600695462</v>
+        <v>0.90049017554149735</v>
       </c>
       <c r="M45" s="2">
         <v>292586</v>
@@ -8457,14 +8457,14 @@
       </c>
       <c r="O45" s="6">
         <f t="shared" si="4"/>
-        <v>152354</v>
+        <v>152355</v>
       </c>
       <c r="P45" s="5">
-        <v>266644</v>
+        <v>266645</v>
       </c>
       <c r="Q45" s="7">
         <f t="shared" si="5"/>
-        <v>0.9113354705966793</v>
+        <v>0.91133888839520683</v>
       </c>
       <c r="R45" s="5">
         <v>242899</v>
@@ -8474,14 +8474,14 @@
       </c>
       <c r="T45" s="6">
         <f t="shared" si="6"/>
-        <v>110254</v>
+        <v>110255</v>
       </c>
       <c r="U45" s="5">
-        <v>218694</v>
+        <v>218695</v>
       </c>
       <c r="V45" s="7">
         <f t="shared" si="7"/>
-        <v>0.90034952799311652</v>
+        <v>0.90035364493060899</v>
       </c>
       <c r="W45" s="5">
         <v>244806</v>
@@ -8491,14 +8491,14 @@
       </c>
       <c r="Y45" s="6">
         <f t="shared" si="8"/>
-        <v>113530</v>
+        <v>113532</v>
       </c>
       <c r="Z45" s="5">
-        <v>220501</v>
+        <v>220503</v>
       </c>
       <c r="AA45" s="7">
         <f t="shared" si="9"/>
-        <v>0.90071730268048988</v>
+        <v>0.90072547241489176</v>
       </c>
       <c r="AB45" s="6">
         <v>299772</v>
@@ -8508,14 +8508,14 @@
       </c>
       <c r="AD45" s="6">
         <f t="shared" si="10"/>
-        <v>124972</v>
+        <v>124974</v>
       </c>
       <c r="AE45" s="5">
-        <v>271302</v>
+        <v>271304</v>
       </c>
       <c r="AF45" s="7">
         <f t="shared" si="11"/>
-        <v>0.90502782114406954</v>
+        <v>0.90503449288125637</v>
       </c>
       <c r="AG45" s="5">
         <v>246243</v>
@@ -8525,14 +8525,14 @@
       </c>
       <c r="AI45" s="6">
         <f t="shared" si="12"/>
-        <v>101045</v>
+        <v>101047</v>
       </c>
       <c r="AJ45" s="5">
-        <v>222570</v>
+        <v>222572</v>
       </c>
       <c r="AK45" s="7">
         <f t="shared" si="13"/>
-        <v>0.90386325702659565</v>
+        <v>0.90387137908488768</v>
       </c>
       <c r="AL45" s="5">
         <v>247584</v>
@@ -8542,14 +8542,14 @@
       </c>
       <c r="AN45" s="6">
         <f t="shared" si="14"/>
-        <v>40253</v>
+        <v>40255</v>
       </c>
       <c r="AO45" s="5">
-        <v>225200</v>
+        <v>225202</v>
       </c>
       <c r="AP45" s="7">
         <f t="shared" si="15"/>
-        <v>0.90959028047046664</v>
+        <v>0.90959835853690063</v>
       </c>
       <c r="AQ45" s="6">
         <v>303759</v>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="AS45" s="6">
         <f t="shared" si="16"/>
-        <v>134141</v>
+        <v>134143</v>
       </c>
       <c r="AT45" s="5">
-        <v>277034</v>
+        <v>277036</v>
       </c>
       <c r="AU45" s="7">
         <f t="shared" si="17"/>
-        <v>0.91201906774778685</v>
+        <v>0.91202565191484042</v>
       </c>
       <c r="AV45" s="5">
         <v>248547</v>
@@ -8576,14 +8576,14 @@
       </c>
       <c r="AX45" s="6">
         <f t="shared" si="18"/>
-        <v>101077</v>
+        <v>101079</v>
       </c>
       <c r="AY45" s="5">
-        <v>227084</v>
+        <v>227086</v>
       </c>
       <c r="AZ45" s="7">
         <f t="shared" si="19"/>
-        <v>0.91364611119828443</v>
+        <v>0.91365415796609895</v>
       </c>
       <c r="BA45" s="5">
         <v>248925</v>
@@ -8593,14 +8593,14 @@
       </c>
       <c r="BC45" s="6">
         <f t="shared" si="20"/>
-        <v>98870</v>
+        <v>98872</v>
       </c>
       <c r="BD45" s="5">
-        <v>229250</v>
+        <v>229252</v>
       </c>
       <c r="BE45" s="7">
         <f t="shared" si="21"/>
-        <v>0.92096012855277698</v>
+        <v>0.92096816310133578</v>
       </c>
       <c r="BF45" s="5">
         <v>305535</v>
@@ -8610,14 +8610,14 @@
       </c>
       <c r="BH45" s="6">
         <f t="shared" si="24"/>
-        <v>145882</v>
+        <v>145884</v>
       </c>
       <c r="BI45" s="5">
-        <v>281595</v>
+        <v>281597</v>
       </c>
       <c r="BJ45" s="7">
         <f t="shared" si="25"/>
-        <v>0.92164563797928223</v>
+        <v>0.9216521838741879</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9059,15 +9059,15 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" si="0"/>
-        <v>5348076</v>
+        <v>5348139</v>
       </c>
       <c r="F48" s="9">
         <f>SUM(F10:F47)</f>
-        <v>6383806</v>
+        <v>6383869</v>
       </c>
       <c r="G48" s="8">
         <f t="shared" si="1"/>
-        <v>0.92082536385535219</v>
+        <v>0.92083445122390983</v>
       </c>
       <c r="H48" s="9">
         <f>SUM(H10:H47)</f>
@@ -9079,15 +9079,15 @@
       </c>
       <c r="J48" s="10">
         <f t="shared" si="2"/>
-        <v>5526950</v>
+        <v>5527016</v>
       </c>
       <c r="K48" s="9">
         <f>SUM(K10:K47)</f>
-        <v>6398687</v>
+        <v>6398753</v>
       </c>
       <c r="L48" s="8">
         <f t="shared" si="3"/>
-        <v>0.92057663517168964</v>
+        <v>0.92058613056627947</v>
       </c>
       <c r="M48" s="9">
         <f>SUM(M10:M47)</f>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="O48" s="10">
         <f t="shared" si="4"/>
-        <v>5890017</v>
+        <v>5890105</v>
       </c>
       <c r="P48" s="12">
         <f>SUM(P10:P47)</f>
-        <v>10190955</v>
+        <v>10191043</v>
       </c>
       <c r="Q48" s="8">
         <f t="shared" si="5"/>
-        <v>0.93871752988807466</v>
+        <v>0.93872563581559865</v>
       </c>
       <c r="R48" s="9">
         <f>SUM(R10:R47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="T48" s="10">
         <f t="shared" si="6"/>
-        <v>3238865</v>
+        <v>3238937</v>
       </c>
       <c r="U48" s="9">
         <f>SUM(U10:U47)</f>
-        <v>6483922</v>
+        <v>6483994</v>
       </c>
       <c r="V48" s="8">
         <f t="shared" si="7"/>
-        <v>0.92386065551580232</v>
+        <v>0.92387091442502378</v>
       </c>
       <c r="W48" s="9">
         <f>SUM(W10:W47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="Y48" s="9">
         <f t="shared" si="8"/>
-        <v>3177222</v>
+        <v>3177302</v>
       </c>
       <c r="Z48" s="9">
         <f>SUM(Z10:Z47)</f>
-        <v>6602843</v>
+        <v>6602923</v>
       </c>
       <c r="AA48" s="8">
         <f t="shared" si="9"/>
-        <v>0.92660296441411982</v>
+        <v>0.92661419112921106</v>
       </c>
       <c r="AB48" s="9">
         <f>SUM(AB10:AB47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="AD48" s="10">
         <f t="shared" si="10"/>
-        <v>4486660</v>
+        <v>4486754</v>
       </c>
       <c r="AE48" s="12">
         <f>SUM(AE10:AE47)</f>
-        <v>10492230</v>
+        <v>10492324</v>
       </c>
       <c r="AF48" s="8">
         <f t="shared" si="11"/>
-        <v>0.93838323654269706</v>
+        <v>0.93839164352807902</v>
       </c>
       <c r="AG48" s="9">
         <f>SUM(AG10:AG47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="AI48" s="10">
         <f t="shared" si="12"/>
-        <v>2995987</v>
+        <v>2996061</v>
       </c>
       <c r="AJ48" s="9">
         <f>SUM(AJ10:AJ47)</f>
-        <v>6600699</v>
+        <v>6600773</v>
       </c>
       <c r="AK48" s="8">
         <f t="shared" si="13"/>
-        <v>0.92611753712496214</v>
+        <v>0.92612791976742881</v>
       </c>
       <c r="AL48" s="9">
         <f>SUM(AL10:AL47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AN48" s="10">
         <f t="shared" si="14"/>
-        <v>1213361</v>
+        <v>1213434</v>
       </c>
       <c r="AO48" s="9">
         <f>SUM(AO10:AO47)</f>
-        <v>6708530</v>
+        <v>6708603</v>
       </c>
       <c r="AP48" s="8">
         <f t="shared" si="15"/>
-        <v>0.93057331299402457</v>
+        <v>0.93058343918438946</v>
       </c>
       <c r="AQ48" s="9">
         <f>SUM(AQ10:AQ47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AS48" s="10">
         <f t="shared" si="16"/>
-        <v>4624724</v>
+        <v>4624812</v>
       </c>
       <c r="AT48" s="9">
         <f>SUM(AT10:AT47)</f>
-        <v>10740551</v>
+        <v>10740639</v>
       </c>
       <c r="AU48" s="8">
         <f t="shared" si="17"/>
-        <v>0.93975417327005517</v>
+        <v>0.93976187290923074</v>
       </c>
       <c r="AV48" s="9">
         <f>SUM(AV10:AV47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AX48" s="10">
         <f t="shared" si="18"/>
-        <v>2609911</v>
+        <v>2609983</v>
       </c>
       <c r="AY48" s="9">
         <f>SUM(AY10:AY47)</f>
-        <v>6760983</v>
+        <v>6761055</v>
       </c>
       <c r="AZ48" s="8">
         <f t="shared" si="19"/>
-        <v>0.93348080001480094</v>
+        <v>0.93349074096829854</v>
       </c>
       <c r="BA48" s="9">
         <f>SUM(BA10:BA47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="BC48" s="10">
         <f t="shared" si="20"/>
-        <v>2558932</v>
+        <v>2559005</v>
       </c>
       <c r="BD48" s="9">
         <f>SUM(BD10:BD47)</f>
-        <v>6870470</v>
+        <v>6870543</v>
       </c>
       <c r="BE48" s="8">
         <f t="shared" ref="BE48" si="26">BD48/BA48</f>
-        <v>0.939649112249615</v>
+        <v>0.93965909619324539</v>
       </c>
       <c r="BF48" s="9">
         <f>SUM(BF10:BF47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="BH48" s="10">
         <f t="shared" si="24"/>
-        <v>4819336</v>
+        <v>4819442</v>
       </c>
       <c r="BI48" s="9">
         <f>SUM(BI10:BI47)</f>
-        <v>10951001</v>
+        <v>10951107</v>
       </c>
       <c r="BJ48" s="8">
         <f t="shared" si="25"/>
-        <v>0.94151888105851778</v>
+        <v>0.94152799447211277</v>
       </c>
     </row>
   </sheetData>
